--- a/comprehensive_grocery_certifications.xlsx
+++ b/comprehensive_grocery_certifications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StardogChampion\TBL-Grocery-Scanner---DEVELOPMENT-VERSION-Active-development-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1CDC80-CD33-45AF-8D9E-43251CDF89FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DF5234-6FF9-4ADE-A23F-114E5B13D6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31886,7 +31886,7 @@
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <f ca="1">NOW()</f>
-        <v>46099.813945486108</v>
+        <v>46099.985527199075</v>
       </c>
     </row>
   </sheetData>

--- a/comprehensive_grocery_certifications.xlsx
+++ b/comprehensive_grocery_certifications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StardogChampion\TBL-Grocery-Scanner---DEVELOPMENT-VERSION-Active-development-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DF5234-6FF9-4ADE-A23F-114E5B13D6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6963343D-0F58-4A33-99A0-3C40EDA171FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="978">
   <si>
     <t>Product_Brand</t>
   </si>
@@ -2952,6 +2952,9 @@
   </si>
   <si>
     <t>peanut butter, nut butters, peanut butter bars</t>
+  </si>
+  <si>
+    <t>Crunch</t>
   </si>
 </sst>
 </file>
@@ -3077,7 +3080,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3382,7 +3385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K958"/>
+  <dimension ref="A1:K959"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -10727,7 +10730,9 @@
       <c r="G252" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H252" s="7"/>
+      <c r="H252" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I252" s="3" t="b">
         <v>0</v>
       </c>
@@ -10756,7 +10761,9 @@
       <c r="G253" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H253" s="7"/>
+      <c r="H253" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I253" s="3" t="b">
         <v>0</v>
       </c>
@@ -10843,7 +10850,9 @@
       <c r="G256" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H256" s="7"/>
+      <c r="H256" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I256" s="3" t="b">
         <v>0</v>
       </c>
@@ -10932,7 +10941,9 @@
       <c r="G259" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H259" s="7"/>
+      <c r="H259" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I259" s="3" t="b">
         <v>0</v>
       </c>
@@ -10961,7 +10972,9 @@
       <c r="G260" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H260" s="7"/>
+      <c r="H260" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I260" s="3" t="b">
         <v>0</v>
       </c>
@@ -10990,7 +11003,9 @@
       <c r="G261" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H261" s="7"/>
+      <c r="H261" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I261" s="3" t="b">
         <v>0</v>
       </c>
@@ -11048,7 +11063,9 @@
       <c r="G263" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H263" s="7"/>
+      <c r="H263" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I263" s="3" t="b">
         <v>0</v>
       </c>
@@ -11106,7 +11123,9 @@
       <c r="G265" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H265" s="7"/>
+      <c r="H265" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I265" s="3" t="b">
         <v>0</v>
       </c>
@@ -11117,36 +11136,40 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>268</v>
+        <v>977</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>257</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E266" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F266" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G266" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H266" s="7"/>
+      <c r="H266" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I266" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J266" s="9"/>
+      <c r="J266" s="10">
+        <v>46131</v>
+      </c>
       <c r="K266" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>257</v>
@@ -11175,7 +11198,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>257</v>
@@ -11193,7 +11216,9 @@
       <c r="G268" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H268" s="7"/>
+      <c r="H268" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I268" s="3" t="b">
         <v>0</v>
       </c>
@@ -11204,7 +11229,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>257</v>
@@ -11222,7 +11247,9 @@
       <c r="G269" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H269" s="7"/>
+      <c r="H269" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I269" s="3" t="b">
         <v>0</v>
       </c>
@@ -11233,7 +11260,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>257</v>
@@ -11251,7 +11278,9 @@
       <c r="G270" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H270" s="7"/>
+      <c r="H270" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I270" s="3" t="b">
         <v>0</v>
       </c>
@@ -11262,7 +11291,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>257</v>
@@ -11291,7 +11320,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>257</v>
@@ -11320,7 +11349,7 @@
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>257</v>
@@ -11333,7 +11362,7 @@
         <v>0</v>
       </c>
       <c r="F273" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G273" s="3" t="b">
         <v>0</v>
@@ -11351,7 +11380,7 @@
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>928</v>
+        <v>275</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>257</v>
@@ -11382,7 +11411,7 @@
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>276</v>
+        <v>928</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>257</v>
@@ -11395,12 +11424,14 @@
         <v>0</v>
       </c>
       <c r="F275" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H275" s="7"/>
+      <c r="H275" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I275" s="3" t="b">
         <v>0</v>
       </c>
@@ -11411,7 +11442,7 @@
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>257</v>
@@ -11429,7 +11460,9 @@
       <c r="G276" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H276" s="7"/>
+      <c r="H276" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I276" s="3" t="b">
         <v>0</v>
       </c>
@@ -11440,7 +11473,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>257</v>
@@ -11469,7 +11502,7 @@
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>257</v>
@@ -11498,7 +11531,7 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>903</v>
+        <v>279</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>257</v>
@@ -11511,23 +11544,25 @@
         <v>0</v>
       </c>
       <c r="F279" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G279" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H279" s="7"/>
+      <c r="H279" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I279" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J279" s="9"/>
       <c r="K279" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>280</v>
+        <v>903</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>257</v>
@@ -11540,7 +11575,7 @@
         <v>0</v>
       </c>
       <c r="F280" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G280" s="3" t="b">
         <v>0</v>
@@ -11551,12 +11586,12 @@
       </c>
       <c r="J280" s="9"/>
       <c r="K280" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>888</v>
+        <v>280</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>257</v>
@@ -11569,23 +11604,25 @@
         <v>0</v>
       </c>
       <c r="F281" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G281" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H281" s="7"/>
+      <c r="H281" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I281" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J281" s="9"/>
       <c r="K281" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>281</v>
+        <v>888</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>257</v>
@@ -11598,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="F282" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G282" s="3" t="b">
         <v>0</v>
@@ -11609,12 +11646,12 @@
       </c>
       <c r="J282" s="9"/>
       <c r="K282" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>257</v>
@@ -11643,7 +11680,7 @@
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>257</v>
@@ -11661,7 +11698,9 @@
       <c r="G284" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H284" s="7"/>
+      <c r="H284" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I284" s="3" t="b">
         <v>0</v>
       </c>
@@ -11672,7 +11711,7 @@
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>257</v>
@@ -11690,7 +11729,9 @@
       <c r="G285" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H285" s="7"/>
+      <c r="H285" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I285" s="3" t="b">
         <v>0</v>
       </c>
@@ -11701,7 +11742,7 @@
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>257</v>
@@ -11730,7 +11771,7 @@
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>257</v>
@@ -11748,7 +11789,9 @@
       <c r="G287" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H287" s="7"/>
+      <c r="H287" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I287" s="3" t="b">
         <v>0</v>
       </c>
@@ -11759,7 +11802,7 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>257</v>
@@ -11777,7 +11820,9 @@
       <c r="G288" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H288" s="7"/>
+      <c r="H288" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I288" s="3" t="b">
         <v>0</v>
       </c>
@@ -11788,20 +11833,20 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>950</v>
+        <v>287</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>257</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G289" s="3" t="b">
         <v>0</v>
@@ -11812,41 +11857,43 @@
       </c>
       <c r="J289" s="9"/>
       <c r="K289" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>288</v>
+        <v>950</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>257</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E290" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F290" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G290" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H290" s="7"/>
+      <c r="H290" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I290" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J290" s="9"/>
       <c r="K290" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>257</v>
@@ -11875,7 +11922,7 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>257</v>
@@ -11904,7 +11951,7 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>257</v>
@@ -11933,7 +11980,7 @@
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>257</v>
@@ -11951,7 +11998,9 @@
       <c r="G294" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H294" s="7"/>
+      <c r="H294" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I294" s="3" t="b">
         <v>0</v>
       </c>
@@ -11962,7 +12011,7 @@
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>257</v>
@@ -11991,7 +12040,7 @@
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>901</v>
+        <v>293</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>257</v>
@@ -12004,23 +12053,25 @@
         <v>0</v>
       </c>
       <c r="F296" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G296" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H296" s="7"/>
+      <c r="H296" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I296" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J296" s="9"/>
       <c r="K296" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>294</v>
+        <v>901</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>257</v>
@@ -12033,23 +12084,25 @@
         <v>0</v>
       </c>
       <c r="F297" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G297" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H297" s="7"/>
+      <c r="H297" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I297" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J297" s="9"/>
       <c r="K297" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>257</v>
@@ -12067,7 +12120,9 @@
       <c r="G298" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H298" s="7"/>
+      <c r="H298" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I298" s="3" t="b">
         <v>0</v>
       </c>
@@ -12078,7 +12133,7 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>257</v>
@@ -12107,7 +12162,7 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>257</v>
@@ -12125,7 +12180,6 @@
       <c r="G300" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H300" s="7"/>
       <c r="I300" s="3" t="b">
         <v>0</v>
       </c>
@@ -12136,7 +12190,7 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>257</v>
@@ -12154,7 +12208,9 @@
       <c r="G301" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H301" s="7"/>
+      <c r="H301" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I301" s="3" t="b">
         <v>0</v>
       </c>
@@ -12165,7 +12221,7 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>257</v>
@@ -12194,7 +12250,7 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>257</v>
@@ -12223,7 +12279,7 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>257</v>
@@ -12252,7 +12308,7 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>257</v>
@@ -12281,7 +12337,7 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>257</v>
@@ -12299,7 +12355,9 @@
       <c r="G306" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H306" s="7"/>
+      <c r="H306" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I306" s="3" t="b">
         <v>0</v>
       </c>
@@ -12310,7 +12368,7 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>257</v>
@@ -12339,7 +12397,7 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>257</v>
@@ -12368,7 +12426,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>257</v>
@@ -12386,7 +12444,9 @@
       <c r="G309" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H309" s="7"/>
+      <c r="H309" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I309" s="3" t="b">
         <v>0</v>
       </c>
@@ -12397,7 +12457,7 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>257</v>
@@ -12426,7 +12486,7 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>257</v>
@@ -12444,7 +12504,9 @@
       <c r="G311" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H311" s="7"/>
+      <c r="H311" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I311" s="3" t="b">
         <v>0</v>
       </c>
@@ -12455,7 +12517,7 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>257</v>
@@ -12473,7 +12535,9 @@
       <c r="G312" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H312" s="7"/>
+      <c r="H312" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I312" s="3" t="b">
         <v>0</v>
       </c>
@@ -12484,10 +12548,10 @@
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>311</v>
+        <v>257</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" s="3" t="b">
@@ -12513,7 +12577,7 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>311</v>
@@ -12542,7 +12606,7 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>311</v>
@@ -12571,7 +12635,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>311</v>
@@ -12600,7 +12664,7 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>311</v>
@@ -12629,7 +12693,7 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>311</v>
@@ -12658,7 +12722,7 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>311</v>
@@ -12687,7 +12751,7 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>311</v>
@@ -12716,7 +12780,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>311</v>
@@ -12745,7 +12809,7 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>311</v>
@@ -12774,7 +12838,7 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>311</v>
@@ -12803,7 +12867,7 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>311</v>
@@ -12832,7 +12896,7 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>311</v>
@@ -12861,7 +12925,7 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>311</v>
@@ -12890,7 +12954,7 @@
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>311</v>
@@ -12919,7 +12983,7 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>311</v>
@@ -12948,7 +13012,7 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>311</v>
@@ -12977,7 +13041,7 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>311</v>
@@ -13006,7 +13070,7 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>311</v>
@@ -13035,7 +13099,7 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>311</v>
@@ -13064,7 +13128,7 @@
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>311</v>
@@ -13093,7 +13157,7 @@
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>311</v>
@@ -13122,7 +13186,7 @@
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>311</v>
@@ -13151,7 +13215,7 @@
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>311</v>
@@ -13180,7 +13244,7 @@
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>311</v>
@@ -13209,7 +13273,7 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>311</v>
@@ -13238,7 +13302,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>311</v>
@@ -13267,7 +13331,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>311</v>
@@ -13296,7 +13360,7 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>311</v>
@@ -13325,7 +13389,7 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>311</v>
@@ -13354,7 +13418,7 @@
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>311</v>
@@ -13383,7 +13447,7 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>311</v>
@@ -13412,7 +13476,7 @@
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>311</v>
@@ -13441,7 +13505,7 @@
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>311</v>
@@ -13470,7 +13534,7 @@
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>311</v>
@@ -13499,7 +13563,7 @@
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>311</v>
@@ -13528,7 +13592,7 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>311</v>
@@ -13557,7 +13621,7 @@
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>311</v>
@@ -13586,7 +13650,7 @@
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>311</v>
@@ -13615,7 +13679,7 @@
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>311</v>
@@ -13644,7 +13708,7 @@
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>311</v>
@@ -13673,7 +13737,7 @@
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>311</v>
@@ -13702,7 +13766,7 @@
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>311</v>
@@ -13731,7 +13795,7 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>311</v>
@@ -13760,7 +13824,7 @@
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>311</v>
@@ -13789,7 +13853,7 @@
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>311</v>
@@ -13818,7 +13882,7 @@
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>311</v>
@@ -13847,7 +13911,7 @@
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>311</v>
@@ -13876,7 +13940,7 @@
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>311</v>
@@ -13905,10 +13969,10 @@
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
-        <v>876</v>
+        <v>359</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>361</v>
+        <v>311</v>
       </c>
       <c r="C362" s="2"/>
       <c r="D362" s="3" t="b">
@@ -13921,22 +13985,20 @@
         <v>0</v>
       </c>
       <c r="G362" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H362" s="7" t="s">
-        <v>954</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H362" s="7"/>
       <c r="I362" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J362" s="9"/>
       <c r="K362" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
-        <v>360</v>
+        <v>876</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>361</v>
@@ -13952,20 +14014,22 @@
         <v>0</v>
       </c>
       <c r="G363" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H363" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H363" s="7" t="s">
+        <v>954</v>
+      </c>
       <c r="I363" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J363" s="9"/>
       <c r="K363" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>361</v>
@@ -13994,7 +14058,7 @@
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>361</v>
@@ -14023,7 +14087,7 @@
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>361</v>
@@ -14052,7 +14116,7 @@
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>361</v>
@@ -14081,7 +14145,7 @@
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>361</v>
@@ -14110,7 +14174,7 @@
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>361</v>
@@ -14139,7 +14203,7 @@
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>361</v>
@@ -14168,7 +14232,7 @@
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>361</v>
@@ -14197,7 +14261,7 @@
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>361</v>
@@ -14226,7 +14290,7 @@
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>361</v>
@@ -14255,7 +14319,7 @@
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>361</v>
@@ -14284,7 +14348,7 @@
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>361</v>
@@ -14313,7 +14377,7 @@
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>361</v>
@@ -14342,7 +14406,7 @@
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>361</v>
@@ -14371,7 +14435,7 @@
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>361</v>
@@ -14400,7 +14464,7 @@
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>361</v>
@@ -14429,7 +14493,7 @@
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>361</v>
@@ -14458,7 +14522,7 @@
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>361</v>
@@ -14487,7 +14551,7 @@
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>361</v>
@@ -14516,7 +14580,7 @@
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>361</v>
@@ -14545,7 +14609,7 @@
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>361</v>
@@ -14574,7 +14638,7 @@
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>361</v>
@@ -14603,7 +14667,7 @@
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>361</v>
@@ -14632,7 +14696,7 @@
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>361</v>
@@ -14661,7 +14725,7 @@
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>361</v>
@@ -14690,7 +14754,7 @@
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>361</v>
@@ -14719,7 +14783,7 @@
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>361</v>
@@ -14748,7 +14812,7 @@
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>361</v>
@@ -14777,7 +14841,7 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>361</v>
@@ -14806,7 +14870,7 @@
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>361</v>
@@ -14835,7 +14899,7 @@
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>361</v>
@@ -14864,7 +14928,7 @@
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>361</v>
@@ -14893,7 +14957,7 @@
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>361</v>
@@ -14922,7 +14986,7 @@
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>361</v>
@@ -14951,7 +15015,7 @@
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>361</v>
@@ -14980,7 +15044,7 @@
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>361</v>
@@ -15009,7 +15073,7 @@
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>361</v>
@@ -15038,7 +15102,7 @@
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>361</v>
@@ -15067,7 +15131,7 @@
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>361</v>
@@ -15096,7 +15160,7 @@
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>361</v>
@@ -15125,7 +15189,7 @@
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>361</v>
@@ -15154,7 +15218,7 @@
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>361</v>
@@ -15183,7 +15247,7 @@
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>361</v>
@@ -15212,7 +15276,7 @@
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>361</v>
@@ -15241,17 +15305,17 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>891</v>
+        <v>405</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>929</v>
+        <v>361</v>
       </c>
       <c r="C408" s="2"/>
       <c r="D408" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E408" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F408" s="3" t="b">
         <v>0</v>
@@ -15265,25 +15329,25 @@
       </c>
       <c r="J408" s="9"/>
       <c r="K408" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>406</v>
+        <v>891</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E409" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F409" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" s="3" t="b">
         <v>0</v>
@@ -15299,7 +15363,7 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>929</v>
@@ -15312,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="F410" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G410" s="3" t="b">
         <v>0</v>
@@ -15323,12 +15387,12 @@
       </c>
       <c r="J410" s="9"/>
       <c r="K410" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>919</v>
+        <v>407</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>929</v>
@@ -15341,7 +15405,7 @@
         <v>0</v>
       </c>
       <c r="F411" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G411" s="3" t="b">
         <v>0</v>
@@ -15352,12 +15416,12 @@
       </c>
       <c r="J411" s="9"/>
       <c r="K411" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>408</v>
+        <v>919</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>929</v>
@@ -15370,7 +15434,7 @@
         <v>0</v>
       </c>
       <c r="F412" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G412" s="3" t="b">
         <v>0</v>
@@ -15381,12 +15445,12 @@
       </c>
       <c r="J412" s="9"/>
       <c r="K412" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
-        <v>892</v>
+        <v>408</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>929</v>
@@ -15396,7 +15460,7 @@
         <v>0</v>
       </c>
       <c r="E413" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F413" s="3" t="b">
         <v>0</v>
@@ -15406,16 +15470,16 @@
       </c>
       <c r="H413" s="7"/>
       <c r="I413" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J413" s="9"/>
       <c r="K413" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
-        <v>409</v>
+        <v>892</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>929</v>
@@ -15425,7 +15489,7 @@
         <v>0</v>
       </c>
       <c r="E414" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F414" s="3" t="b">
         <v>0</v>
@@ -15435,16 +15499,16 @@
       </c>
       <c r="H414" s="7"/>
       <c r="I414" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J414" s="9"/>
       <c r="K414" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>929</v>
@@ -15473,7 +15537,7 @@
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
-        <v>915</v>
+        <v>410</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>929</v>
@@ -15486,7 +15550,7 @@
         <v>0</v>
       </c>
       <c r="F416" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G416" s="3" t="b">
         <v>0</v>
@@ -15497,12 +15561,12 @@
       </c>
       <c r="J416" s="9"/>
       <c r="K416" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>890</v>
+        <v>915</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>929</v>
@@ -15512,10 +15576,10 @@
         <v>0</v>
       </c>
       <c r="E417" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F417" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="F417" s="3" t="b">
-        <v>0</v>
       </c>
       <c r="G417" s="3" t="b">
         <v>0</v>
@@ -15531,7 +15595,7 @@
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>929</v>
@@ -15541,10 +15605,10 @@
         <v>0</v>
       </c>
       <c r="E418" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F418" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G418" s="3" t="b">
         <v>0</v>
@@ -15560,7 +15624,7 @@
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>411</v>
+        <v>898</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>929</v>
@@ -15573,7 +15637,7 @@
         <v>0</v>
       </c>
       <c r="F419" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G419" s="3" t="b">
         <v>0</v>
@@ -15584,12 +15648,12 @@
       </c>
       <c r="J419" s="9"/>
       <c r="K419" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>929</v>
@@ -15618,7 +15682,7 @@
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>929</v>
@@ -15647,7 +15711,7 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>929</v>
@@ -15676,7 +15740,7 @@
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
-        <v>893</v>
+        <v>414</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>929</v>
@@ -15686,7 +15750,7 @@
         <v>0</v>
       </c>
       <c r="E423" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F423" s="3" t="b">
         <v>0</v>
@@ -15700,12 +15764,12 @@
       </c>
       <c r="J423" s="9"/>
       <c r="K423" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>917</v>
+        <v>893</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>929</v>
@@ -15715,10 +15779,10 @@
         <v>0</v>
       </c>
       <c r="E424" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F424" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G424" s="3" t="b">
         <v>0</v>
@@ -15734,7 +15798,7 @@
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
-        <v>104</v>
+        <v>917</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>929</v>
@@ -15747,7 +15811,7 @@
         <v>0</v>
       </c>
       <c r="F425" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G425" s="3" t="b">
         <v>0</v>
@@ -15758,12 +15822,12 @@
       </c>
       <c r="J425" s="9"/>
       <c r="K425" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>415</v>
+        <v>104</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>929</v>
@@ -15792,7 +15856,7 @@
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>929</v>
@@ -15821,7 +15885,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>897</v>
+        <v>416</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>929</v>
@@ -15834,7 +15898,7 @@
         <v>0</v>
       </c>
       <c r="F428" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G428" s="3" t="b">
         <v>0</v>
@@ -15845,25 +15909,25 @@
       </c>
       <c r="J428" s="9"/>
       <c r="K428" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>417</v>
+        <v>897</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C429" s="2"/>
       <c r="D429" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E429" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F429" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="E429" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F429" s="3" t="b">
-        <v>0</v>
       </c>
       <c r="G429" s="3" t="b">
         <v>0</v>
@@ -15879,14 +15943,14 @@
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C430" s="2"/>
       <c r="D430" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E430" s="3" t="b">
         <v>0</v>
@@ -15903,12 +15967,12 @@
       </c>
       <c r="J430" s="9"/>
       <c r="K430" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>929</v>
@@ -15937,7 +16001,7 @@
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>929</v>
@@ -15966,7 +16030,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>916</v>
+        <v>420</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>929</v>
@@ -15979,25 +16043,23 @@
         <v>0</v>
       </c>
       <c r="F433" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G433" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H433" s="7" t="s">
-        <v>932</v>
-      </c>
+      <c r="H433" s="7"/>
       <c r="I433" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J433" s="9"/>
       <c r="K433" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>421</v>
+        <v>916</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>929</v>
@@ -16015,7 +16077,9 @@
       <c r="G434" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H434" s="7"/>
+      <c r="H434" s="7" t="s">
+        <v>932</v>
+      </c>
       <c r="I434" s="3" t="b">
         <v>0</v>
       </c>
@@ -16026,7 +16090,7 @@
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
-        <v>114</v>
+        <v>421</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>929</v>
@@ -16039,7 +16103,7 @@
         <v>0</v>
       </c>
       <c r="F435" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G435" s="3" t="b">
         <v>0</v>
@@ -16050,12 +16114,12 @@
       </c>
       <c r="J435" s="9"/>
       <c r="K435" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>894</v>
+        <v>114</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>929</v>
@@ -16065,7 +16129,7 @@
         <v>0</v>
       </c>
       <c r="E436" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F436" s="3" t="b">
         <v>0</v>
@@ -16075,16 +16139,16 @@
       </c>
       <c r="H436" s="7"/>
       <c r="I436" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J436" s="9"/>
       <c r="K436" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>422</v>
+        <v>894</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>929</v>
@@ -16094,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="E437" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F437" s="3" t="b">
         <v>0</v>
@@ -16104,16 +16168,16 @@
       </c>
       <c r="H437" s="7"/>
       <c r="I437" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J437" s="9"/>
       <c r="K437" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>929</v>
@@ -16142,7 +16206,7 @@
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>929</v>
@@ -16171,7 +16235,7 @@
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
-        <v>935</v>
+        <v>424</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>929</v>
@@ -16184,25 +16248,23 @@
         <v>0</v>
       </c>
       <c r="F440" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G440" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H440" s="7" t="s">
-        <v>927</v>
-      </c>
+      <c r="H440" s="7"/>
       <c r="I440" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J440" s="9"/>
       <c r="K440" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
-        <v>878</v>
+        <v>935</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>929</v>
@@ -16220,7 +16282,9 @@
       <c r="G441" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H441" s="7"/>
+      <c r="H441" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I441" s="3" t="b">
         <v>0</v>
       </c>
@@ -16231,7 +16295,7 @@
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>425</v>
+        <v>878</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>929</v>
@@ -16244,7 +16308,7 @@
         <v>0</v>
       </c>
       <c r="F442" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G442" s="3" t="b">
         <v>0</v>
@@ -16255,12 +16319,12 @@
       </c>
       <c r="J442" s="9"/>
       <c r="K442" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>929</v>
@@ -16289,7 +16353,7 @@
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>884</v>
+        <v>426</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>929</v>
@@ -16302,7 +16366,7 @@
         <v>0</v>
       </c>
       <c r="F444" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G444" s="3" t="b">
         <v>0</v>
@@ -16313,12 +16377,12 @@
       </c>
       <c r="J444" s="9"/>
       <c r="K444" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>929</v>
@@ -16347,7 +16411,7 @@
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>119</v>
+        <v>883</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>929</v>
@@ -16357,7 +16421,7 @@
         <v>0</v>
       </c>
       <c r="E446" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F446" s="3" t="b">
         <v>1</v>
@@ -16371,12 +16435,12 @@
       </c>
       <c r="J446" s="9"/>
       <c r="K446" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>427</v>
+        <v>119</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>929</v>
@@ -16386,10 +16450,10 @@
         <v>0</v>
       </c>
       <c r="E447" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F447" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G447" s="3" t="b">
         <v>0</v>
@@ -16405,7 +16469,7 @@
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>888</v>
+        <v>427</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>929</v>
@@ -16418,7 +16482,7 @@
         <v>0</v>
       </c>
       <c r="F448" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G448" s="3" t="b">
         <v>0</v>
@@ -16429,12 +16493,12 @@
       </c>
       <c r="J448" s="9"/>
       <c r="K448" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>428</v>
+        <v>888</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>929</v>
@@ -16463,7 +16527,7 @@
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>929</v>
@@ -16492,7 +16556,7 @@
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
-        <v>896</v>
+        <v>429</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>929</v>
@@ -16510,9 +16574,7 @@
       <c r="G451" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H451" s="7" t="s">
-        <v>936</v>
-      </c>
+      <c r="H451" s="7"/>
       <c r="I451" s="3" t="b">
         <v>0</v>
       </c>
@@ -16523,7 +16585,7 @@
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>929</v>
@@ -16541,7 +16603,9 @@
       <c r="G452" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H452" s="7"/>
+      <c r="H452" s="7" t="s">
+        <v>936</v>
+      </c>
       <c r="I452" s="3" t="b">
         <v>0</v>
       </c>
@@ -16552,7 +16616,7 @@
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>430</v>
+        <v>911</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>929</v>
@@ -16565,7 +16629,7 @@
         <v>0</v>
       </c>
       <c r="F453" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G453" s="3" t="b">
         <v>0</v>
@@ -16576,12 +16640,12 @@
       </c>
       <c r="J453" s="9"/>
       <c r="K453" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>929</v>
@@ -16610,7 +16674,7 @@
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
-        <v>123</v>
+        <v>431</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>929</v>
@@ -16639,7 +16703,7 @@
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
-        <v>432</v>
+        <v>123</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>929</v>
@@ -16668,7 +16732,7 @@
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>929</v>
@@ -16697,7 +16761,7 @@
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>929</v>
@@ -16726,38 +16790,36 @@
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
-        <v>947</v>
+        <v>434</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C459" s="2"/>
       <c r="D459" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E459" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F459" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G459" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H459" s="7" t="s">
-        <v>939</v>
-      </c>
+      <c r="H459" s="7"/>
       <c r="I459" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J459" s="9"/>
       <c r="K459" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>929</v>
@@ -16788,17 +16850,17 @@
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
-        <v>881</v>
+        <v>906</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C461" s="2"/>
       <c r="D461" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E461" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F461" s="3" t="b">
         <v>1</v>
@@ -16807,7 +16869,7 @@
         <v>0</v>
       </c>
       <c r="H461" s="7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I461" s="3" t="b">
         <v>0</v>
@@ -16819,17 +16881,17 @@
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
-        <v>907</v>
+        <v>881</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C462" s="2"/>
       <c r="D462" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E462" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F462" s="3" t="b">
         <v>1</v>
@@ -16838,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="H462" s="7" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I462" s="3" t="b">
         <v>0</v>
@@ -16850,36 +16912,38 @@
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
-        <v>435</v>
+        <v>907</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C463" s="2"/>
       <c r="D463" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E463" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F463" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G463" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H463" s="7"/>
+      <c r="H463" s="7" t="s">
+        <v>941</v>
+      </c>
       <c r="I463" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J463" s="9"/>
       <c r="K463" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
-        <v>887</v>
+        <v>435</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>929</v>
@@ -16892,7 +16956,7 @@
         <v>0</v>
       </c>
       <c r="F464" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G464" s="3" t="b">
         <v>0</v>
@@ -16903,12 +16967,12 @@
       </c>
       <c r="J464" s="9"/>
       <c r="K464" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
-        <v>436</v>
+        <v>887</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>929</v>
@@ -16921,7 +16985,7 @@
         <v>0</v>
       </c>
       <c r="F465" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G465" s="3" t="b">
         <v>0</v>
@@ -16932,12 +16996,12 @@
       </c>
       <c r="J465" s="9"/>
       <c r="K465" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>929</v>
@@ -16950,7 +17014,7 @@
         <v>0</v>
       </c>
       <c r="F466" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G466" s="3" t="b">
         <v>0</v>
@@ -16961,12 +17025,12 @@
       </c>
       <c r="J466" s="9"/>
       <c r="K466" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
-        <v>131</v>
+        <v>437</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>929</v>
@@ -16979,7 +17043,7 @@
         <v>0</v>
       </c>
       <c r="F467" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G467" s="3" t="b">
         <v>0</v>
@@ -16990,12 +17054,12 @@
       </c>
       <c r="J467" s="9"/>
       <c r="K467" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
-        <v>438</v>
+        <v>131</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>929</v>
@@ -17024,7 +17088,7 @@
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>929</v>
@@ -17053,7 +17117,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
-        <v>912</v>
+        <v>439</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>929</v>
@@ -17066,7 +17130,7 @@
         <v>0</v>
       </c>
       <c r="F470" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G470" s="3" t="b">
         <v>0</v>
@@ -17077,12 +17141,12 @@
       </c>
       <c r="J470" s="9"/>
       <c r="K470" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>929</v>
@@ -17111,7 +17175,7 @@
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>929</v>
@@ -17140,7 +17204,7 @@
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>929</v>
@@ -17150,7 +17214,7 @@
         <v>0</v>
       </c>
       <c r="E473" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F473" s="3" t="b">
         <v>1</v>
@@ -17169,7 +17233,7 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>929</v>
@@ -17179,7 +17243,7 @@
         <v>0</v>
       </c>
       <c r="E474" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F474" s="3" t="b">
         <v>1</v>
@@ -17198,7 +17262,7 @@
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>929</v>
@@ -17227,7 +17291,7 @@
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
-        <v>143</v>
+        <v>885</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>929</v>
@@ -17237,17 +17301,15 @@
         <v>0</v>
       </c>
       <c r="E476" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F476" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F476" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G476" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H476" s="7" t="s">
-        <v>932</v>
-      </c>
+      <c r="H476" s="7"/>
       <c r="I476" s="3" t="b">
         <v>0</v>
       </c>
@@ -17258,7 +17320,7 @@
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
-        <v>440</v>
+        <v>143</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>929</v>
@@ -17268,7 +17330,7 @@
         <v>0</v>
       </c>
       <c r="E477" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F477" s="3" t="b">
         <v>0</v>
@@ -17276,18 +17338,20 @@
       <c r="G477" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H477" s="7"/>
+      <c r="H477" s="7" t="s">
+        <v>932</v>
+      </c>
       <c r="I477" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J477" s="9"/>
       <c r="K477" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" s="2" t="s">
-        <v>889</v>
+        <v>440</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>929</v>
@@ -17297,7 +17361,7 @@
         <v>0</v>
       </c>
       <c r="E478" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F478" s="3" t="b">
         <v>0</v>
@@ -17311,12 +17375,12 @@
       </c>
       <c r="J478" s="9"/>
       <c r="K478" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
-        <v>920</v>
+        <v>889</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>929</v>
@@ -17326,10 +17390,10 @@
         <v>0</v>
       </c>
       <c r="E479" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F479" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G479" s="3" t="b">
         <v>0</v>
@@ -17345,7 +17409,7 @@
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>929</v>
@@ -17374,7 +17438,7 @@
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
-        <v>441</v>
+        <v>910</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>929</v>
@@ -17387,7 +17451,7 @@
         <v>0</v>
       </c>
       <c r="F481" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G481" s="3" t="b">
         <v>0</v>
@@ -17398,12 +17462,12 @@
       </c>
       <c r="J481" s="9"/>
       <c r="K481" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
-        <v>886</v>
+        <v>441</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>929</v>
@@ -17416,7 +17480,7 @@
         <v>0</v>
       </c>
       <c r="F482" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G482" s="3" t="b">
         <v>0</v>
@@ -17427,12 +17491,12 @@
       </c>
       <c r="J482" s="9"/>
       <c r="K482" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>929</v>
@@ -17461,7 +17525,7 @@
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>929</v>
@@ -17490,7 +17554,7 @@
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
-        <v>914</v>
+        <v>879</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>929</v>
@@ -17519,7 +17583,7 @@
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
-        <v>442</v>
+        <v>914</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>929</v>
@@ -17548,7 +17612,7 @@
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>929</v>
@@ -17561,7 +17625,7 @@
         <v>0</v>
       </c>
       <c r="F487" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G487" s="3" t="b">
         <v>0</v>
@@ -17572,12 +17636,12 @@
       </c>
       <c r="J487" s="9"/>
       <c r="K487" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>929</v>
@@ -17606,7 +17670,7 @@
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
-        <v>877</v>
+        <v>444</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>929</v>
@@ -17619,7 +17683,7 @@
         <v>0</v>
       </c>
       <c r="F489" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G489" s="3" t="b">
         <v>0</v>
@@ -17630,12 +17694,12 @@
       </c>
       <c r="J489" s="9"/>
       <c r="K489" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
-        <v>148</v>
+        <v>877</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>929</v>
@@ -17648,7 +17712,7 @@
         <v>0</v>
       </c>
       <c r="F490" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G490" s="3" t="b">
         <v>0</v>
@@ -17659,12 +17723,12 @@
       </c>
       <c r="J490" s="9"/>
       <c r="K490" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
-        <v>445</v>
+        <v>148</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>929</v>
@@ -17693,7 +17757,7 @@
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>929</v>
@@ -17706,7 +17770,7 @@
         <v>0</v>
       </c>
       <c r="F492" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G492" s="3" t="b">
         <v>0</v>
@@ -17717,12 +17781,12 @@
       </c>
       <c r="J492" s="9"/>
       <c r="K492" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
-        <v>899</v>
+        <v>446</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>929</v>
@@ -17751,7 +17815,7 @@
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
-        <v>447</v>
+        <v>899</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>929</v>
@@ -17780,7 +17844,7 @@
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495" s="2" t="s">
-        <v>895</v>
+        <v>447</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>929</v>
@@ -17809,7 +17873,7 @@
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496" s="2" t="s">
-        <v>918</v>
+        <v>895</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>929</v>
@@ -17819,7 +17883,7 @@
         <v>0</v>
       </c>
       <c r="E496" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F496" s="3" t="b">
         <v>1</v>
@@ -17838,20 +17902,20 @@
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
-        <v>448</v>
+        <v>918</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>449</v>
+        <v>929</v>
       </c>
       <c r="C497" s="2"/>
       <c r="D497" s="3" t="b">
         <v>0</v>
       </c>
       <c r="E497" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F497" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G497" s="3" t="b">
         <v>0</v>
@@ -17862,12 +17926,12 @@
       </c>
       <c r="J497" s="9"/>
       <c r="K497" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
-        <v>313</v>
+        <v>448</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>449</v>
@@ -17896,7 +17960,7 @@
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
-        <v>450</v>
+        <v>313</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>449</v>
@@ -17925,7 +17989,7 @@
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>449</v>
@@ -17954,7 +18018,7 @@
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>449</v>
@@ -17983,7 +18047,7 @@
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>449</v>
@@ -18012,7 +18076,7 @@
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>449</v>
@@ -18041,7 +18105,7 @@
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>449</v>
@@ -18070,7 +18134,7 @@
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>449</v>
@@ -18099,7 +18163,7 @@
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A506" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>449</v>
@@ -18128,7 +18192,7 @@
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>449</v>
@@ -18157,7 +18221,7 @@
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>449</v>
@@ -18186,7 +18250,7 @@
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>449</v>
@@ -18215,7 +18279,7 @@
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>449</v>
@@ -18244,7 +18308,7 @@
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>449</v>
@@ -18273,7 +18337,7 @@
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>449</v>
@@ -18302,7 +18366,7 @@
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>449</v>
@@ -18331,7 +18395,7 @@
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>449</v>
@@ -18360,7 +18424,7 @@
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>449</v>
@@ -18389,7 +18453,7 @@
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>449</v>
@@ -18418,7 +18482,7 @@
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>449</v>
@@ -18447,7 +18511,7 @@
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A518" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>449</v>
@@ -18476,7 +18540,7 @@
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A519" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>449</v>
@@ -18505,7 +18569,7 @@
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A520" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>449</v>
@@ -18534,7 +18598,7 @@
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A521" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>449</v>
@@ -18563,7 +18627,7 @@
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A522" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>449</v>
@@ -18592,7 +18656,7 @@
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>449</v>
@@ -18621,7 +18685,7 @@
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A524" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>449</v>
@@ -18650,7 +18714,7 @@
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A525" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>449</v>
@@ -18679,7 +18743,7 @@
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A526" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>449</v>
@@ -18708,7 +18772,7 @@
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>449</v>
@@ -18737,7 +18801,7 @@
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>449</v>
@@ -18766,7 +18830,7 @@
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>449</v>
@@ -18795,7 +18859,7 @@
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>449</v>
@@ -18824,7 +18888,7 @@
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>449</v>
@@ -18853,7 +18917,7 @@
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>449</v>
@@ -18882,7 +18946,7 @@
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>449</v>
@@ -18911,7 +18975,7 @@
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>449</v>
@@ -18940,7 +19004,7 @@
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A535" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>449</v>
@@ -18969,7 +19033,7 @@
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>449</v>
@@ -18998,7 +19062,7 @@
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A537" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>449</v>
@@ -19027,7 +19091,7 @@
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>449</v>
@@ -19056,7 +19120,7 @@
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>449</v>
@@ -19085,7 +19149,7 @@
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>449</v>
@@ -19114,7 +19178,7 @@
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>449</v>
@@ -19143,7 +19207,7 @@
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A542" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>449</v>
@@ -19172,7 +19236,7 @@
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A543" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>449</v>
@@ -19201,7 +19265,7 @@
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>449</v>
@@ -19230,10 +19294,10 @@
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>497</v>
+        <v>449</v>
       </c>
       <c r="C545" s="2"/>
       <c r="D545" s="3" t="b">
@@ -19259,7 +19323,7 @@
     </row>
     <row r="546" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
-        <v>313</v>
+        <v>496</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>497</v>
@@ -19288,7 +19352,7 @@
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
-        <v>498</v>
+        <v>313</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>497</v>
@@ -19317,7 +19381,7 @@
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>497</v>
@@ -19346,7 +19410,7 @@
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>497</v>
@@ -19375,7 +19439,7 @@
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>497</v>
@@ -19404,7 +19468,7 @@
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>497</v>
@@ -19433,7 +19497,7 @@
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>497</v>
@@ -19462,7 +19526,7 @@
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>497</v>
@@ -19491,7 +19555,7 @@
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A554" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>497</v>
@@ -19520,7 +19584,7 @@
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>497</v>
@@ -19549,7 +19613,7 @@
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>497</v>
@@ -19578,7 +19642,7 @@
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>497</v>
@@ -19607,7 +19671,7 @@
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A558" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>497</v>
@@ -19636,7 +19700,7 @@
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A559" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>497</v>
@@ -19665,7 +19729,7 @@
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A560" s="2" t="s">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>497</v>
@@ -19694,7 +19758,7 @@
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A561" s="2" t="s">
-        <v>511</v>
+        <v>220</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>497</v>
@@ -19723,7 +19787,7 @@
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A562" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>497</v>
@@ -19752,7 +19816,7 @@
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A563" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>497</v>
@@ -19781,7 +19845,7 @@
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A564" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>497</v>
@@ -19810,7 +19874,7 @@
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A565" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>497</v>
@@ -19839,7 +19903,7 @@
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A566" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>497</v>
@@ -19868,7 +19932,7 @@
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A567" s="2" t="s">
-        <v>227</v>
+        <v>516</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>497</v>
@@ -19897,7 +19961,7 @@
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A568" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>497</v>
@@ -19926,7 +19990,7 @@
     </row>
     <row r="569" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A569" s="2" t="s">
-        <v>517</v>
+        <v>233</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>497</v>
@@ -19955,7 +20019,7 @@
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A570" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>497</v>
@@ -19984,7 +20048,7 @@
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A571" s="2" t="s">
-        <v>237</v>
+        <v>518</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>497</v>
@@ -20013,7 +20077,7 @@
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A572" s="2" t="s">
-        <v>519</v>
+        <v>237</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>497</v>
@@ -20042,7 +20106,7 @@
     </row>
     <row r="573" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A573" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>497</v>
@@ -20071,7 +20135,7 @@
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A574" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>497</v>
@@ -20100,7 +20164,7 @@
     </row>
     <row r="575" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A575" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>497</v>
@@ -20129,7 +20193,7 @@
     </row>
     <row r="576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A576" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>497</v>
@@ -20158,7 +20222,7 @@
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A577" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>497</v>
@@ -20187,7 +20251,7 @@
     </row>
     <row r="578" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A578" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>497</v>
@@ -20216,7 +20280,7 @@
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A579" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>497</v>
@@ -20245,7 +20309,7 @@
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A580" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>497</v>
@@ -20274,7 +20338,7 @@
     </row>
     <row r="581" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A581" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>497</v>
@@ -20303,7 +20367,7 @@
     </row>
     <row r="582" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A582" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>497</v>
@@ -20332,7 +20396,7 @@
     </row>
     <row r="583" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A583" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>497</v>
@@ -20361,7 +20425,7 @@
     </row>
     <row r="584" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A584" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>497</v>
@@ -20390,7 +20454,7 @@
     </row>
     <row r="585" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A585" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>497</v>
@@ -20419,7 +20483,7 @@
     </row>
     <row r="586" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A586" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>497</v>
@@ -20448,7 +20512,7 @@
     </row>
     <row r="587" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A587" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>497</v>
@@ -20477,7 +20541,7 @@
     </row>
     <row r="588" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A588" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>497</v>
@@ -20506,7 +20570,7 @@
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A589" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>497</v>
@@ -20535,7 +20599,7 @@
     </row>
     <row r="590" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A590" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>497</v>
@@ -20564,7 +20628,7 @@
     </row>
     <row r="591" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A591" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>497</v>
@@ -20593,7 +20657,7 @@
     </row>
     <row r="592" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A592" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>497</v>
@@ -20622,7 +20686,7 @@
     </row>
     <row r="593" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A593" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>497</v>
@@ -20651,7 +20715,7 @@
     </row>
     <row r="594" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A594" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>497</v>
@@ -20680,7 +20744,7 @@
     </row>
     <row r="595" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A595" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>497</v>
@@ -20709,10 +20773,10 @@
     </row>
     <row r="596" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A596" s="2" t="s">
-        <v>876</v>
+        <v>542</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>544</v>
+        <v>497</v>
       </c>
       <c r="C596" s="2"/>
       <c r="D596" s="3" t="b">
@@ -20725,24 +20789,20 @@
         <v>0</v>
       </c>
       <c r="G596" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H596" s="7" t="s">
-        <v>955</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H596" s="7"/>
       <c r="I596" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J596" s="10">
-        <v>46095</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J596" s="9"/>
       <c r="K596" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="597" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A597" s="2" t="s">
-        <v>543</v>
+        <v>876</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>544</v>
@@ -20758,20 +20818,24 @@
         <v>0</v>
       </c>
       <c r="G597" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H597" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H597" s="7" t="s">
+        <v>955</v>
+      </c>
       <c r="I597" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J597" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J597" s="10">
+        <v>46095</v>
+      </c>
       <c r="K597" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A598" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>544</v>
@@ -20800,7 +20864,7 @@
     </row>
     <row r="599" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A599" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>544</v>
@@ -20829,7 +20893,7 @@
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A600" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>544</v>
@@ -20858,7 +20922,7 @@
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A601" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>544</v>
@@ -20887,7 +20951,7 @@
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A602" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>544</v>
@@ -20916,7 +20980,7 @@
     </row>
     <row r="603" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A603" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>544</v>
@@ -20945,7 +21009,7 @@
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A604" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>544</v>
@@ -20974,7 +21038,7 @@
     </row>
     <row r="605" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A605" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>544</v>
@@ -21003,7 +21067,7 @@
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A606" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>544</v>
@@ -21032,7 +21096,7 @@
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A607" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>544</v>
@@ -21061,7 +21125,7 @@
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A608" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>544</v>
@@ -21090,7 +21154,7 @@
     </row>
     <row r="609" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A609" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>544</v>
@@ -21119,7 +21183,7 @@
     </row>
     <row r="610" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A610" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>544</v>
@@ -21148,7 +21212,7 @@
     </row>
     <row r="611" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A611" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>544</v>
@@ -21177,7 +21241,7 @@
     </row>
     <row r="612" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A612" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>544</v>
@@ -21206,7 +21270,7 @@
     </row>
     <row r="613" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A613" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>544</v>
@@ -21235,7 +21299,7 @@
     </row>
     <row r="614" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A614" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>544</v>
@@ -21264,7 +21328,7 @@
     </row>
     <row r="615" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A615" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>544</v>
@@ -21293,7 +21357,7 @@
     </row>
     <row r="616" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A616" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>544</v>
@@ -21322,7 +21386,7 @@
     </row>
     <row r="617" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A617" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>544</v>
@@ -21351,7 +21415,7 @@
     </row>
     <row r="618" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A618" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>544</v>
@@ -21380,7 +21444,7 @@
     </row>
     <row r="619" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A619" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>544</v>
@@ -21409,7 +21473,7 @@
     </row>
     <row r="620" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A620" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>544</v>
@@ -21438,7 +21502,7 @@
     </row>
     <row r="621" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A621" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>544</v>
@@ -21467,7 +21531,7 @@
     </row>
     <row r="622" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A622" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>544</v>
@@ -21496,7 +21560,7 @@
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A623" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>544</v>
@@ -21525,7 +21589,7 @@
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A624" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>544</v>
@@ -21554,7 +21618,7 @@
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A625" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>544</v>
@@ -21583,7 +21647,7 @@
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A626" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>544</v>
@@ -21612,7 +21676,7 @@
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A627" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>544</v>
@@ -21641,7 +21705,7 @@
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A628" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>544</v>
@@ -21670,7 +21734,7 @@
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A629" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>544</v>
@@ -21699,7 +21763,7 @@
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A630" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>544</v>
@@ -21728,7 +21792,7 @@
     </row>
     <row r="631" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A631" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>544</v>
@@ -21757,7 +21821,7 @@
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A632" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>544</v>
@@ -21786,7 +21850,7 @@
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A633" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>544</v>
@@ -21815,7 +21879,7 @@
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A634" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>544</v>
@@ -21844,7 +21908,7 @@
     </row>
     <row r="635" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A635" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>544</v>
@@ -21873,7 +21937,7 @@
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A636" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>544</v>
@@ -21902,7 +21966,7 @@
     </row>
     <row r="637" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A637" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>544</v>
@@ -21931,7 +21995,7 @@
     </row>
     <row r="638" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A638" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>544</v>
@@ -21960,7 +22024,7 @@
     </row>
     <row r="639" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A639" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>544</v>
@@ -21989,7 +22053,7 @@
     </row>
     <row r="640" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A640" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>544</v>
@@ -22018,7 +22082,7 @@
     </row>
     <row r="641" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A641" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>544</v>
@@ -22047,7 +22111,7 @@
     </row>
     <row r="642" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A642" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>544</v>
@@ -22076,7 +22140,7 @@
     </row>
     <row r="643" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A643" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>544</v>
@@ -22105,7 +22169,7 @@
     </row>
     <row r="644" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A644" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>544</v>
@@ -22134,7 +22198,7 @@
     </row>
     <row r="645" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A645" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>544</v>
@@ -22162,13 +22226,15 @@
       </c>
     </row>
     <row r="646" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A646" s="2"/>
+      <c r="A646" s="2" t="s">
+        <v>592</v>
+      </c>
       <c r="B646" s="2" t="s">
         <v>544</v>
       </c>
       <c r="C646" s="2"/>
       <c r="D646" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E646" s="3" t="b">
         <v>0</v>
@@ -22179,29 +22245,23 @@
       <c r="G646" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H646" s="7" t="s">
-        <v>970</v>
-      </c>
+      <c r="H646" s="7"/>
       <c r="I646" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J646" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J646" s="9"/>
       <c r="K646" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="647" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A647" s="2" t="s">
-        <v>593</v>
-      </c>
+      <c r="A647" s="2"/>
       <c r="B647" s="2" t="s">
         <v>544</v>
       </c>
       <c r="C647" s="2"/>
       <c r="D647" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E647" s="3" t="b">
         <v>0</v>
@@ -22212,18 +22272,22 @@
       <c r="G647" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H647" s="7"/>
+      <c r="H647" s="7" t="s">
+        <v>970</v>
+      </c>
       <c r="I647" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J647" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J647" s="10">
+        <v>46099</v>
+      </c>
       <c r="K647" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="648" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A648" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>544</v>
@@ -22252,7 +22316,7 @@
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A649" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>544</v>
@@ -22281,7 +22345,7 @@
     </row>
     <row r="650" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A650" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>544</v>
@@ -22310,7 +22374,7 @@
     </row>
     <row r="651" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A651" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>544</v>
@@ -22339,10 +22403,10 @@
     </row>
     <row r="652" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A652" s="2" t="s">
-        <v>876</v>
+        <v>597</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>598</v>
+        <v>544</v>
       </c>
       <c r="C652" s="2"/>
       <c r="D652" s="3" t="b">
@@ -22368,14 +22432,14 @@
     </row>
     <row r="653" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A653" s="2" t="s">
-        <v>599</v>
+        <v>876</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C653" s="2"/>
       <c r="D653" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E653" s="3" t="b">
         <v>0</v>
@@ -22386,9 +22450,7 @@
       <c r="G653" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H653" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H653" s="7"/>
       <c r="I653" s="3" t="b">
         <v>0</v>
       </c>
@@ -22399,14 +22461,14 @@
     </row>
     <row r="654" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A654" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C654" s="2"/>
       <c r="D654" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E654" s="3" t="b">
         <v>0</v>
@@ -22417,7 +22479,9 @@
       <c r="G654" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H654" s="7"/>
+      <c r="H654" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I654" s="3" t="b">
         <v>0</v>
       </c>
@@ -22428,7 +22492,7 @@
     </row>
     <row r="655" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A655" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>598</v>
@@ -22457,7 +22521,7 @@
     </row>
     <row r="656" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A656" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>598</v>
@@ -22486,7 +22550,7 @@
     </row>
     <row r="657" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A657" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>598</v>
@@ -22515,7 +22579,7 @@
     </row>
     <row r="658" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A658" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>598</v>
@@ -22544,7 +22608,7 @@
     </row>
     <row r="659" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A659" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>598</v>
@@ -22573,7 +22637,7 @@
     </row>
     <row r="660" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A660" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>598</v>
@@ -22602,7 +22666,7 @@
     </row>
     <row r="661" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A661" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>598</v>
@@ -22631,7 +22695,7 @@
     </row>
     <row r="662" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A662" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>598</v>
@@ -22660,7 +22724,7 @@
     </row>
     <row r="663" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A663" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>598</v>
@@ -22689,7 +22753,7 @@
     </row>
     <row r="664" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A664" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>598</v>
@@ -22718,7 +22782,7 @@
     </row>
     <row r="665" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A665" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>598</v>
@@ -22747,14 +22811,14 @@
     </row>
     <row r="666" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A666" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C666" s="2"/>
       <c r="D666" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E666" s="3" t="b">
         <v>0</v>
@@ -22765,9 +22829,7 @@
       <c r="G666" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H666" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H666" s="7"/>
       <c r="I666" s="3" t="b">
         <v>0</v>
       </c>
@@ -22778,14 +22840,14 @@
     </row>
     <row r="667" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A667" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C667" s="2"/>
       <c r="D667" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E667" s="3" t="b">
         <v>0</v>
@@ -22796,7 +22858,9 @@
       <c r="G667" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H667" s="7"/>
+      <c r="H667" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I667" s="3" t="b">
         <v>0</v>
       </c>
@@ -22807,7 +22871,7 @@
     </row>
     <row r="668" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A668" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>598</v>
@@ -22836,7 +22900,7 @@
     </row>
     <row r="669" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A669" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>598</v>
@@ -22865,7 +22929,7 @@
     </row>
     <row r="670" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A670" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>598</v>
@@ -22894,7 +22958,7 @@
     </row>
     <row r="671" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A671" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>598</v>
@@ -22923,7 +22987,7 @@
     </row>
     <row r="672" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A672" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>598</v>
@@ -22952,7 +23016,7 @@
     </row>
     <row r="673" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A673" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>598</v>
@@ -22981,7 +23045,7 @@
     </row>
     <row r="674" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A674" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>598</v>
@@ -23010,7 +23074,7 @@
     </row>
     <row r="675" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A675" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>598</v>
@@ -23039,7 +23103,7 @@
     </row>
     <row r="676" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A676" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>598</v>
@@ -23068,7 +23132,7 @@
     </row>
     <row r="677" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A677" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>598</v>
@@ -23097,7 +23161,7 @@
     </row>
     <row r="678" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A678" s="2" t="s">
-        <v>26</v>
+        <v>623</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>598</v>
@@ -23126,7 +23190,7 @@
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A679" s="2" t="s">
-        <v>624</v>
+        <v>26</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>598</v>
@@ -23155,7 +23219,7 @@
     </row>
     <row r="680" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A680" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>598</v>
@@ -23184,7 +23248,7 @@
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A681" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>598</v>
@@ -23213,7 +23277,7 @@
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A682" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>598</v>
@@ -23242,7 +23306,7 @@
     </row>
     <row r="683" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A683" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>598</v>
@@ -23271,7 +23335,7 @@
     </row>
     <row r="684" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A684" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>598</v>
@@ -23300,7 +23364,7 @@
     </row>
     <row r="685" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A685" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>598</v>
@@ -23329,14 +23393,14 @@
     </row>
     <row r="686" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A686" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C686" s="2"/>
       <c r="D686" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E686" s="3" t="b">
         <v>0</v>
@@ -23347,27 +23411,25 @@
       <c r="G686" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H686" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H686" s="7"/>
       <c r="I686" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J686" s="9"/>
       <c r="K686" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="687" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A687" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C687" s="2"/>
       <c r="D687" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E687" s="3" t="b">
         <v>0</v>
@@ -23378,18 +23440,20 @@
       <c r="G687" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H687" s="7"/>
+      <c r="H687" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I687" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J687" s="9"/>
       <c r="K687" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="688" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A688" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>598</v>
@@ -23418,7 +23482,7 @@
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A689" s="2" t="s">
-        <v>346</v>
+        <v>633</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>598</v>
@@ -23447,7 +23511,7 @@
     </row>
     <row r="690" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A690" s="2" t="s">
-        <v>634</v>
+        <v>346</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>598</v>
@@ -23476,7 +23540,7 @@
     </row>
     <row r="691" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A691" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>598</v>
@@ -23505,7 +23569,7 @@
     </row>
     <row r="692" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A692" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>598</v>
@@ -23534,7 +23598,7 @@
     </row>
     <row r="693" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A693" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>598</v>
@@ -23563,7 +23627,7 @@
     </row>
     <row r="694" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A694" s="2" t="s">
-        <v>37</v>
+        <v>637</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>598</v>
@@ -23592,7 +23656,7 @@
     </row>
     <row r="695" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A695" s="2" t="s">
-        <v>638</v>
+        <v>37</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>598</v>
@@ -23621,14 +23685,14 @@
     </row>
     <row r="696" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A696" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C696" s="2"/>
       <c r="D696" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E696" s="3" t="b">
         <v>0</v>
@@ -23639,27 +23703,25 @@
       <c r="G696" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H696" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H696" s="7"/>
       <c r="I696" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J696" s="9"/>
       <c r="K696" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="697" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A697" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C697" s="2"/>
       <c r="D697" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E697" s="3" t="b">
         <v>0</v>
@@ -23670,18 +23732,20 @@
       <c r="G697" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H697" s="7"/>
+      <c r="H697" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I697" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J697" s="9"/>
       <c r="K697" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="698" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A698" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>598</v>
@@ -23710,7 +23774,7 @@
     </row>
     <row r="699" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A699" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>598</v>
@@ -23739,7 +23803,7 @@
     </row>
     <row r="700" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A700" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>598</v>
@@ -23768,7 +23832,7 @@
     </row>
     <row r="701" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A701" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B701" s="2" t="s">
         <v>598</v>
@@ -23797,14 +23861,14 @@
     </row>
     <row r="702" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A702" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B702" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C702" s="2"/>
       <c r="D702" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E702" s="3" t="b">
         <v>0</v>
@@ -23815,23 +23879,21 @@
       <c r="G702" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H702" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H702" s="7"/>
       <c r="I702" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J702" s="9"/>
       <c r="K702" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="703" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A703" s="2" t="s">
-        <v>964</v>
+        <v>645</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>966</v>
+        <v>598</v>
       </c>
       <c r="C703" s="2"/>
       <c r="D703" s="3" t="b">
@@ -23847,28 +23909,26 @@
         <v>0</v>
       </c>
       <c r="H703" s="7" t="s">
-        <v>967</v>
+        <v>931</v>
       </c>
       <c r="I703" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J703" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J703" s="9"/>
       <c r="K703" s="2" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A704" s="2" t="s">
-        <v>646</v>
+        <v>964</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>647</v>
+        <v>966</v>
       </c>
       <c r="C704" s="2"/>
       <c r="D704" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E704" s="3" t="b">
         <v>0</v>
@@ -23879,18 +23939,22 @@
       <c r="G704" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H704" s="7"/>
+      <c r="H704" s="7" t="s">
+        <v>967</v>
+      </c>
       <c r="I704" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J704" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J704" s="10">
+        <v>46099</v>
+      </c>
       <c r="K704" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="705" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A705" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B705" s="2" t="s">
         <v>647</v>
@@ -23919,7 +23983,7 @@
     </row>
     <row r="706" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A706" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B706" s="2" t="s">
         <v>647</v>
@@ -23948,17 +24012,17 @@
     </row>
     <row r="707" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A707" s="2" t="s">
-        <v>874</v>
+        <v>649</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>647</v>
       </c>
       <c r="C707" s="2"/>
       <c r="D707" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E707" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F707" s="3" t="b">
         <v>0</v>
@@ -23966,30 +24030,28 @@
       <c r="G707" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H707" s="7" t="s">
-        <v>937</v>
-      </c>
+      <c r="H707" s="7"/>
       <c r="I707" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J707" s="9"/>
       <c r="K707" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A708" s="2" t="s">
-        <v>45</v>
+        <v>874</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>647</v>
       </c>
       <c r="C708" s="2"/>
       <c r="D708" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E708" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F708" s="3" t="b">
         <v>0</v>
@@ -23997,18 +24059,20 @@
       <c r="G708" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H708" s="7"/>
+      <c r="H708" s="7" t="s">
+        <v>937</v>
+      </c>
       <c r="I708" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J708" s="9"/>
       <c r="K708" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="709" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A709" s="2" t="s">
-        <v>650</v>
+        <v>45</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>647</v>
@@ -24037,7 +24101,7 @@
     </row>
     <row r="710" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A710" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B710" s="2" t="s">
         <v>647</v>
@@ -24066,7 +24130,7 @@
     </row>
     <row r="711" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A711" s="2" t="s">
-        <v>909</v>
+        <v>651</v>
       </c>
       <c r="B711" s="2" t="s">
         <v>647</v>
@@ -24079,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="F711" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G711" s="3" t="b">
         <v>0</v>
@@ -24090,12 +24154,12 @@
       </c>
       <c r="J711" s="9"/>
       <c r="K711" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="712" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A712" s="2" t="s">
-        <v>652</v>
+        <v>909</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>647</v>
@@ -24108,7 +24172,7 @@
         <v>0</v>
       </c>
       <c r="F712" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G712" s="3" t="b">
         <v>0</v>
@@ -24119,12 +24183,12 @@
       </c>
       <c r="J712" s="9"/>
       <c r="K712" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="713" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A713" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B713" s="2" t="s">
         <v>647</v>
@@ -24153,7 +24217,7 @@
     </row>
     <row r="714" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A714" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B714" s="2" t="s">
         <v>647</v>
@@ -24182,7 +24246,7 @@
     </row>
     <row r="715" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A715" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B715" s="2" t="s">
         <v>647</v>
@@ -24211,7 +24275,7 @@
     </row>
     <row r="716" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A716" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B716" s="2" t="s">
         <v>647</v>
@@ -24240,7 +24304,7 @@
     </row>
     <row r="717" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A717" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B717" s="2" t="s">
         <v>647</v>
@@ -24269,7 +24333,7 @@
     </row>
     <row r="718" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A718" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B718" s="2" t="s">
         <v>647</v>
@@ -24298,7 +24362,7 @@
     </row>
     <row r="719" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A719" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B719" s="2" t="s">
         <v>647</v>
@@ -24327,7 +24391,7 @@
     </row>
     <row r="720" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A720" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B720" s="2" t="s">
         <v>647</v>
@@ -24356,7 +24420,7 @@
     </row>
     <row r="721" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A721" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B721" s="2" t="s">
         <v>647</v>
@@ -24385,7 +24449,7 @@
     </row>
     <row r="722" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A722" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B722" s="2" t="s">
         <v>647</v>
@@ -24414,7 +24478,7 @@
     </row>
     <row r="723" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A723" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>647</v>
@@ -24443,7 +24507,7 @@
     </row>
     <row r="724" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A724" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B724" s="2" t="s">
         <v>647</v>
@@ -24472,7 +24536,7 @@
     </row>
     <row r="725" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A725" s="2" t="s">
-        <v>328</v>
+        <v>664</v>
       </c>
       <c r="B725" s="2" t="s">
         <v>647</v>
@@ -24501,7 +24565,7 @@
     </row>
     <row r="726" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A726" s="2" t="s">
-        <v>665</v>
+        <v>328</v>
       </c>
       <c r="B726" s="2" t="s">
         <v>647</v>
@@ -24530,7 +24594,7 @@
     </row>
     <row r="727" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A727" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B727" s="2" t="s">
         <v>647</v>
@@ -24559,7 +24623,7 @@
     </row>
     <row r="728" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A728" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B728" s="2" t="s">
         <v>647</v>
@@ -24588,7 +24652,7 @@
     </row>
     <row r="729" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A729" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B729" s="2" t="s">
         <v>647</v>
@@ -24617,7 +24681,7 @@
     </row>
     <row r="730" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A730" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B730" s="2" t="s">
         <v>647</v>
@@ -24646,7 +24710,7 @@
     </row>
     <row r="731" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A731" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B731" s="2" t="s">
         <v>647</v>
@@ -24675,7 +24739,7 @@
     </row>
     <row r="732" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A732" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B732" s="2" t="s">
         <v>647</v>
@@ -24704,7 +24768,7 @@
     </row>
     <row r="733" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A733" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B733" s="2" t="s">
         <v>647</v>
@@ -24733,7 +24797,7 @@
     </row>
     <row r="734" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A734" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B734" s="2" t="s">
         <v>647</v>
@@ -24762,7 +24826,7 @@
     </row>
     <row r="735" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A735" s="2" t="s">
-        <v>938</v>
+        <v>673</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>647</v>
@@ -24775,25 +24839,23 @@
         <v>0</v>
       </c>
       <c r="F735" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G735" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H735" s="7" t="s">
-        <v>937</v>
-      </c>
+      <c r="H735" s="7"/>
       <c r="I735" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J735" s="9"/>
       <c r="K735" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="736" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A736" s="2" t="s">
-        <v>674</v>
+        <v>938</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>647</v>
@@ -24806,23 +24868,25 @@
         <v>0</v>
       </c>
       <c r="F736" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G736" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H736" s="7"/>
+      <c r="H736" s="7" t="s">
+        <v>937</v>
+      </c>
       <c r="I736" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J736" s="9"/>
       <c r="K736" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="737" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A737" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B737" s="2" t="s">
         <v>647</v>
@@ -24851,7 +24915,7 @@
     </row>
     <row r="738" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A738" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B738" s="2" t="s">
         <v>647</v>
@@ -24880,7 +24944,7 @@
     </row>
     <row r="739" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A739" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>647</v>
@@ -24909,7 +24973,7 @@
     </row>
     <row r="740" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A740" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>647</v>
@@ -24938,7 +25002,7 @@
     </row>
     <row r="741" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A741" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>647</v>
@@ -24967,7 +25031,7 @@
     </row>
     <row r="742" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A742" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>647</v>
@@ -24996,7 +25060,7 @@
     </row>
     <row r="743" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A743" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>647</v>
@@ -25025,7 +25089,7 @@
     </row>
     <row r="744" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A744" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B744" s="2" t="s">
         <v>647</v>
@@ -25054,7 +25118,7 @@
     </row>
     <row r="745" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A745" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B745" s="2" t="s">
         <v>647</v>
@@ -25083,7 +25147,7 @@
     </row>
     <row r="746" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A746" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B746" s="2" t="s">
         <v>647</v>
@@ -25112,7 +25176,7 @@
     </row>
     <row r="747" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A747" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B747" s="2" t="s">
         <v>647</v>
@@ -25141,7 +25205,7 @@
     </row>
     <row r="748" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A748" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B748" s="2" t="s">
         <v>647</v>
@@ -25170,7 +25234,7 @@
     </row>
     <row r="749" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A749" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B749" s="2" t="s">
         <v>647</v>
@@ -25199,7 +25263,7 @@
     </row>
     <row r="750" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A750" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B750" s="2" t="s">
         <v>647</v>
@@ -25228,7 +25292,7 @@
     </row>
     <row r="751" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A751" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B751" s="2" t="s">
         <v>647</v>
@@ -25257,7 +25321,7 @@
     </row>
     <row r="752" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A752" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B752" s="2" t="s">
         <v>647</v>
@@ -25286,7 +25350,7 @@
     </row>
     <row r="753" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A753" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B753" s="2" t="s">
         <v>647</v>
@@ -25315,7 +25379,7 @@
     </row>
     <row r="754" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A754" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B754" s="2" t="s">
         <v>647</v>
@@ -25344,7 +25408,7 @@
     </row>
     <row r="755" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A755" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B755" s="2" t="s">
         <v>647</v>
@@ -25373,7 +25437,7 @@
     </row>
     <row r="756" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A756" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B756" s="2" t="s">
         <v>647</v>
@@ -25402,10 +25466,10 @@
     </row>
     <row r="757" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A757" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>696</v>
+        <v>647</v>
       </c>
       <c r="C757" s="2"/>
       <c r="D757" s="3" t="b">
@@ -25431,7 +25495,7 @@
     </row>
     <row r="758" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A758" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B758" s="2" t="s">
         <v>696</v>
@@ -25460,7 +25524,7 @@
     </row>
     <row r="759" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A759" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B759" s="2" t="s">
         <v>696</v>
@@ -25489,7 +25553,7 @@
     </row>
     <row r="760" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A760" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B760" s="2" t="s">
         <v>696</v>
@@ -25518,7 +25582,7 @@
     </row>
     <row r="761" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A761" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B761" s="2" t="s">
         <v>696</v>
@@ -25547,7 +25611,7 @@
     </row>
     <row r="762" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A762" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B762" s="2" t="s">
         <v>696</v>
@@ -25576,7 +25640,7 @@
     </row>
     <row r="763" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A763" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B763" s="2" t="s">
         <v>696</v>
@@ -25605,7 +25669,7 @@
     </row>
     <row r="764" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A764" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B764" s="2" t="s">
         <v>696</v>
@@ -25618,7 +25682,7 @@
         <v>0</v>
       </c>
       <c r="F764" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G764" s="3" t="b">
         <v>0</v>
@@ -25629,12 +25693,12 @@
       </c>
       <c r="J764" s="9"/>
       <c r="K764" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="765" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A765" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B765" s="2" t="s">
         <v>696</v>
@@ -25647,7 +25711,7 @@
         <v>0</v>
       </c>
       <c r="F765" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G765" s="3" t="b">
         <v>0</v>
@@ -25658,12 +25722,12 @@
       </c>
       <c r="J765" s="9"/>
       <c r="K765" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="766" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A766" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B766" s="2" t="s">
         <v>696</v>
@@ -25692,7 +25756,7 @@
     </row>
     <row r="767" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A767" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B767" s="2" t="s">
         <v>696</v>
@@ -25721,7 +25785,7 @@
     </row>
     <row r="768" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A768" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B768" s="2" t="s">
         <v>696</v>
@@ -25750,7 +25814,7 @@
     </row>
     <row r="769" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A769" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B769" s="2" t="s">
         <v>696</v>
@@ -25779,7 +25843,7 @@
     </row>
     <row r="770" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A770" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B770" s="2" t="s">
         <v>696</v>
@@ -25808,7 +25872,7 @@
     </row>
     <row r="771" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A771" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B771" s="2" t="s">
         <v>696</v>
@@ -25837,7 +25901,7 @@
     </row>
     <row r="772" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A772" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B772" s="2" t="s">
         <v>696</v>
@@ -25866,7 +25930,7 @@
     </row>
     <row r="773" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A773" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>696</v>
@@ -25895,14 +25959,14 @@
     </row>
     <row r="774" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A774" s="2" t="s">
-        <v>952</v>
+        <v>712</v>
       </c>
       <c r="B774" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C774" s="2"/>
       <c r="D774" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E774" s="3" t="b">
         <v>0</v>
@@ -25913,29 +25977,25 @@
       <c r="G774" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H774" s="7" t="s">
-        <v>953</v>
-      </c>
+      <c r="H774" s="7"/>
       <c r="I774" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J774" s="10">
-        <v>46095</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J774" s="9"/>
       <c r="K774" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="775" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A775" s="2" t="s">
-        <v>713</v>
+        <v>952</v>
       </c>
       <c r="B775" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C775" s="2"/>
       <c r="D775" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E775" s="3" t="b">
         <v>0</v>
@@ -25946,18 +26006,22 @@
       <c r="G775" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H775" s="7"/>
+      <c r="H775" s="7" t="s">
+        <v>953</v>
+      </c>
       <c r="I775" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J775" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J775" s="10">
+        <v>46095</v>
+      </c>
       <c r="K775" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="776" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A776" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B776" s="2" t="s">
         <v>696</v>
@@ -25986,7 +26050,7 @@
     </row>
     <row r="777" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A777" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B777" s="2" t="s">
         <v>696</v>
@@ -26015,7 +26079,7 @@
     </row>
     <row r="778" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A778" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B778" s="2" t="s">
         <v>696</v>
@@ -26044,7 +26108,7 @@
     </row>
     <row r="779" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A779" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>696</v>
@@ -26073,7 +26137,7 @@
     </row>
     <row r="780" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A780" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B780" s="2" t="s">
         <v>696</v>
@@ -26102,7 +26166,7 @@
     </row>
     <row r="781" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A781" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>696</v>
@@ -26131,7 +26195,7 @@
     </row>
     <row r="782" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A782" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B782" s="2" t="s">
         <v>696</v>
@@ -26160,7 +26224,7 @@
     </row>
     <row r="783" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A783" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B783" s="2" t="s">
         <v>696</v>
@@ -26189,7 +26253,7 @@
     </row>
     <row r="784" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A784" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B784" s="2" t="s">
         <v>696</v>
@@ -26218,7 +26282,7 @@
     </row>
     <row r="785" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A785" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>696</v>
@@ -26247,7 +26311,7 @@
     </row>
     <row r="786" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A786" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>696</v>
@@ -26276,7 +26340,7 @@
     </row>
     <row r="787" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A787" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B787" s="2" t="s">
         <v>696</v>
@@ -26305,7 +26369,7 @@
     </row>
     <row r="788" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A788" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B788" s="2" t="s">
         <v>696</v>
@@ -26334,7 +26398,7 @@
     </row>
     <row r="789" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A789" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>696</v>
@@ -26363,7 +26427,7 @@
     </row>
     <row r="790" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A790" s="2" t="s">
-        <v>887</v>
+        <v>727</v>
       </c>
       <c r="B790" s="2" t="s">
         <v>696</v>
@@ -26376,7 +26440,7 @@
         <v>0</v>
       </c>
       <c r="F790" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G790" s="3" t="b">
         <v>0</v>
@@ -26387,12 +26451,12 @@
       </c>
       <c r="J790" s="9"/>
       <c r="K790" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="791" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A791" s="2" t="s">
-        <v>728</v>
+        <v>887</v>
       </c>
       <c r="B791" s="2" t="s">
         <v>696</v>
@@ -26405,7 +26469,7 @@
         <v>0</v>
       </c>
       <c r="F791" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G791" s="3" t="b">
         <v>0</v>
@@ -26416,12 +26480,12 @@
       </c>
       <c r="J791" s="9"/>
       <c r="K791" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="792" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A792" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B792" s="2" t="s">
         <v>696</v>
@@ -26450,7 +26514,7 @@
     </row>
     <row r="793" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A793" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B793" s="2" t="s">
         <v>696</v>
@@ -26479,7 +26543,7 @@
     </row>
     <row r="794" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A794" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B794" s="2" t="s">
         <v>696</v>
@@ -26508,7 +26572,7 @@
     </row>
     <row r="795" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A795" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B795" s="2" t="s">
         <v>696</v>
@@ -26537,7 +26601,7 @@
     </row>
     <row r="796" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A796" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B796" s="2" t="s">
         <v>696</v>
@@ -26566,7 +26630,7 @@
     </row>
     <row r="797" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A797" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B797" s="2" t="s">
         <v>696</v>
@@ -26595,7 +26659,7 @@
     </row>
     <row r="798" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A798" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B798" s="2" t="s">
         <v>696</v>
@@ -26624,7 +26688,7 @@
     </row>
     <row r="799" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A799" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B799" s="2" t="s">
         <v>696</v>
@@ -26653,7 +26717,7 @@
     </row>
     <row r="800" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A800" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B800" s="2" t="s">
         <v>696</v>
@@ -26682,7 +26746,7 @@
     </row>
     <row r="801" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A801" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B801" s="2" t="s">
         <v>696</v>
@@ -26711,14 +26775,14 @@
     </row>
     <row r="802" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A802" s="2" t="s">
-        <v>971</v>
+        <v>738</v>
       </c>
       <c r="B802" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C802" s="2"/>
       <c r="D802" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E802" s="3" t="b">
         <v>0</v>
@@ -26729,29 +26793,25 @@
       <c r="G802" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H802" s="7" t="s">
-        <v>972</v>
-      </c>
+      <c r="H802" s="7"/>
       <c r="I802" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J802" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J802" s="9"/>
       <c r="K802" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="803" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A803" s="2" t="s">
-        <v>739</v>
+        <v>971</v>
       </c>
       <c r="B803" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C803" s="2"/>
       <c r="D803" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E803" s="3" t="b">
         <v>0</v>
@@ -26762,18 +26822,22 @@
       <c r="G803" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H803" s="7"/>
+      <c r="H803" s="7" t="s">
+        <v>972</v>
+      </c>
       <c r="I803" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J803" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J803" s="10">
+        <v>46099</v>
+      </c>
       <c r="K803" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="804" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A804" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B804" s="2" t="s">
         <v>696</v>
@@ -26802,7 +26866,7 @@
     </row>
     <row r="805" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A805" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B805" s="2" t="s">
         <v>696</v>
@@ -26831,7 +26895,7 @@
     </row>
     <row r="806" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A806" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B806" s="2" t="s">
         <v>696</v>
@@ -26860,7 +26924,7 @@
     </row>
     <row r="807" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A807" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B807" s="2" t="s">
         <v>696</v>
@@ -26889,7 +26953,7 @@
     </row>
     <row r="808" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A808" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B808" s="2" t="s">
         <v>696</v>
@@ -26918,14 +26982,14 @@
     </row>
     <row r="809" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A809" s="2" t="s">
-        <v>961</v>
+        <v>744</v>
       </c>
       <c r="B809" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C809" s="2"/>
       <c r="D809" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E809" s="3" t="b">
         <v>0</v>
@@ -26936,29 +27000,25 @@
       <c r="G809" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H809" s="7" t="s">
-        <v>962</v>
-      </c>
+      <c r="H809" s="7"/>
       <c r="I809" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J809" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J809" s="9"/>
       <c r="K809" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="810" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A810" s="2" t="s">
-        <v>745</v>
+        <v>961</v>
       </c>
       <c r="B810" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C810" s="2"/>
       <c r="D810" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E810" s="3" t="b">
         <v>0</v>
@@ -26969,21 +27029,25 @@
       <c r="G810" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H810" s="7"/>
+      <c r="H810" s="7" t="s">
+        <v>962</v>
+      </c>
       <c r="I810" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J810" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J810" s="10">
+        <v>46099</v>
+      </c>
       <c r="K810" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="811" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A811" s="2" t="s">
-        <v>648</v>
+        <v>745</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>746</v>
+        <v>696</v>
       </c>
       <c r="C811" s="2"/>
       <c r="D811" s="3" t="b">
@@ -27009,7 +27073,7 @@
     </row>
     <row r="812" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A812" s="2" t="s">
-        <v>747</v>
+        <v>648</v>
       </c>
       <c r="B812" s="2" t="s">
         <v>746</v>
@@ -27038,7 +27102,7 @@
     </row>
     <row r="813" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A813" s="2" t="s">
-        <v>208</v>
+        <v>747</v>
       </c>
       <c r="B813" s="2" t="s">
         <v>746</v>
@@ -27067,7 +27131,7 @@
     </row>
     <row r="814" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A814" s="2" t="s">
-        <v>748</v>
+        <v>208</v>
       </c>
       <c r="B814" s="2" t="s">
         <v>746</v>
@@ -27096,7 +27160,7 @@
     </row>
     <row r="815" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A815" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B815" s="2" t="s">
         <v>746</v>
@@ -27125,7 +27189,7 @@
     </row>
     <row r="816" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A816" s="2" t="s">
-        <v>214</v>
+        <v>749</v>
       </c>
       <c r="B816" s="2" t="s">
         <v>746</v>
@@ -27154,7 +27218,7 @@
     </row>
     <row r="817" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A817" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B817" s="2" t="s">
         <v>746</v>
@@ -27183,7 +27247,7 @@
     </row>
     <row r="818" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A818" s="2" t="s">
-        <v>656</v>
+        <v>216</v>
       </c>
       <c r="B818" s="2" t="s">
         <v>746</v>
@@ -27212,7 +27276,7 @@
     </row>
     <row r="819" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A819" s="2" t="s">
-        <v>750</v>
+        <v>656</v>
       </c>
       <c r="B819" s="2" t="s">
         <v>746</v>
@@ -27241,7 +27305,7 @@
     </row>
     <row r="820" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A820" s="2" t="s">
-        <v>19</v>
+        <v>750</v>
       </c>
       <c r="B820" s="2" t="s">
         <v>746</v>
@@ -27270,7 +27334,7 @@
     </row>
     <row r="821" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A821" s="2" t="s">
-        <v>751</v>
+        <v>19</v>
       </c>
       <c r="B821" s="2" t="s">
         <v>746</v>
@@ -27299,7 +27363,7 @@
     </row>
     <row r="822" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A822" s="2" t="s">
-        <v>325</v>
+        <v>751</v>
       </c>
       <c r="B822" s="2" t="s">
         <v>746</v>
@@ -27328,7 +27392,7 @@
     </row>
     <row r="823" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A823" s="2" t="s">
-        <v>752</v>
+        <v>325</v>
       </c>
       <c r="B823" s="2" t="s">
         <v>746</v>
@@ -27357,7 +27421,7 @@
     </row>
     <row r="824" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A824" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B824" s="2" t="s">
         <v>746</v>
@@ -27386,7 +27450,7 @@
     </row>
     <row r="825" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A825" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B825" s="2" t="s">
         <v>746</v>
@@ -27415,7 +27479,7 @@
     </row>
     <row r="826" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A826" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B826" s="2" t="s">
         <v>746</v>
@@ -27444,7 +27508,7 @@
     </row>
     <row r="827" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A827" s="2" t="s">
-        <v>22</v>
+        <v>755</v>
       </c>
       <c r="B827" s="2" t="s">
         <v>746</v>
@@ -27473,7 +27537,7 @@
     </row>
     <row r="828" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A828" s="2" t="s">
-        <v>756</v>
+        <v>22</v>
       </c>
       <c r="B828" s="2" t="s">
         <v>746</v>
@@ -27502,7 +27566,7 @@
     </row>
     <row r="829" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A829" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B829" s="2" t="s">
         <v>746</v>
@@ -27531,7 +27595,7 @@
     </row>
     <row r="830" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A830" s="2" t="s">
-        <v>23</v>
+        <v>757</v>
       </c>
       <c r="B830" s="2" t="s">
         <v>746</v>
@@ -27560,7 +27624,7 @@
     </row>
     <row r="831" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A831" s="2" t="s">
-        <v>758</v>
+        <v>23</v>
       </c>
       <c r="B831" s="2" t="s">
         <v>746</v>
@@ -27589,7 +27653,7 @@
     </row>
     <row r="832" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A832" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B832" s="2" t="s">
         <v>746</v>
@@ -27618,7 +27682,7 @@
     </row>
     <row r="833" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A833" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B833" s="2" t="s">
         <v>746</v>
@@ -27647,7 +27711,7 @@
     </row>
     <row r="834" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A834" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B834" s="2" t="s">
         <v>746</v>
@@ -27676,7 +27740,7 @@
     </row>
     <row r="835" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A835" s="2" t="s">
-        <v>233</v>
+        <v>761</v>
       </c>
       <c r="B835" s="2" t="s">
         <v>746</v>
@@ -27705,7 +27769,7 @@
     </row>
     <row r="836" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A836" s="2" t="s">
-        <v>762</v>
+        <v>233</v>
       </c>
       <c r="B836" s="2" t="s">
         <v>746</v>
@@ -27734,7 +27798,7 @@
     </row>
     <row r="837" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A837" s="2" t="s">
-        <v>28</v>
+        <v>762</v>
       </c>
       <c r="B837" s="2" t="s">
         <v>746</v>
@@ -27763,7 +27827,7 @@
     </row>
     <row r="838" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A838" s="2" t="s">
-        <v>626</v>
+        <v>28</v>
       </c>
       <c r="B838" s="2" t="s">
         <v>746</v>
@@ -27792,7 +27856,7 @@
     </row>
     <row r="839" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A839" s="2" t="s">
-        <v>763</v>
+        <v>626</v>
       </c>
       <c r="B839" s="2" t="s">
         <v>746</v>
@@ -27821,7 +27885,7 @@
     </row>
     <row r="840" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A840" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B840" s="2" t="s">
         <v>746</v>
@@ -27850,7 +27914,7 @@
     </row>
     <row r="841" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A841" s="2" t="s">
-        <v>342</v>
+        <v>764</v>
       </c>
       <c r="B841" s="2" t="s">
         <v>746</v>
@@ -27879,7 +27943,7 @@
     </row>
     <row r="842" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A842" s="2" t="s">
-        <v>765</v>
+        <v>342</v>
       </c>
       <c r="B842" s="2" t="s">
         <v>746</v>
@@ -27908,7 +27972,7 @@
     </row>
     <row r="843" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A843" s="2" t="s">
-        <v>480</v>
+        <v>765</v>
       </c>
       <c r="B843" s="2" t="s">
         <v>746</v>
@@ -27937,7 +28001,7 @@
     </row>
     <row r="844" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A844" s="2" t="s">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="B844" s="2" t="s">
         <v>746</v>
@@ -27966,7 +28030,7 @@
     </row>
     <row r="845" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A845" s="2" t="s">
-        <v>766</v>
+        <v>30</v>
       </c>
       <c r="B845" s="2" t="s">
         <v>746</v>
@@ -27995,14 +28059,14 @@
     </row>
     <row r="846" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A846" s="2" t="s">
-        <v>32</v>
+        <v>766</v>
       </c>
       <c r="B846" s="2" t="s">
         <v>746</v>
       </c>
       <c r="C846" s="2"/>
       <c r="D846" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E846" s="3" t="b">
         <v>0</v>
@@ -28013,29 +28077,25 @@
       <c r="G846" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H846" s="7" t="s">
-        <v>951</v>
-      </c>
+      <c r="H846" s="7"/>
       <c r="I846" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J846" s="10">
-        <v>46095</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J846" s="9"/>
       <c r="K846" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="847" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A847" s="2" t="s">
-        <v>767</v>
+        <v>32</v>
       </c>
       <c r="B847" s="2" t="s">
         <v>746</v>
       </c>
       <c r="C847" s="2"/>
       <c r="D847" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E847" s="3" t="b">
         <v>0</v>
@@ -28046,18 +28106,22 @@
       <c r="G847" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H847" s="7"/>
+      <c r="H847" s="7" t="s">
+        <v>951</v>
+      </c>
       <c r="I847" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J847" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J847" s="10">
+        <v>46095</v>
+      </c>
       <c r="K847" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="848" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A848" s="2" t="s">
-        <v>34</v>
+        <v>767</v>
       </c>
       <c r="B848" s="2" t="s">
         <v>746</v>
@@ -28086,7 +28150,7 @@
     </row>
     <row r="849" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A849" s="2" t="s">
-        <v>768</v>
+        <v>34</v>
       </c>
       <c r="B849" s="2" t="s">
         <v>746</v>
@@ -28115,7 +28179,7 @@
     </row>
     <row r="850" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A850" s="2" t="s">
-        <v>35</v>
+        <v>768</v>
       </c>
       <c r="B850" s="2" t="s">
         <v>746</v>
@@ -28144,7 +28208,7 @@
     </row>
     <row r="851" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A851" s="2" t="s">
-        <v>769</v>
+        <v>35</v>
       </c>
       <c r="B851" s="2" t="s">
         <v>746</v>
@@ -28173,7 +28237,7 @@
     </row>
     <row r="852" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A852" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B852" s="2" t="s">
         <v>746</v>
@@ -28202,7 +28266,7 @@
     </row>
     <row r="853" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A853" s="2" t="s">
-        <v>37</v>
+        <v>770</v>
       </c>
       <c r="B853" s="2" t="s">
         <v>746</v>
@@ -28231,7 +28295,7 @@
     </row>
     <row r="854" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A854" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B854" s="2" t="s">
         <v>746</v>
@@ -28260,7 +28324,7 @@
     </row>
     <row r="855" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A855" s="2" t="s">
-        <v>639</v>
+        <v>38</v>
       </c>
       <c r="B855" s="2" t="s">
         <v>746</v>
@@ -28289,7 +28353,7 @@
     </row>
     <row r="856" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A856" s="2" t="s">
-        <v>771</v>
+        <v>639</v>
       </c>
       <c r="B856" s="2" t="s">
         <v>746</v>
@@ -28318,7 +28382,7 @@
     </row>
     <row r="857" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A857" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B857" s="2" t="s">
         <v>746</v>
@@ -28347,7 +28411,7 @@
     </row>
     <row r="858" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A858" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B858" s="2" t="s">
         <v>746</v>
@@ -28376,7 +28440,7 @@
     </row>
     <row r="859" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A859" s="2" t="s">
-        <v>876</v>
+        <v>773</v>
       </c>
       <c r="B859" s="2" t="s">
         <v>746</v>
@@ -28405,7 +28469,7 @@
     </row>
     <row r="860" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A860" s="2" t="s">
-        <v>42</v>
+        <v>876</v>
       </c>
       <c r="B860" s="2" t="s">
         <v>746</v>
@@ -28434,14 +28498,14 @@
     </row>
     <row r="861" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A861" s="2" t="s">
-        <v>973</v>
+        <v>42</v>
       </c>
       <c r="B861" s="2" t="s">
-        <v>975</v>
+        <v>746</v>
       </c>
       <c r="C861" s="2"/>
       <c r="D861" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E861" s="3" t="b">
         <v>0</v>
@@ -28452,29 +28516,25 @@
       <c r="G861" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H861" s="7" t="s">
-        <v>976</v>
-      </c>
+      <c r="H861" s="7"/>
       <c r="I861" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J861" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J861" s="9"/>
       <c r="K861" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="862" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A862" s="2" t="s">
-        <v>774</v>
+        <v>973</v>
       </c>
       <c r="B862" s="2" t="s">
-        <v>775</v>
+        <v>975</v>
       </c>
       <c r="C862" s="2"/>
       <c r="D862" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E862" s="3" t="b">
         <v>0</v>
@@ -28485,18 +28545,22 @@
       <c r="G862" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H862" s="7"/>
+      <c r="H862" s="7" t="s">
+        <v>976</v>
+      </c>
       <c r="I862" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J862" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J862" s="10">
+        <v>46099</v>
+      </c>
       <c r="K862" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="863" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A863" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B863" s="2" t="s">
         <v>775</v>
@@ -28525,7 +28589,7 @@
     </row>
     <row r="864" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A864" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B864" s="2" t="s">
         <v>775</v>
@@ -28554,7 +28618,7 @@
     </row>
     <row r="865" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A865" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B865" s="2" t="s">
         <v>775</v>
@@ -28583,7 +28647,7 @@
     </row>
     <row r="866" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A866" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B866" s="2" t="s">
         <v>775</v>
@@ -28612,7 +28676,7 @@
     </row>
     <row r="867" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A867" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B867" s="2" t="s">
         <v>775</v>
@@ -28641,14 +28705,14 @@
     </row>
     <row r="868" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A868" s="2" t="s">
-        <v>973</v>
+        <v>780</v>
       </c>
       <c r="B868" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C868" s="2"/>
       <c r="D868" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E868" s="3" t="b">
         <v>0</v>
@@ -28659,29 +28723,25 @@
       <c r="G868" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H868" s="7" t="s">
-        <v>974</v>
-      </c>
+      <c r="H868" s="7"/>
       <c r="I868" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J868" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J868" s="9"/>
       <c r="K868" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="869" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A869" s="2" t="s">
-        <v>781</v>
+        <v>973</v>
       </c>
       <c r="B869" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C869" s="2"/>
       <c r="D869" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E869" s="3" t="b">
         <v>0</v>
@@ -28692,18 +28752,22 @@
       <c r="G869" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H869" s="7"/>
+      <c r="H869" s="7" t="s">
+        <v>974</v>
+      </c>
       <c r="I869" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J869" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J869" s="10">
+        <v>46099</v>
+      </c>
       <c r="K869" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="870" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A870" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B870" s="2" t="s">
         <v>775</v>
@@ -28732,7 +28796,7 @@
     </row>
     <row r="871" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A871" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B871" s="2" t="s">
         <v>775</v>
@@ -28761,7 +28825,7 @@
     </row>
     <row r="872" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A872" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B872" s="2" t="s">
         <v>775</v>
@@ -28790,14 +28854,14 @@
     </row>
     <row r="873" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A873" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B873" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C873" s="2"/>
       <c r="D873" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E873" s="3" t="b">
         <v>0</v>
@@ -28808,29 +28872,25 @@
       <c r="G873" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H873" s="7" t="s">
-        <v>969</v>
-      </c>
+      <c r="H873" s="7"/>
       <c r="I873" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J873" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J873" s="9"/>
       <c r="K873" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="874" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A874" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B874" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C874" s="2"/>
       <c r="D874" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E874" s="3" t="b">
         <v>0</v>
@@ -28841,18 +28901,22 @@
       <c r="G874" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H874" s="7"/>
+      <c r="H874" s="7" t="s">
+        <v>969</v>
+      </c>
       <c r="I874" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J874" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J874" s="10">
+        <v>46099</v>
+      </c>
       <c r="K874" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="875" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A875" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B875" s="2" t="s">
         <v>775</v>
@@ -28881,7 +28945,7 @@
     </row>
     <row r="876" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A876" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B876" s="2" t="s">
         <v>775</v>
@@ -28910,7 +28974,7 @@
     </row>
     <row r="877" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A877" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B877" s="2" t="s">
         <v>775</v>
@@ -28939,7 +29003,7 @@
     </row>
     <row r="878" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A878" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B878" s="2" t="s">
         <v>775</v>
@@ -28968,7 +29032,7 @@
     </row>
     <row r="879" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A879" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B879" s="2" t="s">
         <v>775</v>
@@ -28997,14 +29061,14 @@
     </row>
     <row r="880" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A880" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B880" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C880" s="2"/>
       <c r="D880" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E880" s="3" t="b">
         <v>0</v>
@@ -29015,29 +29079,25 @@
       <c r="G880" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H880" s="7" t="s">
-        <v>968</v>
-      </c>
+      <c r="H880" s="7"/>
       <c r="I880" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J880" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J880" s="9"/>
       <c r="K880" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="881" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A881" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B881" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C881" s="2"/>
       <c r="D881" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E881" s="3" t="b">
         <v>0</v>
@@ -29048,18 +29108,22 @@
       <c r="G881" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H881" s="7"/>
+      <c r="H881" s="7" t="s">
+        <v>968</v>
+      </c>
       <c r="I881" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J881" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J881" s="10">
+        <v>46099</v>
+      </c>
       <c r="K881" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="882" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A882" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B882" s="2" t="s">
         <v>775</v>
@@ -29088,7 +29152,7 @@
     </row>
     <row r="883" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A883" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B883" s="2" t="s">
         <v>775</v>
@@ -29117,7 +29181,7 @@
     </row>
     <row r="884" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A884" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B884" s="2" t="s">
         <v>775</v>
@@ -29146,7 +29210,7 @@
     </row>
     <row r="885" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A885" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B885" s="2" t="s">
         <v>775</v>
@@ -29175,7 +29239,7 @@
     </row>
     <row r="886" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A886" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B886" s="2" t="s">
         <v>775</v>
@@ -29204,7 +29268,7 @@
     </row>
     <row r="887" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A887" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B887" s="2" t="s">
         <v>775</v>
@@ -29233,7 +29297,7 @@
     </row>
     <row r="888" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A888" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B888" s="2" t="s">
         <v>775</v>
@@ -29262,7 +29326,7 @@
     </row>
     <row r="889" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A889" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>775</v>
@@ -29291,7 +29355,7 @@
     </row>
     <row r="890" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A890" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B890" s="2" t="s">
         <v>775</v>
@@ -29320,7 +29384,7 @@
     </row>
     <row r="891" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A891" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B891" s="2" t="s">
         <v>775</v>
@@ -29349,7 +29413,7 @@
     </row>
     <row r="892" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A892" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B892" s="2" t="s">
         <v>775</v>
@@ -29378,7 +29442,7 @@
     </row>
     <row r="893" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A893" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B893" s="2" t="s">
         <v>775</v>
@@ -29407,7 +29471,7 @@
     </row>
     <row r="894" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A894" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B894" s="2" t="s">
         <v>775</v>
@@ -29436,7 +29500,7 @@
     </row>
     <row r="895" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A895" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B895" s="2" t="s">
         <v>775</v>
@@ -29465,7 +29529,7 @@
     </row>
     <row r="896" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A896" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B896" s="2" t="s">
         <v>775</v>
@@ -29494,7 +29558,7 @@
     </row>
     <row r="897" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A897" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B897" s="2" t="s">
         <v>775</v>
@@ -29523,7 +29587,7 @@
     </row>
     <row r="898" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A898" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B898" s="2" t="s">
         <v>775</v>
@@ -29552,7 +29616,7 @@
     </row>
     <row r="899" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A899" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B899" s="2" t="s">
         <v>775</v>
@@ -29581,7 +29645,7 @@
     </row>
     <row r="900" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A900" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B900" s="2" t="s">
         <v>775</v>
@@ -29610,7 +29674,7 @@
     </row>
     <row r="901" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A901" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B901" s="2" t="s">
         <v>775</v>
@@ -29639,7 +29703,7 @@
     </row>
     <row r="902" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A902" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B902" s="2" t="s">
         <v>775</v>
@@ -29668,7 +29732,7 @@
     </row>
     <row r="903" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A903" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B903" s="2" t="s">
         <v>775</v>
@@ -29697,7 +29761,7 @@
     </row>
     <row r="904" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A904" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B904" s="2" t="s">
         <v>775</v>
@@ -29726,7 +29790,7 @@
     </row>
     <row r="905" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A905" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B905" s="2" t="s">
         <v>775</v>
@@ -29755,7 +29819,7 @@
     </row>
     <row r="906" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A906" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B906" s="2" t="s">
         <v>775</v>
@@ -29784,7 +29848,7 @@
     </row>
     <row r="907" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A907" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B907" s="2" t="s">
         <v>775</v>
@@ -29813,7 +29877,7 @@
     </row>
     <row r="908" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A908" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B908" s="2" t="s">
         <v>775</v>
@@ -29842,10 +29906,10 @@
     </row>
     <row r="909" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A909" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B909" s="2" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
       <c r="C909" s="2"/>
       <c r="D909" s="3" t="b">
@@ -29871,7 +29935,7 @@
     </row>
     <row r="910" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A910" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B910" s="2" t="s">
         <v>822</v>
@@ -29900,7 +29964,7 @@
     </row>
     <row r="911" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A911" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B911" s="2" t="s">
         <v>822</v>
@@ -29929,7 +29993,7 @@
     </row>
     <row r="912" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A912" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B912" s="2" t="s">
         <v>822</v>
@@ -29958,7 +30022,7 @@
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A913" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>822</v>
@@ -29987,7 +30051,7 @@
     </row>
     <row r="914" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A914" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B914" s="2" t="s">
         <v>822</v>
@@ -30016,7 +30080,7 @@
     </row>
     <row r="915" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A915" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B915" s="2" t="s">
         <v>822</v>
@@ -30045,7 +30109,7 @@
     </row>
     <row r="916" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A916" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B916" s="2" t="s">
         <v>822</v>
@@ -30074,7 +30138,7 @@
     </row>
     <row r="917" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A917" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B917" s="2" t="s">
         <v>822</v>
@@ -30103,7 +30167,7 @@
     </row>
     <row r="918" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A918" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B918" s="2" t="s">
         <v>822</v>
@@ -30132,7 +30196,7 @@
     </row>
     <row r="919" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A919" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B919" s="2" t="s">
         <v>822</v>
@@ -30161,7 +30225,7 @@
     </row>
     <row r="920" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A920" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B920" s="2" t="s">
         <v>822</v>
@@ -30190,7 +30254,7 @@
     </row>
     <row r="921" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A921" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B921" s="2" t="s">
         <v>822</v>
@@ -30219,7 +30283,7 @@
     </row>
     <row r="922" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A922" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B922" s="2" t="s">
         <v>822</v>
@@ -30248,7 +30312,7 @@
     </row>
     <row r="923" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A923" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B923" s="2" t="s">
         <v>822</v>
@@ -30277,7 +30341,7 @@
     </row>
     <row r="924" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A924" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B924" s="2" t="s">
         <v>822</v>
@@ -30306,7 +30370,7 @@
     </row>
     <row r="925" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A925" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B925" s="2" t="s">
         <v>822</v>
@@ -30335,7 +30399,7 @@
     </row>
     <row r="926" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A926" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B926" s="2" t="s">
         <v>822</v>
@@ -30364,7 +30428,7 @@
     </row>
     <row r="927" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A927" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B927" s="2" t="s">
         <v>822</v>
@@ -30393,7 +30457,7 @@
     </row>
     <row r="928" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A928" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B928" s="2" t="s">
         <v>822</v>
@@ -30422,7 +30486,7 @@
     </row>
     <row r="929" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A929" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B929" s="2" t="s">
         <v>822</v>
@@ -30451,7 +30515,7 @@
     </row>
     <row r="930" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A930" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B930" s="2" t="s">
         <v>822</v>
@@ -30480,7 +30544,7 @@
     </row>
     <row r="931" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A931" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B931" s="2" t="s">
         <v>822</v>
@@ -30509,7 +30573,7 @@
     </row>
     <row r="932" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A932" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B932" s="2" t="s">
         <v>822</v>
@@ -30538,7 +30602,7 @@
     </row>
     <row r="933" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A933" s="2" t="s">
-        <v>945</v>
+        <v>845</v>
       </c>
       <c r="B933" s="2" t="s">
         <v>822</v>
@@ -30556,9 +30620,7 @@
       <c r="G933" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H933" s="7" t="s">
-        <v>946</v>
-      </c>
+      <c r="H933" s="7"/>
       <c r="I933" s="3" t="b">
         <v>0</v>
       </c>
@@ -30569,7 +30631,7 @@
     </row>
     <row r="934" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A934" s="2" t="s">
-        <v>846</v>
+        <v>945</v>
       </c>
       <c r="B934" s="2" t="s">
         <v>822</v>
@@ -30587,7 +30649,9 @@
       <c r="G934" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H934" s="7"/>
+      <c r="H934" s="7" t="s">
+        <v>946</v>
+      </c>
       <c r="I934" s="3" t="b">
         <v>0</v>
       </c>
@@ -30598,7 +30662,7 @@
     </row>
     <row r="935" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A935" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B935" s="2" t="s">
         <v>822</v>
@@ -30627,7 +30691,7 @@
     </row>
     <row r="936" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A936" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B936" s="2" t="s">
         <v>822</v>
@@ -30656,7 +30720,7 @@
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A937" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B937" s="2" t="s">
         <v>822</v>
@@ -30685,7 +30749,7 @@
     </row>
     <row r="938" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A938" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B938" s="2" t="s">
         <v>822</v>
@@ -30714,7 +30778,7 @@
     </row>
     <row r="939" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A939" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B939" s="2" t="s">
         <v>822</v>
@@ -30743,14 +30807,14 @@
     </row>
     <row r="940" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A940" s="2" t="s">
-        <v>956</v>
+        <v>851</v>
       </c>
       <c r="B940" s="2" t="s">
         <v>822</v>
       </c>
       <c r="C940" s="2"/>
       <c r="D940" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E940" s="3" t="b">
         <v>0</v>
@@ -30761,27 +30825,25 @@
       <c r="G940" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H940" s="7" t="s">
-        <v>957</v>
-      </c>
+      <c r="H940" s="7"/>
       <c r="I940" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J940" s="9"/>
       <c r="K940" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="941" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A941" s="2" t="s">
-        <v>852</v>
+        <v>956</v>
       </c>
       <c r="B941" s="2" t="s">
         <v>822</v>
       </c>
       <c r="C941" s="2"/>
       <c r="D941" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E941" s="3" t="b">
         <v>0</v>
@@ -30792,18 +30854,20 @@
       <c r="G941" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H941" s="7"/>
+      <c r="H941" s="7" t="s">
+        <v>957</v>
+      </c>
       <c r="I941" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J941" s="9"/>
       <c r="K941" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="942" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A942" s="2" t="s">
-        <v>735</v>
+        <v>852</v>
       </c>
       <c r="B942" s="2" t="s">
         <v>822</v>
@@ -30832,7 +30896,7 @@
     </row>
     <row r="943" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A943" s="2" t="s">
-        <v>853</v>
+        <v>735</v>
       </c>
       <c r="B943" s="2" t="s">
         <v>822</v>
@@ -30861,7 +30925,7 @@
     </row>
     <row r="944" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A944" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B944" s="2" t="s">
         <v>822</v>
@@ -30890,7 +30954,7 @@
     </row>
     <row r="945" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A945" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B945" s="2" t="s">
         <v>822</v>
@@ -30919,7 +30983,7 @@
     </row>
     <row r="946" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A946" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B946" s="2" t="s">
         <v>822</v>
@@ -30948,7 +31012,7 @@
     </row>
     <row r="947" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A947" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B947" s="2" t="s">
         <v>822</v>
@@ -30977,7 +31041,7 @@
     </row>
     <row r="948" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A948" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B948" s="2" t="s">
         <v>822</v>
@@ -31006,7 +31070,7 @@
     </row>
     <row r="949" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A949" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B949" s="2" t="s">
         <v>822</v>
@@ -31035,7 +31099,7 @@
     </row>
     <row r="950" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A950" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B950" s="2" t="s">
         <v>822</v>
@@ -31064,7 +31128,7 @@
     </row>
     <row r="951" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A951" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B951" s="2" t="s">
         <v>822</v>
@@ -31093,7 +31157,7 @@
     </row>
     <row r="952" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A952" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B952" s="2" t="s">
         <v>822</v>
@@ -31122,7 +31186,7 @@
     </row>
     <row r="953" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A953" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B953" s="2" t="s">
         <v>822</v>
@@ -31151,7 +31215,7 @@
     </row>
     <row r="954" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A954" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B954" s="2" t="s">
         <v>822</v>
@@ -31180,7 +31244,7 @@
     </row>
     <row r="955" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A955" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B955" s="2" t="s">
         <v>822</v>
@@ -31209,7 +31273,7 @@
     </row>
     <row r="956" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A956" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B956" s="2" t="s">
         <v>822</v>
@@ -31238,7 +31302,7 @@
     </row>
     <row r="957" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A957" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B957" s="2" t="s">
         <v>822</v>
@@ -31267,7 +31331,7 @@
     </row>
     <row r="958" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A958" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B958" s="2" t="s">
         <v>822</v>
@@ -31291,6 +31355,35 @@
       </c>
       <c r="J958" s="9"/>
       <c r="K958" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="959" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A959" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B959" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C959" s="2"/>
+      <c r="D959" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E959" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F959" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G959" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H959" s="7"/>
+      <c r="I959" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J959" s="9"/>
+      <c r="K959" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -31334,27 +31427,27 @@
         <v>95</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A2)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A2)</f>
         <v>64</v>
       </c>
       <c r="C2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A2,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>3</v>
       </c>
       <c r="D2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A2,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>2</v>
       </c>
       <c r="E2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A2,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>4</v>
       </c>
       <c r="F2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A2,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31363,27 +31456,27 @@
         <v>257</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A3)</f>
-        <v>61</v>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A3)</f>
+        <v>62</v>
       </c>
       <c r="C3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A3,
-          Certifications!$D$3:$D$5017, TRUE)</f>
-        <v>2</v>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
+          Certifications!$D$3:$D$5018, TRUE)</f>
+        <v>3</v>
       </c>
       <c r="D3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A3,
-          Certifications!$E$3:$E$5017, TRUE)</f>
-        <v>2</v>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
+          Certifications!$E$3:$E$5018, TRUE)</f>
+        <v>3</v>
       </c>
       <c r="E3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A3,
-          Certifications!$F$3:$F$5017, TRUE)</f>
-        <v>9</v>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
+          Certifications!$F$3:$F$5018, TRUE)</f>
+        <v>10</v>
       </c>
       <c r="F3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A3,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31392,27 +31485,27 @@
         <v>544</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A4)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A4)</f>
         <v>56</v>
       </c>
       <c r="C4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A4,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>1</v>
       </c>
       <c r="D4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A4,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A4,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A4,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>1</v>
       </c>
     </row>
@@ -31421,27 +31514,27 @@
         <v>598</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A5)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A5)</f>
         <v>51</v>
       </c>
       <c r="C5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A5,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>5</v>
       </c>
       <c r="D5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A5,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A5,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A5,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31450,27 +31543,27 @@
         <v>497</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A6)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A6)</f>
         <v>51</v>
       </c>
       <c r="C6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A6,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A6,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A6,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A6,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31479,27 +31572,27 @@
         <v>155</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A7)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A7)</f>
         <v>51</v>
       </c>
       <c r="C7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A7,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A7,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A7,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A7,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31508,27 +31601,27 @@
         <v>696</v>
       </c>
       <c r="B8">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A8)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A8)</f>
         <v>54</v>
       </c>
       <c r="C8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A8,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>3</v>
       </c>
       <c r="D8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A8,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A8,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>2</v>
       </c>
       <c r="F8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A8,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31537,27 +31630,27 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A9)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A9)</f>
         <v>50</v>
       </c>
       <c r="C9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A9,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A9,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A9,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A9,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31566,27 +31659,27 @@
         <v>880</v>
       </c>
       <c r="B10">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A10)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A10)</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A10,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A10,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A10,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A10,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31595,27 +31688,27 @@
         <v>207</v>
       </c>
       <c r="B11">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A11)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A11)</f>
         <v>50</v>
       </c>
       <c r="C11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A11,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A11,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A11,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A11,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31624,27 +31717,27 @@
         <v>647</v>
       </c>
       <c r="B12">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A12)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A12)</f>
         <v>53</v>
       </c>
       <c r="C12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A12,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>1</v>
       </c>
       <c r="D12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A12,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>1</v>
       </c>
       <c r="E12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A12,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>2</v>
       </c>
       <c r="F12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A12,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31653,27 +31746,27 @@
         <v>746</v>
       </c>
       <c r="B13">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A13)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A13)</f>
         <v>50</v>
       </c>
       <c r="C13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A13,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>1</v>
       </c>
       <c r="D13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A13,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A13,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A13,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31682,27 +31775,27 @@
         <v>822</v>
       </c>
       <c r="B14">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A14)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A14)</f>
         <v>50</v>
       </c>
       <c r="C14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A14,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>1</v>
       </c>
       <c r="D14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A14,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A14,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A14,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31711,27 +31804,27 @@
         <v>311</v>
       </c>
       <c r="B15">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A15)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A15)</f>
         <v>49</v>
       </c>
       <c r="C15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A15,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A15,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A15,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A15,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31740,27 +31833,27 @@
         <v>449</v>
       </c>
       <c r="B16">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A16)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A16)</f>
         <v>48</v>
       </c>
       <c r="C16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A16,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A16,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A16,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A16,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31769,27 +31862,27 @@
         <v>775</v>
       </c>
       <c r="B17">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A17)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A17)</f>
         <v>47</v>
       </c>
       <c r="C17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A17,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>3</v>
       </c>
       <c r="D17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A17,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A17,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A17,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31798,27 +31891,27 @@
         <v>361</v>
       </c>
       <c r="B18">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A18)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A18)</f>
         <v>46</v>
       </c>
       <c r="C18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A18,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A18,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A18,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A18,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>1</v>
       </c>
     </row>
@@ -31827,27 +31920,27 @@
         <v>10</v>
       </c>
       <c r="B19">
-        <f>COUNTIF(Certifications!$B$3:$B$5017, Statistics!$A19)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A19)</f>
         <v>33</v>
       </c>
       <c r="C19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A19,
-          Certifications!$D$3:$D$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
+          Certifications!$D$3:$D$5018, TRUE)</f>
         <v>2</v>
       </c>
       <c r="D19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A19,
-          Certifications!$E$3:$E$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
+          Certifications!$E$3:$E$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A19,
-          Certifications!$F$3:$F$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
+          Certifications!$F$3:$F$5018, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5017, Statistics!$A19,
-          Certifications!$G$3:$G$5017, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
+          Certifications!$G$3:$G$5018, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31873,20 +31966,20 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <f>COUNTA(Certifications!$A$3:$A$5017)</f>
-        <v>955</v>
+        <f>COUNTA(Certifications!$A$3:$A$5018)</f>
+        <v>956</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <f ca="1">COUNTA(UNIQUE(Certifications!$B$3:$B$5017))</f>
+        <f ca="1">COUNTA(UNIQUE(Certifications!$B$3:$B$5018))</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <f ca="1">NOW()</f>
-        <v>46099.985527199075</v>
+        <v>46131.408686921299</v>
       </c>
     </row>
   </sheetData>

--- a/comprehensive_grocery_certifications.xlsx
+++ b/comprehensive_grocery_certifications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StardogChampion\TBL-Grocery-Scanner---DEVELOPMENT-VERSION-Active-development-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6963343D-0F58-4A33-99A0-3C40EDA171FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F25695B-AD1B-4CF4-A241-27367D758348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3005" uniqueCount="991">
   <si>
     <t>Product_Brand</t>
   </si>
@@ -2933,9 +2933,6 @@
     <t>canned cat food, pouch cat food, freeze-dried cat food, cat supplements, cat treats</t>
   </si>
   <si>
-    <t>skin oils, skin serums, anti-aging, anti-wrinkle, skin creams, skin moisturizers, face-lift treatments</t>
-  </si>
-  <si>
     <t>SISTERLY</t>
   </si>
   <si>
@@ -2955,6 +2952,48 @@
   </si>
   <si>
     <t>Crunch</t>
+  </si>
+  <si>
+    <t>Remedii</t>
+  </si>
+  <si>
+    <t>stain remover, degreaser, pre-wash for laundry, bathroom cleaner, carpet cleaner, floor cleaner, household cleaner, cleaning wipes</t>
+  </si>
+  <si>
+    <t>True Botanicals</t>
+  </si>
+  <si>
+    <t>skin oils, skin serums, anti-aging, anti-wrinkle, skin creams, skin moisturizers, face-lift treatments. cleansers, toners, face oils, eye treatments, body lotion, hand cream, body scrub, fragrance roller, bath bubbles and salts, body care, face care, hair care, shampoo, conditioner, soap, sun care</t>
+  </si>
+  <si>
+    <t>Meraki</t>
+  </si>
+  <si>
+    <t>shampoo, conditioner, scalp cleanse, scalp detox, hydrating shampoo, hair reparative treatment, hair repair conditioner, hair glow oil, leave-in hair conditioner, pre-shampoo masque, hair styling</t>
+  </si>
+  <si>
+    <t>Paper Products</t>
+  </si>
+  <si>
+    <t>Caboo</t>
+  </si>
+  <si>
+    <t>toilet paper, paper towels, baby wipes, flushable wipes, baby care, body care</t>
+  </si>
+  <si>
+    <t>This Works</t>
+  </si>
+  <si>
+    <t>sleep aids, sleep pillow spray, sleep shower gel, sleep beauty soak, sleep overnight cream, sleep retinoid complex, sleep breathe in, sleep beauty oil, sleep bath oil, sleep body whip, sleep body cocoon, sleep overnight cleanser, anti-wrinkle moisturizer, sun screen, bronzing serum, skin moisturizing serum, eye wrinkle care, eye wrinkle repair, skin cleansing pads, pre-shower beauty wash, leg care, hand and foot care, body oils, neck and bust, body moisturizers, leg moisturizer, leg oil</t>
+  </si>
+  <si>
+    <t>Household Goods</t>
+  </si>
+  <si>
+    <t>UNNI</t>
+  </si>
+  <si>
+    <t>sandwich bags, food storage bags, compostable food storage bags, compostable kitchen trash bags, compostable drawstring kitchen bags, compostable bags with handles, storage bags, gloves</t>
   </si>
 </sst>
 </file>
@@ -3385,7 +3424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K959"/>
+  <dimension ref="A1:K964"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -11136,7 +11175,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>257</v>
@@ -15189,14 +15228,14 @@
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
-        <v>401</v>
+        <v>977</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>361</v>
       </c>
       <c r="C404" s="2"/>
       <c r="D404" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E404" s="3" t="b">
         <v>0</v>
@@ -15205,20 +15244,24 @@
         <v>0</v>
       </c>
       <c r="G404" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H404" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H404" s="7" t="s">
+        <v>978</v>
+      </c>
       <c r="I404" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J404" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J404" s="10">
+        <v>46145</v>
+      </c>
       <c r="K404" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>361</v>
@@ -15247,7 +15290,7 @@
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>361</v>
@@ -15276,7 +15319,7 @@
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>361</v>
@@ -15305,7 +15348,7 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>361</v>
@@ -15334,17 +15377,17 @@
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
-        <v>891</v>
+        <v>405</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>929</v>
+        <v>361</v>
       </c>
       <c r="C409" s="2"/>
       <c r="D409" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E409" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F409" s="3" t="b">
         <v>0</v>
@@ -15358,25 +15401,25 @@
       </c>
       <c r="J409" s="9"/>
       <c r="K409" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
-        <v>406</v>
+        <v>891</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C410" s="2"/>
       <c r="D410" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E410" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F410" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G410" s="3" t="b">
         <v>0</v>
@@ -15392,7 +15435,7 @@
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>929</v>
@@ -15405,7 +15448,7 @@
         <v>0</v>
       </c>
       <c r="F411" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G411" s="3" t="b">
         <v>0</v>
@@ -15416,12 +15459,12 @@
       </c>
       <c r="J411" s="9"/>
       <c r="K411" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
-        <v>919</v>
+        <v>407</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>929</v>
@@ -15434,7 +15477,7 @@
         <v>0</v>
       </c>
       <c r="F412" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G412" s="3" t="b">
         <v>0</v>
@@ -15445,12 +15488,12 @@
       </c>
       <c r="J412" s="9"/>
       <c r="K412" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
-        <v>408</v>
+        <v>919</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>929</v>
@@ -15463,7 +15506,7 @@
         <v>0</v>
       </c>
       <c r="F413" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G413" s="3" t="b">
         <v>0</v>
@@ -15474,12 +15517,12 @@
       </c>
       <c r="J413" s="9"/>
       <c r="K413" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
-        <v>892</v>
+        <v>408</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>929</v>
@@ -15489,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="E414" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F414" s="3" t="b">
         <v>0</v>
@@ -15499,16 +15542,16 @@
       </c>
       <c r="H414" s="7"/>
       <c r="I414" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J414" s="9"/>
       <c r="K414" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
-        <v>409</v>
+        <v>892</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>929</v>
@@ -15518,7 +15561,7 @@
         <v>0</v>
       </c>
       <c r="E415" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F415" s="3" t="b">
         <v>0</v>
@@ -15528,16 +15571,16 @@
       </c>
       <c r="H415" s="7"/>
       <c r="I415" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J415" s="9"/>
       <c r="K415" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>929</v>
@@ -15566,7 +15609,7 @@
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
-        <v>915</v>
+        <v>410</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>929</v>
@@ -15579,7 +15622,7 @@
         <v>0</v>
       </c>
       <c r="F417" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G417" s="3" t="b">
         <v>0</v>
@@ -15590,12 +15633,12 @@
       </c>
       <c r="J417" s="9"/>
       <c r="K417" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
-        <v>890</v>
+        <v>915</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>929</v>
@@ -15605,10 +15648,10 @@
         <v>0</v>
       </c>
       <c r="E418" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F418" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="F418" s="3" t="b">
-        <v>0</v>
       </c>
       <c r="G418" s="3" t="b">
         <v>0</v>
@@ -15624,7 +15667,7 @@
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>929</v>
@@ -15634,10 +15677,10 @@
         <v>0</v>
       </c>
       <c r="E419" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F419" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G419" s="3" t="b">
         <v>0</v>
@@ -15653,7 +15696,7 @@
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
-        <v>411</v>
+        <v>898</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>929</v>
@@ -15666,7 +15709,7 @@
         <v>0</v>
       </c>
       <c r="F420" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G420" s="3" t="b">
         <v>0</v>
@@ -15677,12 +15720,12 @@
       </c>
       <c r="J420" s="9"/>
       <c r="K420" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>929</v>
@@ -15711,7 +15754,7 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>929</v>
@@ -15740,7 +15783,7 @@
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>929</v>
@@ -15769,7 +15812,7 @@
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
-        <v>893</v>
+        <v>414</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>929</v>
@@ -15779,7 +15822,7 @@
         <v>0</v>
       </c>
       <c r="E424" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F424" s="3" t="b">
         <v>0</v>
@@ -15793,12 +15836,12 @@
       </c>
       <c r="J424" s="9"/>
       <c r="K424" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
-        <v>917</v>
+        <v>893</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>929</v>
@@ -15808,10 +15851,10 @@
         <v>0</v>
       </c>
       <c r="E425" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F425" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G425" s="3" t="b">
         <v>0</v>
@@ -15827,7 +15870,7 @@
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
-        <v>104</v>
+        <v>917</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>929</v>
@@ -15840,7 +15883,7 @@
         <v>0</v>
       </c>
       <c r="F426" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G426" s="3" t="b">
         <v>0</v>
@@ -15851,12 +15894,12 @@
       </c>
       <c r="J426" s="9"/>
       <c r="K426" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
-        <v>415</v>
+        <v>104</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>929</v>
@@ -15885,7 +15928,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>929</v>
@@ -15914,7 +15957,7 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
-        <v>897</v>
+        <v>416</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>929</v>
@@ -15927,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="F429" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G429" s="3" t="b">
         <v>0</v>
@@ -15938,25 +15981,25 @@
       </c>
       <c r="J429" s="9"/>
       <c r="K429" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
-        <v>417</v>
+        <v>897</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C430" s="2"/>
       <c r="D430" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E430" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F430" s="3" t="b">
         <v>1</v>
-      </c>
-      <c r="E430" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F430" s="3" t="b">
-        <v>0</v>
       </c>
       <c r="G430" s="3" t="b">
         <v>0</v>
@@ -15972,14 +16015,14 @@
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C431" s="2"/>
       <c r="D431" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E431" s="3" t="b">
         <v>0</v>
@@ -15996,12 +16039,12 @@
       </c>
       <c r="J431" s="9"/>
       <c r="K431" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>929</v>
@@ -16030,7 +16073,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>929</v>
@@ -16059,7 +16102,7 @@
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
-        <v>916</v>
+        <v>420</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>929</v>
@@ -16072,25 +16115,23 @@
         <v>0</v>
       </c>
       <c r="F434" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G434" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H434" s="7" t="s">
-        <v>932</v>
-      </c>
+      <c r="H434" s="7"/>
       <c r="I434" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J434" s="9"/>
       <c r="K434" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
-        <v>421</v>
+        <v>916</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>929</v>
@@ -16108,7 +16149,9 @@
       <c r="G435" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H435" s="7"/>
+      <c r="H435" s="7" t="s">
+        <v>932</v>
+      </c>
       <c r="I435" s="3" t="b">
         <v>0</v>
       </c>
@@ -16119,7 +16162,7 @@
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
-        <v>114</v>
+        <v>421</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>929</v>
@@ -16132,7 +16175,7 @@
         <v>0</v>
       </c>
       <c r="F436" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G436" s="3" t="b">
         <v>0</v>
@@ -16143,12 +16186,12 @@
       </c>
       <c r="J436" s="9"/>
       <c r="K436" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
-        <v>894</v>
+        <v>114</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>929</v>
@@ -16158,7 +16201,7 @@
         <v>0</v>
       </c>
       <c r="E437" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F437" s="3" t="b">
         <v>0</v>
@@ -16168,16 +16211,16 @@
       </c>
       <c r="H437" s="7"/>
       <c r="I437" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J437" s="9"/>
       <c r="K437" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
-        <v>422</v>
+        <v>894</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>929</v>
@@ -16187,7 +16230,7 @@
         <v>0</v>
       </c>
       <c r="E438" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F438" s="3" t="b">
         <v>0</v>
@@ -16197,16 +16240,16 @@
       </c>
       <c r="H438" s="7"/>
       <c r="I438" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J438" s="9"/>
       <c r="K438" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>929</v>
@@ -16235,7 +16278,7 @@
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>929</v>
@@ -16264,7 +16307,7 @@
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
-        <v>935</v>
+        <v>424</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>929</v>
@@ -16277,25 +16320,23 @@
         <v>0</v>
       </c>
       <c r="F441" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G441" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H441" s="7" t="s">
-        <v>927</v>
-      </c>
+      <c r="H441" s="7"/>
       <c r="I441" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J441" s="9"/>
       <c r="K441" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
-        <v>878</v>
+        <v>935</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>929</v>
@@ -16313,7 +16354,9 @@
       <c r="G442" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H442" s="7"/>
+      <c r="H442" s="7" t="s">
+        <v>927</v>
+      </c>
       <c r="I442" s="3" t="b">
         <v>0</v>
       </c>
@@ -16324,7 +16367,7 @@
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
-        <v>425</v>
+        <v>878</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>929</v>
@@ -16337,7 +16380,7 @@
         <v>0</v>
       </c>
       <c r="F443" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G443" s="3" t="b">
         <v>0</v>
@@ -16348,12 +16391,12 @@
       </c>
       <c r="J443" s="9"/>
       <c r="K443" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>929</v>
@@ -16382,7 +16425,7 @@
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
-        <v>884</v>
+        <v>426</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>929</v>
@@ -16395,7 +16438,7 @@
         <v>0</v>
       </c>
       <c r="F445" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G445" s="3" t="b">
         <v>0</v>
@@ -16406,12 +16449,12 @@
       </c>
       <c r="J445" s="9"/>
       <c r="K445" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>929</v>
@@ -16440,7 +16483,7 @@
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
-        <v>119</v>
+        <v>883</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>929</v>
@@ -16450,7 +16493,7 @@
         <v>0</v>
       </c>
       <c r="E447" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F447" s="3" t="b">
         <v>1</v>
@@ -16464,12 +16507,12 @@
       </c>
       <c r="J447" s="9"/>
       <c r="K447" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
-        <v>427</v>
+        <v>119</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>929</v>
@@ -16479,10 +16522,10 @@
         <v>0</v>
       </c>
       <c r="E448" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F448" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G448" s="3" t="b">
         <v>0</v>
@@ -16498,7 +16541,7 @@
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
-        <v>888</v>
+        <v>427</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>929</v>
@@ -16511,7 +16554,7 @@
         <v>0</v>
       </c>
       <c r="F449" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G449" s="3" t="b">
         <v>0</v>
@@ -16522,12 +16565,12 @@
       </c>
       <c r="J449" s="9"/>
       <c r="K449" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
-        <v>428</v>
+        <v>888</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>929</v>
@@ -16556,7 +16599,7 @@
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>929</v>
@@ -16585,7 +16628,7 @@
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
-        <v>896</v>
+        <v>429</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>929</v>
@@ -16603,9 +16646,7 @@
       <c r="G452" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H452" s="7" t="s">
-        <v>936</v>
-      </c>
+      <c r="H452" s="7"/>
       <c r="I452" s="3" t="b">
         <v>0</v>
       </c>
@@ -16616,7 +16657,7 @@
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>929</v>
@@ -16634,7 +16675,9 @@
       <c r="G453" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H453" s="7"/>
+      <c r="H453" s="7" t="s">
+        <v>936</v>
+      </c>
       <c r="I453" s="3" t="b">
         <v>0</v>
       </c>
@@ -16645,7 +16688,7 @@
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
-        <v>430</v>
+        <v>911</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>929</v>
@@ -16658,7 +16701,7 @@
         <v>0</v>
       </c>
       <c r="F454" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G454" s="3" t="b">
         <v>0</v>
@@ -16669,12 +16712,12 @@
       </c>
       <c r="J454" s="9"/>
       <c r="K454" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>929</v>
@@ -16703,7 +16746,7 @@
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
-        <v>123</v>
+        <v>431</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>929</v>
@@ -16732,7 +16775,7 @@
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
-        <v>432</v>
+        <v>123</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>929</v>
@@ -16761,7 +16804,7 @@
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>929</v>
@@ -16790,7 +16833,7 @@
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>929</v>
@@ -16819,38 +16862,36 @@
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
-        <v>947</v>
+        <v>434</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C460" s="2"/>
       <c r="D460" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E460" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F460" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G460" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H460" s="7" t="s">
-        <v>939</v>
-      </c>
+      <c r="H460" s="7"/>
       <c r="I460" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J460" s="9"/>
       <c r="K460" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
-        <v>906</v>
+        <v>947</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>929</v>
@@ -16881,17 +16922,17 @@
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
-        <v>881</v>
+        <v>906</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C462" s="2"/>
       <c r="D462" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E462" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F462" s="3" t="b">
         <v>1</v>
@@ -16900,7 +16941,7 @@
         <v>0</v>
       </c>
       <c r="H462" s="7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="I462" s="3" t="b">
         <v>0</v>
@@ -16912,17 +16953,17 @@
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
-        <v>907</v>
+        <v>881</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C463" s="2"/>
       <c r="D463" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E463" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F463" s="3" t="b">
         <v>1</v>
@@ -16931,7 +16972,7 @@
         <v>0</v>
       </c>
       <c r="H463" s="7" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I463" s="3" t="b">
         <v>0</v>
@@ -16943,36 +16984,38 @@
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
-        <v>435</v>
+        <v>907</v>
       </c>
       <c r="B464" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C464" s="2"/>
       <c r="D464" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E464" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F464" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G464" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H464" s="7"/>
+      <c r="H464" s="7" t="s">
+        <v>941</v>
+      </c>
       <c r="I464" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J464" s="9"/>
       <c r="K464" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
-        <v>887</v>
+        <v>435</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>929</v>
@@ -16985,7 +17028,7 @@
         <v>0</v>
       </c>
       <c r="F465" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G465" s="3" t="b">
         <v>0</v>
@@ -16996,12 +17039,12 @@
       </c>
       <c r="J465" s="9"/>
       <c r="K465" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
-        <v>436</v>
+        <v>887</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>929</v>
@@ -17014,7 +17057,7 @@
         <v>0</v>
       </c>
       <c r="F466" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G466" s="3" t="b">
         <v>0</v>
@@ -17025,12 +17068,12 @@
       </c>
       <c r="J466" s="9"/>
       <c r="K466" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>929</v>
@@ -17043,7 +17086,7 @@
         <v>0</v>
       </c>
       <c r="F467" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G467" s="3" t="b">
         <v>0</v>
@@ -17054,12 +17097,12 @@
       </c>
       <c r="J467" s="9"/>
       <c r="K467" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
-        <v>131</v>
+        <v>437</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>929</v>
@@ -17072,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="F468" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G468" s="3" t="b">
         <v>0</v>
@@ -17083,12 +17126,12 @@
       </c>
       <c r="J468" s="9"/>
       <c r="K468" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
-        <v>438</v>
+        <v>131</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>929</v>
@@ -17117,7 +17160,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>929</v>
@@ -17146,7 +17189,7 @@
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
-        <v>912</v>
+        <v>439</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>929</v>
@@ -17159,7 +17202,7 @@
         <v>0</v>
       </c>
       <c r="F471" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G471" s="3" t="b">
         <v>0</v>
@@ -17170,12 +17213,12 @@
       </c>
       <c r="J471" s="9"/>
       <c r="K471" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
-        <v>902</v>
+        <v>912</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>929</v>
@@ -17204,7 +17247,7 @@
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>929</v>
@@ -17233,7 +17276,7 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>929</v>
@@ -17243,7 +17286,7 @@
         <v>0</v>
       </c>
       <c r="E474" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F474" s="3" t="b">
         <v>1</v>
@@ -17262,7 +17305,7 @@
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>929</v>
@@ -17272,7 +17315,7 @@
         <v>0</v>
       </c>
       <c r="E475" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F475" s="3" t="b">
         <v>1</v>
@@ -17291,7 +17334,7 @@
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>929</v>
@@ -17320,7 +17363,7 @@
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
-        <v>143</v>
+        <v>885</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>929</v>
@@ -17330,17 +17373,15 @@
         <v>0</v>
       </c>
       <c r="E477" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F477" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F477" s="3" t="b">
-        <v>0</v>
-      </c>
       <c r="G477" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H477" s="7" t="s">
-        <v>932</v>
-      </c>
+      <c r="H477" s="7"/>
       <c r="I477" s="3" t="b">
         <v>0</v>
       </c>
@@ -17351,7 +17392,7 @@
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" s="2" t="s">
-        <v>440</v>
+        <v>143</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>929</v>
@@ -17361,7 +17402,7 @@
         <v>0</v>
       </c>
       <c r="E478" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F478" s="3" t="b">
         <v>0</v>
@@ -17369,18 +17410,20 @@
       <c r="G478" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H478" s="7"/>
+      <c r="H478" s="7" t="s">
+        <v>932</v>
+      </c>
       <c r="I478" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J478" s="9"/>
       <c r="K478" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
-        <v>889</v>
+        <v>440</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>929</v>
@@ -17390,7 +17433,7 @@
         <v>0</v>
       </c>
       <c r="E479" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F479" s="3" t="b">
         <v>0</v>
@@ -17404,12 +17447,12 @@
       </c>
       <c r="J479" s="9"/>
       <c r="K479" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
-        <v>920</v>
+        <v>889</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>929</v>
@@ -17419,10 +17462,10 @@
         <v>0</v>
       </c>
       <c r="E480" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F480" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G480" s="3" t="b">
         <v>0</v>
@@ -17438,7 +17481,7 @@
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>929</v>
@@ -17467,7 +17510,7 @@
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
-        <v>441</v>
+        <v>910</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>929</v>
@@ -17480,7 +17523,7 @@
         <v>0</v>
       </c>
       <c r="F482" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G482" s="3" t="b">
         <v>0</v>
@@ -17491,12 +17534,12 @@
       </c>
       <c r="J482" s="9"/>
       <c r="K482" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
-        <v>886</v>
+        <v>441</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>929</v>
@@ -17509,7 +17552,7 @@
         <v>0</v>
       </c>
       <c r="F483" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G483" s="3" t="b">
         <v>0</v>
@@ -17520,12 +17563,12 @@
       </c>
       <c r="J483" s="9"/>
       <c r="K483" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>929</v>
@@ -17554,7 +17597,7 @@
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>929</v>
@@ -17583,7 +17626,7 @@
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
-        <v>914</v>
+        <v>879</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>929</v>
@@ -17612,7 +17655,7 @@
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
-        <v>442</v>
+        <v>914</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>929</v>
@@ -17641,7 +17684,7 @@
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>929</v>
@@ -17654,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="F488" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G488" s="3" t="b">
         <v>0</v>
@@ -17665,12 +17708,12 @@
       </c>
       <c r="J488" s="9"/>
       <c r="K488" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>929</v>
@@ -17699,7 +17742,7 @@
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
-        <v>877</v>
+        <v>444</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>929</v>
@@ -17712,7 +17755,7 @@
         <v>0</v>
       </c>
       <c r="F490" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G490" s="3" t="b">
         <v>0</v>
@@ -17723,12 +17766,12 @@
       </c>
       <c r="J490" s="9"/>
       <c r="K490" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
-        <v>148</v>
+        <v>877</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>929</v>
@@ -17741,7 +17784,7 @@
         <v>0</v>
       </c>
       <c r="F491" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G491" s="3" t="b">
         <v>0</v>
@@ -17752,12 +17795,12 @@
       </c>
       <c r="J491" s="9"/>
       <c r="K491" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" s="2" t="s">
-        <v>445</v>
+        <v>148</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>929</v>
@@ -17786,7 +17829,7 @@
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>929</v>
@@ -17799,7 +17842,7 @@
         <v>0</v>
       </c>
       <c r="F493" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G493" s="3" t="b">
         <v>0</v>
@@ -17810,12 +17853,12 @@
       </c>
       <c r="J493" s="9"/>
       <c r="K493" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
-        <v>899</v>
+        <v>446</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>929</v>
@@ -17844,7 +17887,7 @@
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495" s="2" t="s">
-        <v>447</v>
+        <v>899</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>929</v>
@@ -17873,7 +17916,7 @@
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496" s="2" t="s">
-        <v>895</v>
+        <v>447</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>929</v>
@@ -17902,7 +17945,7 @@
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
-        <v>918</v>
+        <v>895</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>929</v>
@@ -17912,7 +17955,7 @@
         <v>0</v>
       </c>
       <c r="E497" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F497" s="3" t="b">
         <v>1</v>
@@ -17931,20 +17974,20 @@
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
-        <v>448</v>
+        <v>918</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>449</v>
+        <v>929</v>
       </c>
       <c r="C498" s="2"/>
       <c r="D498" s="3" t="b">
         <v>0</v>
       </c>
       <c r="E498" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F498" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G498" s="3" t="b">
         <v>0</v>
@@ -17955,12 +17998,12 @@
       </c>
       <c r="J498" s="9"/>
       <c r="K498" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
-        <v>313</v>
+        <v>448</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>449</v>
@@ -17989,7 +18032,7 @@
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
-        <v>450</v>
+        <v>313</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>449</v>
@@ -18018,7 +18061,7 @@
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>449</v>
@@ -18047,7 +18090,7 @@
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>449</v>
@@ -18076,7 +18119,7 @@
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>449</v>
@@ -18105,7 +18148,7 @@
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>449</v>
@@ -18134,7 +18177,7 @@
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>449</v>
@@ -18163,7 +18206,7 @@
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A506" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>449</v>
@@ -18192,7 +18235,7 @@
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>449</v>
@@ -18221,7 +18264,7 @@
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>449</v>
@@ -18250,7 +18293,7 @@
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>449</v>
@@ -18279,7 +18322,7 @@
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>449</v>
@@ -18308,7 +18351,7 @@
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>449</v>
@@ -18337,7 +18380,7 @@
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>449</v>
@@ -18366,7 +18409,7 @@
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>449</v>
@@ -18395,7 +18438,7 @@
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>449</v>
@@ -18424,7 +18467,7 @@
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>449</v>
@@ -18453,7 +18496,7 @@
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>449</v>
@@ -18482,7 +18525,7 @@
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>449</v>
@@ -18511,7 +18554,7 @@
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A518" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>449</v>
@@ -18540,7 +18583,7 @@
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A519" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>449</v>
@@ -18569,7 +18612,7 @@
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A520" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>449</v>
@@ -18598,7 +18641,7 @@
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A521" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>449</v>
@@ -18627,7 +18670,7 @@
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A522" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>449</v>
@@ -18656,7 +18699,7 @@
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>449</v>
@@ -18685,7 +18728,7 @@
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A524" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>449</v>
@@ -18714,7 +18757,7 @@
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A525" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>449</v>
@@ -18743,7 +18786,7 @@
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A526" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>449</v>
@@ -18772,7 +18815,7 @@
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>449</v>
@@ -18801,7 +18844,7 @@
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>449</v>
@@ -18830,7 +18873,7 @@
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>449</v>
@@ -18859,7 +18902,7 @@
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>449</v>
@@ -18888,7 +18931,7 @@
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>449</v>
@@ -18917,7 +18960,7 @@
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>449</v>
@@ -18946,7 +18989,7 @@
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>449</v>
@@ -18975,7 +19018,7 @@
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>449</v>
@@ -19004,7 +19047,7 @@
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A535" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>449</v>
@@ -19033,7 +19076,7 @@
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>449</v>
@@ -19062,7 +19105,7 @@
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A537" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>449</v>
@@ -19091,7 +19134,7 @@
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>449</v>
@@ -19120,7 +19163,7 @@
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>449</v>
@@ -19149,7 +19192,7 @@
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>449</v>
@@ -19178,7 +19221,7 @@
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>449</v>
@@ -19207,7 +19250,7 @@
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A542" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>449</v>
@@ -19236,7 +19279,7 @@
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A543" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>449</v>
@@ -19265,7 +19308,7 @@
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>449</v>
@@ -19294,7 +19337,7 @@
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>449</v>
@@ -19323,10 +19366,10 @@
     </row>
     <row r="546" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>497</v>
+        <v>449</v>
       </c>
       <c r="C546" s="2"/>
       <c r="D546" s="3" t="b">
@@ -19352,7 +19395,7 @@
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
-        <v>313</v>
+        <v>496</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>497</v>
@@ -19381,7 +19424,7 @@
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
-        <v>498</v>
+        <v>313</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>497</v>
@@ -19410,7 +19453,7 @@
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>497</v>
@@ -19439,7 +19482,7 @@
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>497</v>
@@ -19468,7 +19511,7 @@
     </row>
     <row r="551" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>497</v>
@@ -19497,7 +19540,7 @@
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>497</v>
@@ -19526,7 +19569,7 @@
     </row>
     <row r="553" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>497</v>
@@ -19555,7 +19598,7 @@
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A554" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>497</v>
@@ -19584,7 +19627,7 @@
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>497</v>
@@ -19613,7 +19656,7 @@
     </row>
     <row r="556" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>497</v>
@@ -19642,7 +19685,7 @@
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>497</v>
@@ -19671,7 +19714,7 @@
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A558" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>497</v>
@@ -19700,7 +19743,7 @@
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A559" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>497</v>
@@ -19729,7 +19772,7 @@
     </row>
     <row r="560" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A560" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>497</v>
@@ -19758,7 +19801,7 @@
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A561" s="2" t="s">
-        <v>220</v>
+        <v>510</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>497</v>
@@ -19787,7 +19830,7 @@
     </row>
     <row r="562" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A562" s="2" t="s">
-        <v>511</v>
+        <v>220</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>497</v>
@@ -19816,7 +19859,7 @@
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A563" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>497</v>
@@ -19845,7 +19888,7 @@
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A564" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>497</v>
@@ -19874,7 +19917,7 @@
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A565" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>497</v>
@@ -19903,7 +19946,7 @@
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A566" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>497</v>
@@ -19932,7 +19975,7 @@
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A567" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>497</v>
@@ -19961,7 +20004,7 @@
     </row>
     <row r="568" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A568" s="2" t="s">
-        <v>227</v>
+        <v>516</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>497</v>
@@ -19990,7 +20033,7 @@
     </row>
     <row r="569" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A569" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>497</v>
@@ -20019,7 +20062,7 @@
     </row>
     <row r="570" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A570" s="2" t="s">
-        <v>517</v>
+        <v>233</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>497</v>
@@ -20048,7 +20091,7 @@
     </row>
     <row r="571" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A571" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>497</v>
@@ -20077,7 +20120,7 @@
     </row>
     <row r="572" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A572" s="2" t="s">
-        <v>237</v>
+        <v>518</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>497</v>
@@ -20106,7 +20149,7 @@
     </row>
     <row r="573" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A573" s="2" t="s">
-        <v>519</v>
+        <v>237</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>497</v>
@@ -20135,7 +20178,7 @@
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A574" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>497</v>
@@ -20164,7 +20207,7 @@
     </row>
     <row r="575" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A575" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>497</v>
@@ -20193,7 +20236,7 @@
     </row>
     <row r="576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A576" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>497</v>
@@ -20222,7 +20265,7 @@
     </row>
     <row r="577" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A577" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>497</v>
@@ -20251,7 +20294,7 @@
     </row>
     <row r="578" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A578" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>497</v>
@@ -20280,7 +20323,7 @@
     </row>
     <row r="579" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A579" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>497</v>
@@ -20309,7 +20352,7 @@
     </row>
     <row r="580" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A580" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>497</v>
@@ -20338,7 +20381,7 @@
     </row>
     <row r="581" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A581" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>497</v>
@@ -20367,7 +20410,7 @@
     </row>
     <row r="582" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A582" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>497</v>
@@ -20396,7 +20439,7 @@
     </row>
     <row r="583" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A583" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>497</v>
@@ -20425,7 +20468,7 @@
     </row>
     <row r="584" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A584" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>497</v>
@@ -20454,7 +20497,7 @@
     </row>
     <row r="585" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A585" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>497</v>
@@ -20483,7 +20526,7 @@
     </row>
     <row r="586" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A586" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>497</v>
@@ -20512,7 +20555,7 @@
     </row>
     <row r="587" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A587" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>497</v>
@@ -20541,7 +20584,7 @@
     </row>
     <row r="588" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A588" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>497</v>
@@ -20570,7 +20613,7 @@
     </row>
     <row r="589" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A589" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>497</v>
@@ -20599,7 +20642,7 @@
     </row>
     <row r="590" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A590" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>497</v>
@@ -20628,7 +20671,7 @@
     </row>
     <row r="591" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A591" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>497</v>
@@ -20657,7 +20700,7 @@
     </row>
     <row r="592" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A592" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>497</v>
@@ -20686,7 +20729,7 @@
     </row>
     <row r="593" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A593" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>497</v>
@@ -20715,7 +20758,7 @@
     </row>
     <row r="594" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A594" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>497</v>
@@ -20744,7 +20787,7 @@
     </row>
     <row r="595" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A595" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>497</v>
@@ -20773,7 +20816,7 @@
     </row>
     <row r="596" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A596" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>497</v>
@@ -20802,10 +20845,10 @@
     </row>
     <row r="597" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A597" s="2" t="s">
-        <v>876</v>
+        <v>542</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>544</v>
+        <v>497</v>
       </c>
       <c r="C597" s="2"/>
       <c r="D597" s="3" t="b">
@@ -20818,24 +20861,20 @@
         <v>0</v>
       </c>
       <c r="G597" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H597" s="7" t="s">
-        <v>955</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H597" s="7"/>
       <c r="I597" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J597" s="10">
-        <v>46095</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J597" s="9"/>
       <c r="K597" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="598" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A598" s="2" t="s">
-        <v>543</v>
+        <v>876</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>544</v>
@@ -20851,20 +20890,24 @@
         <v>0</v>
       </c>
       <c r="G598" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H598" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H598" s="7" t="s">
+        <v>955</v>
+      </c>
       <c r="I598" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J598" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J598" s="10">
+        <v>46095</v>
+      </c>
       <c r="K598" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="599" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A599" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>544</v>
@@ -20893,7 +20936,7 @@
     </row>
     <row r="600" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A600" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>544</v>
@@ -20922,7 +20965,7 @@
     </row>
     <row r="601" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A601" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>544</v>
@@ -20951,7 +20994,7 @@
     </row>
     <row r="602" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A602" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>544</v>
@@ -20980,7 +21023,7 @@
     </row>
     <row r="603" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A603" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>544</v>
@@ -21009,7 +21052,7 @@
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A604" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>544</v>
@@ -21038,7 +21081,7 @@
     </row>
     <row r="605" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A605" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>544</v>
@@ -21067,7 +21110,7 @@
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A606" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>544</v>
@@ -21096,7 +21139,7 @@
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A607" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>544</v>
@@ -21125,7 +21168,7 @@
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A608" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>544</v>
@@ -21154,7 +21197,7 @@
     </row>
     <row r="609" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A609" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>544</v>
@@ -21183,7 +21226,7 @@
     </row>
     <row r="610" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A610" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>544</v>
@@ -21212,7 +21255,7 @@
     </row>
     <row r="611" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A611" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>544</v>
@@ -21241,7 +21284,7 @@
     </row>
     <row r="612" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A612" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>544</v>
@@ -21270,7 +21313,7 @@
     </row>
     <row r="613" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A613" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>544</v>
@@ -21299,7 +21342,7 @@
     </row>
     <row r="614" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A614" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>544</v>
@@ -21328,7 +21371,7 @@
     </row>
     <row r="615" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A615" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>544</v>
@@ -21357,7 +21400,7 @@
     </row>
     <row r="616" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A616" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>544</v>
@@ -21386,7 +21429,7 @@
     </row>
     <row r="617" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A617" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>544</v>
@@ -21415,7 +21458,7 @@
     </row>
     <row r="618" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A618" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>544</v>
@@ -21444,7 +21487,7 @@
     </row>
     <row r="619" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A619" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>544</v>
@@ -21473,7 +21516,7 @@
     </row>
     <row r="620" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A620" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>544</v>
@@ -21502,7 +21545,7 @@
     </row>
     <row r="621" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A621" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>544</v>
@@ -21531,7 +21574,7 @@
     </row>
     <row r="622" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A622" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>544</v>
@@ -21560,7 +21603,7 @@
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A623" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>544</v>
@@ -21589,7 +21632,7 @@
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A624" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>544</v>
@@ -21618,7 +21661,7 @@
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A625" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>544</v>
@@ -21647,7 +21690,7 @@
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A626" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>544</v>
@@ -21676,7 +21719,7 @@
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A627" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>544</v>
@@ -21705,7 +21748,7 @@
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A628" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>544</v>
@@ -21734,14 +21777,14 @@
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A629" s="2" t="s">
-        <v>575</v>
+        <v>981</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>544</v>
       </c>
       <c r="C629" s="2"/>
       <c r="D629" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E629" s="3" t="b">
         <v>0</v>
@@ -21752,18 +21795,22 @@
       <c r="G629" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H629" s="7"/>
+      <c r="H629" s="7" t="s">
+        <v>982</v>
+      </c>
       <c r="I629" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J629" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J629" s="10">
+        <v>46145</v>
+      </c>
       <c r="K629" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A630" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>544</v>
@@ -21792,7 +21839,7 @@
     </row>
     <row r="631" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A631" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>544</v>
@@ -21821,7 +21868,7 @@
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A632" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>544</v>
@@ -21850,7 +21897,7 @@
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A633" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>544</v>
@@ -21879,7 +21926,7 @@
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A634" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>544</v>
@@ -21908,7 +21955,7 @@
     </row>
     <row r="635" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A635" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>544</v>
@@ -21937,7 +21984,7 @@
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A636" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>544</v>
@@ -21966,7 +22013,7 @@
     </row>
     <row r="637" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A637" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>544</v>
@@ -21995,7 +22042,7 @@
     </row>
     <row r="638" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A638" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>544</v>
@@ -22024,7 +22071,7 @@
     </row>
     <row r="639" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A639" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>544</v>
@@ -22053,7 +22100,7 @@
     </row>
     <row r="640" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A640" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>544</v>
@@ -22082,7 +22129,7 @@
     </row>
     <row r="641" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A641" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>544</v>
@@ -22111,7 +22158,7 @@
     </row>
     <row r="642" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A642" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>544</v>
@@ -22140,7 +22187,7 @@
     </row>
     <row r="643" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A643" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>544</v>
@@ -22169,7 +22216,7 @@
     </row>
     <row r="644" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A644" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>544</v>
@@ -22198,7 +22245,7 @@
     </row>
     <row r="645" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A645" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>544</v>
@@ -22227,7 +22274,7 @@
     </row>
     <row r="646" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A646" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>544</v>
@@ -22255,7 +22302,9 @@
       </c>
     </row>
     <row r="647" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A647" s="2"/>
+      <c r="A647" s="2" t="s">
+        <v>986</v>
+      </c>
       <c r="B647" s="2" t="s">
         <v>544</v>
       </c>
@@ -22273,13 +22322,13 @@
         <v>0</v>
       </c>
       <c r="H647" s="7" t="s">
-        <v>970</v>
+        <v>987</v>
       </c>
       <c r="I647" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J647" s="10">
-        <v>46099</v>
+        <v>46145</v>
       </c>
       <c r="K647" s="2" t="s">
         <v>875</v>
@@ -22287,7 +22336,7 @@
     </row>
     <row r="648" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A648" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>544</v>
@@ -22316,7 +22365,7 @@
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A649" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>544</v>
@@ -22345,14 +22394,14 @@
     </row>
     <row r="650" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A650" s="2" t="s">
-        <v>595</v>
+        <v>979</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>544</v>
       </c>
       <c r="C650" s="2"/>
       <c r="D650" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E650" s="3" t="b">
         <v>0</v>
@@ -22361,20 +22410,24 @@
         <v>0</v>
       </c>
       <c r="G650" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H650" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H650" s="7" t="s">
+        <v>980</v>
+      </c>
       <c r="I650" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J650" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J650" s="10">
+        <v>46145</v>
+      </c>
       <c r="K650" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="651" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A651" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>544</v>
@@ -22403,7 +22456,7 @@
     </row>
     <row r="652" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A652" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>544</v>
@@ -22432,10 +22485,10 @@
     </row>
     <row r="653" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A653" s="2" t="s">
-        <v>876</v>
+        <v>595</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>598</v>
+        <v>544</v>
       </c>
       <c r="C653" s="2"/>
       <c r="D653" s="3" t="b">
@@ -22461,14 +22514,14 @@
     </row>
     <row r="654" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A654" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>598</v>
+        <v>544</v>
       </c>
       <c r="C654" s="2"/>
       <c r="D654" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E654" s="3" t="b">
         <v>0</v>
@@ -22479,9 +22532,7 @@
       <c r="G654" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H654" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H654" s="7"/>
       <c r="I654" s="3" t="b">
         <v>0</v>
       </c>
@@ -22492,10 +22543,10 @@
     </row>
     <row r="655" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A655" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>598</v>
+        <v>544</v>
       </c>
       <c r="C655" s="2"/>
       <c r="D655" s="3" t="b">
@@ -22521,7 +22572,7 @@
     </row>
     <row r="656" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A656" s="2" t="s">
-        <v>601</v>
+        <v>876</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>598</v>
@@ -22550,14 +22601,14 @@
     </row>
     <row r="657" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A657" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C657" s="2"/>
       <c r="D657" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E657" s="3" t="b">
         <v>0</v>
@@ -22568,7 +22619,9 @@
       <c r="G657" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H657" s="7"/>
+      <c r="H657" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I657" s="3" t="b">
         <v>0</v>
       </c>
@@ -22579,7 +22632,7 @@
     </row>
     <row r="658" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A658" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>598</v>
@@ -22608,7 +22661,7 @@
     </row>
     <row r="659" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A659" s="2" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>598</v>
@@ -22637,7 +22690,7 @@
     </row>
     <row r="660" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A660" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>598</v>
@@ -22666,7 +22719,7 @@
     </row>
     <row r="661" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A661" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>598</v>
@@ -22695,7 +22748,7 @@
     </row>
     <row r="662" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A662" s="2" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>598</v>
@@ -22724,7 +22777,7 @@
     </row>
     <row r="663" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A663" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>598</v>
@@ -22753,7 +22806,7 @@
     </row>
     <row r="664" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A664" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>598</v>
@@ -22782,7 +22835,7 @@
     </row>
     <row r="665" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A665" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>598</v>
@@ -22811,7 +22864,7 @@
     </row>
     <row r="666" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A666" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>598</v>
@@ -22840,14 +22893,14 @@
     </row>
     <row r="667" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A667" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C667" s="2"/>
       <c r="D667" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E667" s="3" t="b">
         <v>0</v>
@@ -22858,9 +22911,7 @@
       <c r="G667" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H667" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H667" s="7"/>
       <c r="I667" s="3" t="b">
         <v>0</v>
       </c>
@@ -22871,7 +22922,7 @@
     </row>
     <row r="668" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A668" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>598</v>
@@ -22900,7 +22951,7 @@
     </row>
     <row r="669" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A669" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>598</v>
@@ -22929,14 +22980,14 @@
     </row>
     <row r="670" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A670" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C670" s="2"/>
       <c r="D670" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E670" s="3" t="b">
         <v>0</v>
@@ -22947,7 +22998,9 @@
       <c r="G670" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H670" s="7"/>
+      <c r="H670" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I670" s="3" t="b">
         <v>0</v>
       </c>
@@ -22958,7 +23011,7 @@
     </row>
     <row r="671" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A671" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>598</v>
@@ -22987,7 +23040,7 @@
     </row>
     <row r="672" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A672" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>598</v>
@@ -23016,7 +23069,7 @@
     </row>
     <row r="673" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A673" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>598</v>
@@ -23045,7 +23098,7 @@
     </row>
     <row r="674" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A674" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>598</v>
@@ -23074,7 +23127,7 @@
     </row>
     <row r="675" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A675" s="2" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>598</v>
@@ -23103,7 +23156,7 @@
     </row>
     <row r="676" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A676" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>598</v>
@@ -23132,7 +23185,7 @@
     </row>
     <row r="677" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A677" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>598</v>
@@ -23161,7 +23214,7 @@
     </row>
     <row r="678" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A678" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>598</v>
@@ -23190,7 +23243,7 @@
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A679" s="2" t="s">
-        <v>26</v>
+        <v>621</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>598</v>
@@ -23219,7 +23272,7 @@
     </row>
     <row r="680" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A680" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>598</v>
@@ -23248,7 +23301,7 @@
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A681" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>598</v>
@@ -23277,7 +23330,7 @@
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A682" s="2" t="s">
-        <v>626</v>
+        <v>26</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>598</v>
@@ -23306,7 +23359,7 @@
     </row>
     <row r="683" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A683" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>598</v>
@@ -23335,7 +23388,7 @@
     </row>
     <row r="684" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A684" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>598</v>
@@ -23364,7 +23417,7 @@
     </row>
     <row r="685" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A685" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>598</v>
@@ -23393,7 +23446,7 @@
     </row>
     <row r="686" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A686" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>598</v>
@@ -23422,14 +23475,14 @@
     </row>
     <row r="687" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A687" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C687" s="2"/>
       <c r="D687" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E687" s="3" t="b">
         <v>0</v>
@@ -23440,20 +23493,18 @@
       <c r="G687" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H687" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H687" s="7"/>
       <c r="I687" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J687" s="9"/>
       <c r="K687" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="688" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A688" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>598</v>
@@ -23482,7 +23533,7 @@
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A689" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B689" s="2" t="s">
         <v>598</v>
@@ -23511,14 +23562,14 @@
     </row>
     <row r="690" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A690" s="2" t="s">
-        <v>346</v>
+        <v>631</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C690" s="2"/>
       <c r="D690" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E690" s="3" t="b">
         <v>0</v>
@@ -23529,18 +23580,20 @@
       <c r="G690" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H690" s="7"/>
+      <c r="H690" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I690" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J690" s="9"/>
       <c r="K690" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="691" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A691" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>598</v>
@@ -23569,7 +23622,7 @@
     </row>
     <row r="692" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A692" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>598</v>
@@ -23598,7 +23651,7 @@
     </row>
     <row r="693" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A693" s="2" t="s">
-        <v>636</v>
+        <v>346</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>598</v>
@@ -23627,7 +23680,7 @@
     </row>
     <row r="694" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A694" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>598</v>
@@ -23656,7 +23709,7 @@
     </row>
     <row r="695" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A695" s="2" t="s">
-        <v>37</v>
+        <v>635</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>598</v>
@@ -23685,7 +23738,7 @@
     </row>
     <row r="696" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A696" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>598</v>
@@ -23714,14 +23767,14 @@
     </row>
     <row r="697" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A697" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C697" s="2"/>
       <c r="D697" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E697" s="3" t="b">
         <v>0</v>
@@ -23732,20 +23785,18 @@
       <c r="G697" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H697" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H697" s="7"/>
       <c r="I697" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J697" s="9"/>
       <c r="K697" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="698" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A698" s="2" t="s">
-        <v>640</v>
+        <v>37</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>598</v>
@@ -23774,7 +23825,7 @@
     </row>
     <row r="699" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A699" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>598</v>
@@ -23803,14 +23854,14 @@
     </row>
     <row r="700" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A700" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C700" s="2"/>
       <c r="D700" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E700" s="3" t="b">
         <v>0</v>
@@ -23821,18 +23872,20 @@
       <c r="G700" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H700" s="7"/>
+      <c r="H700" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I700" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J700" s="9"/>
       <c r="K700" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="701" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A701" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B701" s="2" t="s">
         <v>598</v>
@@ -23861,7 +23914,7 @@
     </row>
     <row r="702" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A702" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B702" s="2" t="s">
         <v>598</v>
@@ -23890,14 +23943,14 @@
     </row>
     <row r="703" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A703" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B703" s="2" t="s">
         <v>598</v>
       </c>
       <c r="C703" s="2"/>
       <c r="D703" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E703" s="3" t="b">
         <v>0</v>
@@ -23908,27 +23961,25 @@
       <c r="G703" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H703" s="7" t="s">
-        <v>931</v>
-      </c>
+      <c r="H703" s="7"/>
       <c r="I703" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J703" s="9"/>
       <c r="K703" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A704" s="2" t="s">
-        <v>964</v>
+        <v>643</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>966</v>
+        <v>598</v>
       </c>
       <c r="C704" s="2"/>
       <c r="D704" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E704" s="3" t="b">
         <v>0</v>
@@ -23939,25 +23990,21 @@
       <c r="G704" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H704" s="7" t="s">
-        <v>967</v>
-      </c>
+      <c r="H704" s="7"/>
       <c r="I704" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J704" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J704" s="9"/>
       <c r="K704" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="705" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A705" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>647</v>
+        <v>598</v>
       </c>
       <c r="C705" s="2"/>
       <c r="D705" s="3" t="b">
@@ -23983,14 +24030,14 @@
     </row>
     <row r="706" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A706" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>647</v>
+        <v>598</v>
       </c>
       <c r="C706" s="2"/>
       <c r="D706" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E706" s="3" t="b">
         <v>0</v>
@@ -24001,25 +24048,27 @@
       <c r="G706" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H706" s="7"/>
+      <c r="H706" s="7" t="s">
+        <v>931</v>
+      </c>
       <c r="I706" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J706" s="9"/>
       <c r="K706" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="707" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A707" s="2" t="s">
-        <v>649</v>
+        <v>964</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>647</v>
+        <v>966</v>
       </c>
       <c r="C707" s="2"/>
       <c r="D707" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E707" s="3" t="b">
         <v>0</v>
@@ -24030,28 +24079,32 @@
       <c r="G707" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H707" s="7"/>
+      <c r="H707" s="7" t="s">
+        <v>967</v>
+      </c>
       <c r="I707" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J707" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J707" s="10">
+        <v>46099</v>
+      </c>
       <c r="K707" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A708" s="2" t="s">
-        <v>874</v>
+        <v>646</v>
       </c>
       <c r="B708" s="2" t="s">
         <v>647</v>
       </c>
       <c r="C708" s="2"/>
       <c r="D708" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E708" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F708" s="3" t="b">
         <v>0</v>
@@ -24059,20 +24112,18 @@
       <c r="G708" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H708" s="7" t="s">
-        <v>937</v>
-      </c>
+      <c r="H708" s="7"/>
       <c r="I708" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J708" s="9"/>
       <c r="K708" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="709" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A709" s="2" t="s">
-        <v>45</v>
+        <v>648</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>647</v>
@@ -24101,7 +24152,7 @@
     </row>
     <row r="710" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A710" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B710" s="2" t="s">
         <v>647</v>
@@ -24130,17 +24181,17 @@
     </row>
     <row r="711" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A711" s="2" t="s">
-        <v>651</v>
+        <v>874</v>
       </c>
       <c r="B711" s="2" t="s">
         <v>647</v>
       </c>
       <c r="C711" s="2"/>
       <c r="D711" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E711" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F711" s="3" t="b">
         <v>0</v>
@@ -24148,18 +24199,20 @@
       <c r="G711" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H711" s="7"/>
+      <c r="H711" s="7" t="s">
+        <v>937</v>
+      </c>
       <c r="I711" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J711" s="9"/>
       <c r="K711" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="712" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A712" s="2" t="s">
-        <v>909</v>
+        <v>45</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>647</v>
@@ -24172,7 +24225,7 @@
         <v>0</v>
       </c>
       <c r="F712" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G712" s="3" t="b">
         <v>0</v>
@@ -24183,12 +24236,12 @@
       </c>
       <c r="J712" s="9"/>
       <c r="K712" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="713" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A713" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B713" s="2" t="s">
         <v>647</v>
@@ -24217,7 +24270,7 @@
     </row>
     <row r="714" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A714" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B714" s="2" t="s">
         <v>647</v>
@@ -24246,7 +24299,7 @@
     </row>
     <row r="715" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A715" s="2" t="s">
-        <v>654</v>
+        <v>909</v>
       </c>
       <c r="B715" s="2" t="s">
         <v>647</v>
@@ -24259,7 +24312,7 @@
         <v>0</v>
       </c>
       <c r="F715" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G715" s="3" t="b">
         <v>0</v>
@@ -24270,12 +24323,12 @@
       </c>
       <c r="J715" s="9"/>
       <c r="K715" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="716" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A716" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B716" s="2" t="s">
         <v>647</v>
@@ -24304,7 +24357,7 @@
     </row>
     <row r="717" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A717" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B717" s="2" t="s">
         <v>647</v>
@@ -24333,7 +24386,7 @@
     </row>
     <row r="718" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A718" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B718" s="2" t="s">
         <v>647</v>
@@ -24362,7 +24415,7 @@
     </row>
     <row r="719" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A719" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B719" s="2" t="s">
         <v>647</v>
@@ -24391,7 +24444,7 @@
     </row>
     <row r="720" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A720" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B720" s="2" t="s">
         <v>647</v>
@@ -24420,7 +24473,7 @@
     </row>
     <row r="721" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A721" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B721" s="2" t="s">
         <v>647</v>
@@ -24449,7 +24502,7 @@
     </row>
     <row r="722" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A722" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B722" s="2" t="s">
         <v>647</v>
@@ -24478,7 +24531,7 @@
     </row>
     <row r="723" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A723" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>647</v>
@@ -24507,7 +24560,7 @@
     </row>
     <row r="724" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A724" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B724" s="2" t="s">
         <v>647</v>
@@ -24536,7 +24589,7 @@
     </row>
     <row r="725" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A725" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B725" s="2" t="s">
         <v>647</v>
@@ -24565,7 +24618,7 @@
     </row>
     <row r="726" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A726" s="2" t="s">
-        <v>328</v>
+        <v>662</v>
       </c>
       <c r="B726" s="2" t="s">
         <v>647</v>
@@ -24594,7 +24647,7 @@
     </row>
     <row r="727" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A727" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B727" s="2" t="s">
         <v>647</v>
@@ -24623,7 +24676,7 @@
     </row>
     <row r="728" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A728" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B728" s="2" t="s">
         <v>647</v>
@@ -24652,7 +24705,7 @@
     </row>
     <row r="729" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A729" s="2" t="s">
-        <v>667</v>
+        <v>328</v>
       </c>
       <c r="B729" s="2" t="s">
         <v>647</v>
@@ -24681,7 +24734,7 @@
     </row>
     <row r="730" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A730" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B730" s="2" t="s">
         <v>647</v>
@@ -24710,7 +24763,7 @@
     </row>
     <row r="731" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A731" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B731" s="2" t="s">
         <v>647</v>
@@ -24739,7 +24792,7 @@
     </row>
     <row r="732" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A732" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B732" s="2" t="s">
         <v>647</v>
@@ -24768,7 +24821,7 @@
     </row>
     <row r="733" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A733" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B733" s="2" t="s">
         <v>647</v>
@@ -24797,7 +24850,7 @@
     </row>
     <row r="734" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A734" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B734" s="2" t="s">
         <v>647</v>
@@ -24826,7 +24879,7 @@
     </row>
     <row r="735" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A735" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B735" s="2" t="s">
         <v>647</v>
@@ -24855,7 +24908,7 @@
     </row>
     <row r="736" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A736" s="2" t="s">
-        <v>938</v>
+        <v>671</v>
       </c>
       <c r="B736" s="2" t="s">
         <v>647</v>
@@ -24868,25 +24921,23 @@
         <v>0</v>
       </c>
       <c r="F736" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G736" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H736" s="7" t="s">
-        <v>937</v>
-      </c>
+      <c r="H736" s="7"/>
       <c r="I736" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J736" s="9"/>
       <c r="K736" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="737" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A737" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B737" s="2" t="s">
         <v>647</v>
@@ -24915,7 +24966,7 @@
     </row>
     <row r="738" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A738" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B738" s="2" t="s">
         <v>647</v>
@@ -24944,7 +24995,7 @@
     </row>
     <row r="739" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A739" s="2" t="s">
-        <v>676</v>
+        <v>938</v>
       </c>
       <c r="B739" s="2" t="s">
         <v>647</v>
@@ -24957,23 +25008,25 @@
         <v>0</v>
       </c>
       <c r="F739" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G739" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H739" s="7"/>
+      <c r="H739" s="7" t="s">
+        <v>937</v>
+      </c>
       <c r="I739" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J739" s="9"/>
       <c r="K739" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="740" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A740" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B740" s="2" t="s">
         <v>647</v>
@@ -25002,7 +25055,7 @@
     </row>
     <row r="741" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A741" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>647</v>
@@ -25031,7 +25084,7 @@
     </row>
     <row r="742" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A742" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B742" s="2" t="s">
         <v>647</v>
@@ -25060,7 +25113,7 @@
     </row>
     <row r="743" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A743" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>647</v>
@@ -25089,7 +25142,7 @@
     </row>
     <row r="744" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A744" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B744" s="2" t="s">
         <v>647</v>
@@ -25118,7 +25171,7 @@
     </row>
     <row r="745" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A745" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B745" s="2" t="s">
         <v>647</v>
@@ -25147,7 +25200,7 @@
     </row>
     <row r="746" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A746" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B746" s="2" t="s">
         <v>647</v>
@@ -25176,7 +25229,7 @@
     </row>
     <row r="747" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A747" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B747" s="2" t="s">
         <v>647</v>
@@ -25205,7 +25258,7 @@
     </row>
     <row r="748" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A748" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B748" s="2" t="s">
         <v>647</v>
@@ -25234,7 +25287,7 @@
     </row>
     <row r="749" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A749" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B749" s="2" t="s">
         <v>647</v>
@@ -25263,7 +25316,7 @@
     </row>
     <row r="750" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A750" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B750" s="2" t="s">
         <v>647</v>
@@ -25292,7 +25345,7 @@
     </row>
     <row r="751" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A751" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B751" s="2" t="s">
         <v>647</v>
@@ -25321,7 +25374,7 @@
     </row>
     <row r="752" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A752" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B752" s="2" t="s">
         <v>647</v>
@@ -25350,7 +25403,7 @@
     </row>
     <row r="753" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A753" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B753" s="2" t="s">
         <v>647</v>
@@ -25379,7 +25432,7 @@
     </row>
     <row r="754" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A754" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B754" s="2" t="s">
         <v>647</v>
@@ -25408,7 +25461,7 @@
     </row>
     <row r="755" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A755" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B755" s="2" t="s">
         <v>647</v>
@@ -25437,7 +25490,7 @@
     </row>
     <row r="756" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A756" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B756" s="2" t="s">
         <v>647</v>
@@ -25466,7 +25519,7 @@
     </row>
     <row r="757" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A757" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B757" s="2" t="s">
         <v>647</v>
@@ -25495,10 +25548,10 @@
     </row>
     <row r="758" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A758" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>696</v>
+        <v>647</v>
       </c>
       <c r="C758" s="2"/>
       <c r="D758" s="3" t="b">
@@ -25524,10 +25577,10 @@
     </row>
     <row r="759" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A759" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>696</v>
+        <v>647</v>
       </c>
       <c r="C759" s="2"/>
       <c r="D759" s="3" t="b">
@@ -25553,10 +25606,10 @@
     </row>
     <row r="760" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A760" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>696</v>
+        <v>647</v>
       </c>
       <c r="C760" s="2"/>
       <c r="D760" s="3" t="b">
@@ -25582,7 +25635,7 @@
     </row>
     <row r="761" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A761" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B761" s="2" t="s">
         <v>696</v>
@@ -25611,7 +25664,7 @@
     </row>
     <row r="762" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A762" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B762" s="2" t="s">
         <v>696</v>
@@ -25640,7 +25693,7 @@
     </row>
     <row r="763" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A763" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B763" s="2" t="s">
         <v>696</v>
@@ -25669,7 +25722,7 @@
     </row>
     <row r="764" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A764" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B764" s="2" t="s">
         <v>696</v>
@@ -25698,7 +25751,7 @@
     </row>
     <row r="765" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A765" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B765" s="2" t="s">
         <v>696</v>
@@ -25711,7 +25764,7 @@
         <v>0</v>
       </c>
       <c r="F765" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G765" s="3" t="b">
         <v>0</v>
@@ -25722,12 +25775,12 @@
       </c>
       <c r="J765" s="9"/>
       <c r="K765" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="766" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A766" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B766" s="2" t="s">
         <v>696</v>
@@ -25756,7 +25809,7 @@
     </row>
     <row r="767" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A767" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B767" s="2" t="s">
         <v>696</v>
@@ -25785,7 +25838,7 @@
     </row>
     <row r="768" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A768" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B768" s="2" t="s">
         <v>696</v>
@@ -25798,7 +25851,7 @@
         <v>0</v>
       </c>
       <c r="F768" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G768" s="3" t="b">
         <v>0</v>
@@ -25809,12 +25862,12 @@
       </c>
       <c r="J768" s="9"/>
       <c r="K768" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="769" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A769" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B769" s="2" t="s">
         <v>696</v>
@@ -25843,7 +25896,7 @@
     </row>
     <row r="770" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A770" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B770" s="2" t="s">
         <v>696</v>
@@ -25872,7 +25925,7 @@
     </row>
     <row r="771" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A771" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B771" s="2" t="s">
         <v>696</v>
@@ -25901,7 +25954,7 @@
     </row>
     <row r="772" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A772" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B772" s="2" t="s">
         <v>696</v>
@@ -25930,7 +25983,7 @@
     </row>
     <row r="773" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A773" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B773" s="2" t="s">
         <v>696</v>
@@ -25959,7 +26012,7 @@
     </row>
     <row r="774" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A774" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B774" s="2" t="s">
         <v>696</v>
@@ -25988,14 +26041,14 @@
     </row>
     <row r="775" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A775" s="2" t="s">
-        <v>952</v>
+        <v>710</v>
       </c>
       <c r="B775" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C775" s="2"/>
       <c r="D775" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E775" s="3" t="b">
         <v>0</v>
@@ -26006,22 +26059,18 @@
       <c r="G775" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H775" s="7" t="s">
-        <v>953</v>
-      </c>
+      <c r="H775" s="7"/>
       <c r="I775" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J775" s="10">
-        <v>46095</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J775" s="9"/>
       <c r="K775" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="776" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A776" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B776" s="2" t="s">
         <v>696</v>
@@ -26050,7 +26099,7 @@
     </row>
     <row r="777" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A777" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B777" s="2" t="s">
         <v>696</v>
@@ -26079,14 +26128,14 @@
     </row>
     <row r="778" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A778" s="2" t="s">
-        <v>715</v>
+        <v>952</v>
       </c>
       <c r="B778" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C778" s="2"/>
       <c r="D778" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E778" s="3" t="b">
         <v>0</v>
@@ -26097,18 +26146,22 @@
       <c r="G778" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H778" s="7"/>
+      <c r="H778" s="7" t="s">
+        <v>953</v>
+      </c>
       <c r="I778" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J778" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J778" s="10">
+        <v>46095</v>
+      </c>
       <c r="K778" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="779" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A779" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B779" s="2" t="s">
         <v>696</v>
@@ -26137,7 +26190,7 @@
     </row>
     <row r="780" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A780" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B780" s="2" t="s">
         <v>696</v>
@@ -26166,7 +26219,7 @@
     </row>
     <row r="781" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A781" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B781" s="2" t="s">
         <v>696</v>
@@ -26195,7 +26248,7 @@
     </row>
     <row r="782" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A782" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B782" s="2" t="s">
         <v>696</v>
@@ -26224,7 +26277,7 @@
     </row>
     <row r="783" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A783" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B783" s="2" t="s">
         <v>696</v>
@@ -26253,7 +26306,7 @@
     </row>
     <row r="784" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A784" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B784" s="2" t="s">
         <v>696</v>
@@ -26282,7 +26335,7 @@
     </row>
     <row r="785" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A785" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>696</v>
@@ -26311,7 +26364,7 @@
     </row>
     <row r="786" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A786" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B786" s="2" t="s">
         <v>696</v>
@@ -26340,7 +26393,7 @@
     </row>
     <row r="787" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A787" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B787" s="2" t="s">
         <v>696</v>
@@ -26369,7 +26422,7 @@
     </row>
     <row r="788" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A788" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B788" s="2" t="s">
         <v>696</v>
@@ -26398,7 +26451,7 @@
     </row>
     <row r="789" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A789" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B789" s="2" t="s">
         <v>696</v>
@@ -26427,7 +26480,7 @@
     </row>
     <row r="790" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A790" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B790" s="2" t="s">
         <v>696</v>
@@ -26456,7 +26509,7 @@
     </row>
     <row r="791" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A791" s="2" t="s">
-        <v>887</v>
+        <v>725</v>
       </c>
       <c r="B791" s="2" t="s">
         <v>696</v>
@@ -26469,7 +26522,7 @@
         <v>0</v>
       </c>
       <c r="F791" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G791" s="3" t="b">
         <v>0</v>
@@ -26480,12 +26533,12 @@
       </c>
       <c r="J791" s="9"/>
       <c r="K791" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="792" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A792" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B792" s="2" t="s">
         <v>696</v>
@@ -26514,7 +26567,7 @@
     </row>
     <row r="793" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A793" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B793" s="2" t="s">
         <v>696</v>
@@ -26543,7 +26596,7 @@
     </row>
     <row r="794" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A794" s="2" t="s">
-        <v>730</v>
+        <v>887</v>
       </c>
       <c r="B794" s="2" t="s">
         <v>696</v>
@@ -26556,7 +26609,7 @@
         <v>0</v>
       </c>
       <c r="F794" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G794" s="3" t="b">
         <v>0</v>
@@ -26567,12 +26620,12 @@
       </c>
       <c r="J794" s="9"/>
       <c r="K794" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="795" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A795" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B795" s="2" t="s">
         <v>696</v>
@@ -26601,7 +26654,7 @@
     </row>
     <row r="796" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A796" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B796" s="2" t="s">
         <v>696</v>
@@ -26630,7 +26683,7 @@
     </row>
     <row r="797" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A797" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B797" s="2" t="s">
         <v>696</v>
@@ -26659,7 +26712,7 @@
     </row>
     <row r="798" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A798" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B798" s="2" t="s">
         <v>696</v>
@@ -26688,7 +26741,7 @@
     </row>
     <row r="799" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A799" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B799" s="2" t="s">
         <v>696</v>
@@ -26717,7 +26770,7 @@
     </row>
     <row r="800" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A800" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B800" s="2" t="s">
         <v>696</v>
@@ -26746,7 +26799,7 @@
     </row>
     <row r="801" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A801" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B801" s="2" t="s">
         <v>696</v>
@@ -26775,7 +26828,7 @@
     </row>
     <row r="802" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A802" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B802" s="2" t="s">
         <v>696</v>
@@ -26804,14 +26857,14 @@
     </row>
     <row r="803" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A803" s="2" t="s">
-        <v>971</v>
+        <v>736</v>
       </c>
       <c r="B803" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C803" s="2"/>
       <c r="D803" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E803" s="3" t="b">
         <v>0</v>
@@ -26822,22 +26875,18 @@
       <c r="G803" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H803" s="7" t="s">
-        <v>972</v>
-      </c>
+      <c r="H803" s="7"/>
       <c r="I803" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J803" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J803" s="9"/>
       <c r="K803" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="804" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A804" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B804" s="2" t="s">
         <v>696</v>
@@ -26866,7 +26915,7 @@
     </row>
     <row r="805" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A805" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B805" s="2" t="s">
         <v>696</v>
@@ -26895,14 +26944,14 @@
     </row>
     <row r="806" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A806" s="2" t="s">
-        <v>741</v>
+        <v>970</v>
       </c>
       <c r="B806" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C806" s="2"/>
       <c r="D806" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E806" s="3" t="b">
         <v>0</v>
@@ -26913,18 +26962,22 @@
       <c r="G806" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H806" s="7"/>
+      <c r="H806" s="7" t="s">
+        <v>971</v>
+      </c>
       <c r="I806" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J806" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J806" s="10">
+        <v>46099</v>
+      </c>
       <c r="K806" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="807" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A807" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B807" s="2" t="s">
         <v>696</v>
@@ -26953,7 +27006,7 @@
     </row>
     <row r="808" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A808" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B808" s="2" t="s">
         <v>696</v>
@@ -26982,7 +27035,7 @@
     </row>
     <row r="809" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A809" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B809" s="2" t="s">
         <v>696</v>
@@ -27011,14 +27064,14 @@
     </row>
     <row r="810" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A810" s="2" t="s">
-        <v>961</v>
+        <v>742</v>
       </c>
       <c r="B810" s="2" t="s">
         <v>696</v>
       </c>
       <c r="C810" s="2"/>
       <c r="D810" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E810" s="3" t="b">
         <v>0</v>
@@ -27029,22 +27082,18 @@
       <c r="G810" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H810" s="7" t="s">
-        <v>962</v>
-      </c>
+      <c r="H810" s="7"/>
       <c r="I810" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J810" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J810" s="9"/>
       <c r="K810" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="811" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A811" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B811" s="2" t="s">
         <v>696</v>
@@ -27073,10 +27122,10 @@
     </row>
     <row r="812" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A812" s="2" t="s">
-        <v>648</v>
+        <v>744</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>746</v>
+        <v>696</v>
       </c>
       <c r="C812" s="2"/>
       <c r="D812" s="3" t="b">
@@ -27102,14 +27151,14 @@
     </row>
     <row r="813" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A813" s="2" t="s">
-        <v>747</v>
+        <v>961</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>746</v>
+        <v>696</v>
       </c>
       <c r="C813" s="2"/>
       <c r="D813" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E813" s="3" t="b">
         <v>0</v>
@@ -27120,21 +27169,25 @@
       <c r="G813" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H813" s="7"/>
+      <c r="H813" s="7" t="s">
+        <v>962</v>
+      </c>
       <c r="I813" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J813" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J813" s="10">
+        <v>46099</v>
+      </c>
       <c r="K813" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="814" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A814" s="2" t="s">
-        <v>208</v>
+        <v>745</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>746</v>
+        <v>696</v>
       </c>
       <c r="C814" s="2"/>
       <c r="D814" s="3" t="b">
@@ -27160,14 +27213,14 @@
     </row>
     <row r="815" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A815" s="2" t="s">
-        <v>748</v>
+        <v>989</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>746</v>
+        <v>988</v>
       </c>
       <c r="C815" s="2"/>
       <c r="D815" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E815" s="3" t="b">
         <v>0</v>
@@ -27178,18 +27231,22 @@
       <c r="G815" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H815" s="7"/>
+      <c r="H815" s="7" t="s">
+        <v>990</v>
+      </c>
       <c r="I815" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J815" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J815" s="10">
+        <v>46145</v>
+      </c>
       <c r="K815" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="816" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A816" s="2" t="s">
-        <v>749</v>
+        <v>648</v>
       </c>
       <c r="B816" s="2" t="s">
         <v>746</v>
@@ -27218,7 +27275,7 @@
     </row>
     <row r="817" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A817" s="2" t="s">
-        <v>214</v>
+        <v>747</v>
       </c>
       <c r="B817" s="2" t="s">
         <v>746</v>
@@ -27247,7 +27304,7 @@
     </row>
     <row r="818" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A818" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B818" s="2" t="s">
         <v>746</v>
@@ -27276,7 +27333,7 @@
     </row>
     <row r="819" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A819" s="2" t="s">
-        <v>656</v>
+        <v>748</v>
       </c>
       <c r="B819" s="2" t="s">
         <v>746</v>
@@ -27305,7 +27362,7 @@
     </row>
     <row r="820" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A820" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B820" s="2" t="s">
         <v>746</v>
@@ -27334,7 +27391,7 @@
     </row>
     <row r="821" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A821" s="2" t="s">
-        <v>19</v>
+        <v>214</v>
       </c>
       <c r="B821" s="2" t="s">
         <v>746</v>
@@ -27363,7 +27420,7 @@
     </row>
     <row r="822" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A822" s="2" t="s">
-        <v>751</v>
+        <v>216</v>
       </c>
       <c r="B822" s="2" t="s">
         <v>746</v>
@@ -27392,7 +27449,7 @@
     </row>
     <row r="823" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A823" s="2" t="s">
-        <v>325</v>
+        <v>656</v>
       </c>
       <c r="B823" s="2" t="s">
         <v>746</v>
@@ -27421,7 +27478,7 @@
     </row>
     <row r="824" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A824" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B824" s="2" t="s">
         <v>746</v>
@@ -27450,7 +27507,7 @@
     </row>
     <row r="825" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A825" s="2" t="s">
-        <v>753</v>
+        <v>19</v>
       </c>
       <c r="B825" s="2" t="s">
         <v>746</v>
@@ -27479,7 +27536,7 @@
     </row>
     <row r="826" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A826" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B826" s="2" t="s">
         <v>746</v>
@@ -27508,7 +27565,7 @@
     </row>
     <row r="827" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A827" s="2" t="s">
-        <v>755</v>
+        <v>325</v>
       </c>
       <c r="B827" s="2" t="s">
         <v>746</v>
@@ -27537,7 +27594,7 @@
     </row>
     <row r="828" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A828" s="2" t="s">
-        <v>22</v>
+        <v>752</v>
       </c>
       <c r="B828" s="2" t="s">
         <v>746</v>
@@ -27566,7 +27623,7 @@
     </row>
     <row r="829" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A829" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B829" s="2" t="s">
         <v>746</v>
@@ -27595,7 +27652,7 @@
     </row>
     <row r="830" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A830" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B830" s="2" t="s">
         <v>746</v>
@@ -27624,7 +27681,7 @@
     </row>
     <row r="831" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A831" s="2" t="s">
-        <v>23</v>
+        <v>755</v>
       </c>
       <c r="B831" s="2" t="s">
         <v>746</v>
@@ -27653,7 +27710,7 @@
     </row>
     <row r="832" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A832" s="2" t="s">
-        <v>758</v>
+        <v>22</v>
       </c>
       <c r="B832" s="2" t="s">
         <v>746</v>
@@ -27682,7 +27739,7 @@
     </row>
     <row r="833" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A833" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="B833" s="2" t="s">
         <v>746</v>
@@ -27711,7 +27768,7 @@
     </row>
     <row r="834" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A834" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B834" s="2" t="s">
         <v>746</v>
@@ -27740,7 +27797,7 @@
     </row>
     <row r="835" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A835" s="2" t="s">
-        <v>761</v>
+        <v>23</v>
       </c>
       <c r="B835" s="2" t="s">
         <v>746</v>
@@ -27769,7 +27826,7 @@
     </row>
     <row r="836" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A836" s="2" t="s">
-        <v>233</v>
+        <v>758</v>
       </c>
       <c r="B836" s="2" t="s">
         <v>746</v>
@@ -27798,7 +27855,7 @@
     </row>
     <row r="837" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A837" s="2" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B837" s="2" t="s">
         <v>746</v>
@@ -27827,7 +27884,7 @@
     </row>
     <row r="838" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A838" s="2" t="s">
-        <v>28</v>
+        <v>760</v>
       </c>
       <c r="B838" s="2" t="s">
         <v>746</v>
@@ -27856,7 +27913,7 @@
     </row>
     <row r="839" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A839" s="2" t="s">
-        <v>626</v>
+        <v>761</v>
       </c>
       <c r="B839" s="2" t="s">
         <v>746</v>
@@ -27885,7 +27942,7 @@
     </row>
     <row r="840" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A840" s="2" t="s">
-        <v>763</v>
+        <v>233</v>
       </c>
       <c r="B840" s="2" t="s">
         <v>746</v>
@@ -27914,7 +27971,7 @@
     </row>
     <row r="841" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A841" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B841" s="2" t="s">
         <v>746</v>
@@ -27943,7 +28000,7 @@
     </row>
     <row r="842" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A842" s="2" t="s">
-        <v>342</v>
+        <v>28</v>
       </c>
       <c r="B842" s="2" t="s">
         <v>746</v>
@@ -27972,7 +28029,7 @@
     </row>
     <row r="843" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A843" s="2" t="s">
-        <v>765</v>
+        <v>626</v>
       </c>
       <c r="B843" s="2" t="s">
         <v>746</v>
@@ -28001,7 +28058,7 @@
     </row>
     <row r="844" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A844" s="2" t="s">
-        <v>480</v>
+        <v>763</v>
       </c>
       <c r="B844" s="2" t="s">
         <v>746</v>
@@ -28030,7 +28087,7 @@
     </row>
     <row r="845" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A845" s="2" t="s">
-        <v>30</v>
+        <v>764</v>
       </c>
       <c r="B845" s="2" t="s">
         <v>746</v>
@@ -28059,7 +28116,7 @@
     </row>
     <row r="846" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A846" s="2" t="s">
-        <v>766</v>
+        <v>342</v>
       </c>
       <c r="B846" s="2" t="s">
         <v>746</v>
@@ -28088,14 +28145,14 @@
     </row>
     <row r="847" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A847" s="2" t="s">
-        <v>32</v>
+        <v>765</v>
       </c>
       <c r="B847" s="2" t="s">
         <v>746</v>
       </c>
       <c r="C847" s="2"/>
       <c r="D847" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E847" s="3" t="b">
         <v>0</v>
@@ -28106,22 +28163,18 @@
       <c r="G847" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H847" s="7" t="s">
-        <v>951</v>
-      </c>
+      <c r="H847" s="7"/>
       <c r="I847" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J847" s="10">
-        <v>46095</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J847" s="9"/>
       <c r="K847" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="848" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A848" s="2" t="s">
-        <v>767</v>
+        <v>480</v>
       </c>
       <c r="B848" s="2" t="s">
         <v>746</v>
@@ -28150,7 +28203,7 @@
     </row>
     <row r="849" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A849" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B849" s="2" t="s">
         <v>746</v>
@@ -28179,7 +28232,7 @@
     </row>
     <row r="850" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A850" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B850" s="2" t="s">
         <v>746</v>
@@ -28208,14 +28261,14 @@
     </row>
     <row r="851" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A851" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B851" s="2" t="s">
         <v>746</v>
       </c>
       <c r="C851" s="2"/>
       <c r="D851" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E851" s="3" t="b">
         <v>0</v>
@@ -28226,18 +28279,22 @@
       <c r="G851" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H851" s="7"/>
+      <c r="H851" s="7" t="s">
+        <v>951</v>
+      </c>
       <c r="I851" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J851" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J851" s="10">
+        <v>46095</v>
+      </c>
       <c r="K851" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="852" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A852" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B852" s="2" t="s">
         <v>746</v>
@@ -28266,7 +28323,7 @@
     </row>
     <row r="853" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A853" s="2" t="s">
-        <v>770</v>
+        <v>34</v>
       </c>
       <c r="B853" s="2" t="s">
         <v>746</v>
@@ -28295,7 +28352,7 @@
     </row>
     <row r="854" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A854" s="2" t="s">
-        <v>37</v>
+        <v>768</v>
       </c>
       <c r="B854" s="2" t="s">
         <v>746</v>
@@ -28324,7 +28381,7 @@
     </row>
     <row r="855" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A855" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B855" s="2" t="s">
         <v>746</v>
@@ -28353,7 +28410,7 @@
     </row>
     <row r="856" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A856" s="2" t="s">
-        <v>639</v>
+        <v>769</v>
       </c>
       <c r="B856" s="2" t="s">
         <v>746</v>
@@ -28382,7 +28439,7 @@
     </row>
     <row r="857" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A857" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B857" s="2" t="s">
         <v>746</v>
@@ -28411,7 +28468,7 @@
     </row>
     <row r="858" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A858" s="2" t="s">
-        <v>772</v>
+        <v>37</v>
       </c>
       <c r="B858" s="2" t="s">
         <v>746</v>
@@ -28440,7 +28497,7 @@
     </row>
     <row r="859" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A859" s="2" t="s">
-        <v>773</v>
+        <v>38</v>
       </c>
       <c r="B859" s="2" t="s">
         <v>746</v>
@@ -28469,7 +28526,7 @@
     </row>
     <row r="860" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A860" s="2" t="s">
-        <v>876</v>
+        <v>639</v>
       </c>
       <c r="B860" s="2" t="s">
         <v>746</v>
@@ -28498,7 +28555,7 @@
     </row>
     <row r="861" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A861" s="2" t="s">
-        <v>42</v>
+        <v>771</v>
       </c>
       <c r="B861" s="2" t="s">
         <v>746</v>
@@ -28527,14 +28584,14 @@
     </row>
     <row r="862" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A862" s="2" t="s">
-        <v>973</v>
+        <v>772</v>
       </c>
       <c r="B862" s="2" t="s">
-        <v>975</v>
+        <v>746</v>
       </c>
       <c r="C862" s="2"/>
       <c r="D862" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E862" s="3" t="b">
         <v>0</v>
@@ -28545,25 +28602,21 @@
       <c r="G862" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H862" s="7" t="s">
-        <v>976</v>
-      </c>
+      <c r="H862" s="7"/>
       <c r="I862" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J862" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J862" s="9"/>
       <c r="K862" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="863" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A863" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B863" s="2" t="s">
-        <v>775</v>
+        <v>746</v>
       </c>
       <c r="C863" s="2"/>
       <c r="D863" s="3" t="b">
@@ -28589,10 +28642,10 @@
     </row>
     <row r="864" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A864" s="2" t="s">
-        <v>776</v>
+        <v>876</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>775</v>
+        <v>746</v>
       </c>
       <c r="C864" s="2"/>
       <c r="D864" s="3" t="b">
@@ -28618,10 +28671,10 @@
     </row>
     <row r="865" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A865" s="2" t="s">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>775</v>
+        <v>746</v>
       </c>
       <c r="C865" s="2"/>
       <c r="D865" s="3" t="b">
@@ -28647,14 +28700,14 @@
     </row>
     <row r="866" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A866" s="2" t="s">
-        <v>778</v>
+        <v>972</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>775</v>
+        <v>974</v>
       </c>
       <c r="C866" s="2"/>
       <c r="D866" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E866" s="3" t="b">
         <v>0</v>
@@ -28665,25 +28718,29 @@
       <c r="G866" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H866" s="7"/>
+      <c r="H866" s="7" t="s">
+        <v>975</v>
+      </c>
       <c r="I866" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J866" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J866" s="10">
+        <v>46099</v>
+      </c>
       <c r="K866" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="867" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A867" s="2" t="s">
-        <v>779</v>
+        <v>984</v>
       </c>
       <c r="B867" s="2" t="s">
-        <v>775</v>
+        <v>983</v>
       </c>
       <c r="C867" s="2"/>
       <c r="D867" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E867" s="3" t="b">
         <v>0</v>
@@ -28692,20 +28749,24 @@
         <v>0</v>
       </c>
       <c r="G867" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H867" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H867" s="7" t="s">
+        <v>985</v>
+      </c>
       <c r="I867" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J867" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J867" s="10">
+        <v>46145</v>
+      </c>
       <c r="K867" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="868" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A868" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B868" s="2" t="s">
         <v>775</v>
@@ -28734,14 +28795,14 @@
     </row>
     <row r="869" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A869" s="2" t="s">
-        <v>973</v>
+        <v>776</v>
       </c>
       <c r="B869" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C869" s="2"/>
       <c r="D869" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E869" s="3" t="b">
         <v>0</v>
@@ -28752,22 +28813,18 @@
       <c r="G869" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H869" s="7" t="s">
-        <v>974</v>
-      </c>
+      <c r="H869" s="7"/>
       <c r="I869" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J869" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J869" s="9"/>
       <c r="K869" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="870" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A870" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B870" s="2" t="s">
         <v>775</v>
@@ -28796,7 +28853,7 @@
     </row>
     <row r="871" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A871" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B871" s="2" t="s">
         <v>775</v>
@@ -28825,7 +28882,7 @@
     </row>
     <row r="872" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A872" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B872" s="2" t="s">
         <v>775</v>
@@ -28854,7 +28911,7 @@
     </row>
     <row r="873" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A873" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B873" s="2" t="s">
         <v>775</v>
@@ -28883,7 +28940,7 @@
     </row>
     <row r="874" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A874" s="2" t="s">
-        <v>785</v>
+        <v>972</v>
       </c>
       <c r="B874" s="2" t="s">
         <v>775</v>
@@ -28902,7 +28959,7 @@
         <v>0</v>
       </c>
       <c r="H874" s="7" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="I874" s="3" t="b">
         <v>1</v>
@@ -28916,7 +28973,7 @@
     </row>
     <row r="875" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A875" s="2" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B875" s="2" t="s">
         <v>775</v>
@@ -28945,7 +29002,7 @@
     </row>
     <row r="876" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A876" s="2" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B876" s="2" t="s">
         <v>775</v>
@@ -28974,7 +29031,7 @@
     </row>
     <row r="877" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A877" s="2" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B877" s="2" t="s">
         <v>775</v>
@@ -29003,7 +29060,7 @@
     </row>
     <row r="878" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A878" s="2" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B878" s="2" t="s">
         <v>775</v>
@@ -29032,14 +29089,14 @@
     </row>
     <row r="879" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A879" s="2" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B879" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C879" s="2"/>
       <c r="D879" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E879" s="3" t="b">
         <v>0</v>
@@ -29050,18 +29107,22 @@
       <c r="G879" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H879" s="7"/>
+      <c r="H879" s="7" t="s">
+        <v>969</v>
+      </c>
       <c r="I879" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J879" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J879" s="10">
+        <v>46099</v>
+      </c>
       <c r="K879" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="880" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A880" s="2" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B880" s="2" t="s">
         <v>775</v>
@@ -29090,14 +29151,14 @@
     </row>
     <row r="881" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A881" s="2" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B881" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C881" s="2"/>
       <c r="D881" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E881" s="3" t="b">
         <v>0</v>
@@ -29108,22 +29169,18 @@
       <c r="G881" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H881" s="7" t="s">
-        <v>968</v>
-      </c>
+      <c r="H881" s="7"/>
       <c r="I881" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J881" s="10">
-        <v>46099</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J881" s="9"/>
       <c r="K881" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="882" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A882" s="2" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="B882" s="2" t="s">
         <v>775</v>
@@ -29152,7 +29209,7 @@
     </row>
     <row r="883" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A883" s="2" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="B883" s="2" t="s">
         <v>775</v>
@@ -29181,7 +29238,7 @@
     </row>
     <row r="884" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A884" s="2" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B884" s="2" t="s">
         <v>775</v>
@@ -29210,7 +29267,7 @@
     </row>
     <row r="885" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A885" s="2" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="B885" s="2" t="s">
         <v>775</v>
@@ -29239,14 +29296,14 @@
     </row>
     <row r="886" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A886" s="2" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B886" s="2" t="s">
         <v>775</v>
       </c>
       <c r="C886" s="2"/>
       <c r="D886" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E886" s="3" t="b">
         <v>0</v>
@@ -29257,18 +29314,22 @@
       <c r="G886" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H886" s="7"/>
+      <c r="H886" s="7" t="s">
+        <v>968</v>
+      </c>
       <c r="I886" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J886" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="J886" s="10">
+        <v>46099</v>
+      </c>
       <c r="K886" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="887" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A887" s="2" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="B887" s="2" t="s">
         <v>775</v>
@@ -29297,7 +29358,7 @@
     </row>
     <row r="888" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A888" s="2" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="B888" s="2" t="s">
         <v>775</v>
@@ -29326,7 +29387,7 @@
     </row>
     <row r="889" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A889" s="2" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>775</v>
@@ -29355,7 +29416,7 @@
     </row>
     <row r="890" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A890" s="2" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B890" s="2" t="s">
         <v>775</v>
@@ -29384,7 +29445,7 @@
     </row>
     <row r="891" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A891" s="2" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="B891" s="2" t="s">
         <v>775</v>
@@ -29413,7 +29474,7 @@
     </row>
     <row r="892" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A892" s="2" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="B892" s="2" t="s">
         <v>775</v>
@@ -29442,7 +29503,7 @@
     </row>
     <row r="893" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A893" s="2" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B893" s="2" t="s">
         <v>775</v>
@@ -29471,7 +29532,7 @@
     </row>
     <row r="894" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A894" s="2" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="B894" s="2" t="s">
         <v>775</v>
@@ -29500,7 +29561,7 @@
     </row>
     <row r="895" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A895" s="2" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="B895" s="2" t="s">
         <v>775</v>
@@ -29529,7 +29590,7 @@
     </row>
     <row r="896" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A896" s="2" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B896" s="2" t="s">
         <v>775</v>
@@ -29558,7 +29619,7 @@
     </row>
     <row r="897" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A897" s="2" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="B897" s="2" t="s">
         <v>775</v>
@@ -29587,7 +29648,7 @@
     </row>
     <row r="898" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A898" s="2" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B898" s="2" t="s">
         <v>775</v>
@@ -29616,7 +29677,7 @@
     </row>
     <row r="899" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A899" s="2" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="B899" s="2" t="s">
         <v>775</v>
@@ -29645,7 +29706,7 @@
     </row>
     <row r="900" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A900" s="2" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="B900" s="2" t="s">
         <v>775</v>
@@ -29674,7 +29735,7 @@
     </row>
     <row r="901" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A901" s="2" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B901" s="2" t="s">
         <v>775</v>
@@ -29703,7 +29764,7 @@
     </row>
     <row r="902" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A902" s="2" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="B902" s="2" t="s">
         <v>775</v>
@@ -29732,7 +29793,7 @@
     </row>
     <row r="903" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A903" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B903" s="2" t="s">
         <v>775</v>
@@ -29761,7 +29822,7 @@
     </row>
     <row r="904" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A904" s="2" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="B904" s="2" t="s">
         <v>775</v>
@@ -29790,7 +29851,7 @@
     </row>
     <row r="905" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A905" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="B905" s="2" t="s">
         <v>775</v>
@@ -29819,7 +29880,7 @@
     </row>
     <row r="906" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A906" s="2" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="B906" s="2" t="s">
         <v>775</v>
@@ -29848,7 +29909,7 @@
     </row>
     <row r="907" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A907" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B907" s="2" t="s">
         <v>775</v>
@@ -29877,7 +29938,7 @@
     </row>
     <row r="908" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A908" s="2" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B908" s="2" t="s">
         <v>775</v>
@@ -29906,7 +29967,7 @@
     </row>
     <row r="909" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A909" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="B909" s="2" t="s">
         <v>775</v>
@@ -29935,10 +29996,10 @@
     </row>
     <row r="910" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A910" s="2" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B910" s="2" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
       <c r="C910" s="2"/>
       <c r="D910" s="3" t="b">
@@ -29964,10 +30025,10 @@
     </row>
     <row r="911" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A911" s="2" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B911" s="2" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
       <c r="C911" s="2"/>
       <c r="D911" s="3" t="b">
@@ -29993,10 +30054,10 @@
     </row>
     <row r="912" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A912" s="2" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="B912" s="2" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
       <c r="C912" s="2"/>
       <c r="D912" s="3" t="b">
@@ -30022,10 +30083,10 @@
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A913" s="2" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="B913" s="2" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
       <c r="C913" s="2"/>
       <c r="D913" s="3" t="b">
@@ -30051,10 +30112,10 @@
     </row>
     <row r="914" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A914" s="2" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="B914" s="2" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
       <c r="C914" s="2"/>
       <c r="D914" s="3" t="b">
@@ -30080,7 +30141,7 @@
     </row>
     <row r="915" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A915" s="2" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="B915" s="2" t="s">
         <v>822</v>
@@ -30109,7 +30170,7 @@
     </row>
     <row r="916" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A916" s="2" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="B916" s="2" t="s">
         <v>822</v>
@@ -30138,7 +30199,7 @@
     </row>
     <row r="917" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A917" s="2" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="B917" s="2" t="s">
         <v>822</v>
@@ -30167,7 +30228,7 @@
     </row>
     <row r="918" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A918" s="2" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="B918" s="2" t="s">
         <v>822</v>
@@ -30196,7 +30257,7 @@
     </row>
     <row r="919" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A919" s="2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="B919" s="2" t="s">
         <v>822</v>
@@ -30225,7 +30286,7 @@
     </row>
     <row r="920" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A920" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="B920" s="2" t="s">
         <v>822</v>
@@ -30254,7 +30315,7 @@
     </row>
     <row r="921" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A921" s="2" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="B921" s="2" t="s">
         <v>822</v>
@@ -30283,7 +30344,7 @@
     </row>
     <row r="922" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A922" s="2" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="B922" s="2" t="s">
         <v>822</v>
@@ -30312,7 +30373,7 @@
     </row>
     <row r="923" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A923" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="B923" s="2" t="s">
         <v>822</v>
@@ -30341,7 +30402,7 @@
     </row>
     <row r="924" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A924" s="2" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="B924" s="2" t="s">
         <v>822</v>
@@ -30370,7 +30431,7 @@
     </row>
     <row r="925" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A925" s="2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B925" s="2" t="s">
         <v>822</v>
@@ -30399,7 +30460,7 @@
     </row>
     <row r="926" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A926" s="2" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="B926" s="2" t="s">
         <v>822</v>
@@ -30428,7 +30489,7 @@
     </row>
     <row r="927" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A927" s="2" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B927" s="2" t="s">
         <v>822</v>
@@ -30457,7 +30518,7 @@
     </row>
     <row r="928" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A928" s="2" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="B928" s="2" t="s">
         <v>822</v>
@@ -30486,7 +30547,7 @@
     </row>
     <row r="929" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A929" s="2" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="B929" s="2" t="s">
         <v>822</v>
@@ -30515,7 +30576,7 @@
     </row>
     <row r="930" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A930" s="2" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B930" s="2" t="s">
         <v>822</v>
@@ -30544,7 +30605,7 @@
     </row>
     <row r="931" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A931" s="2" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B931" s="2" t="s">
         <v>822</v>
@@ -30573,7 +30634,7 @@
     </row>
     <row r="932" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A932" s="2" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="B932" s="2" t="s">
         <v>822</v>
@@ -30602,7 +30663,7 @@
     </row>
     <row r="933" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A933" s="2" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="B933" s="2" t="s">
         <v>822</v>
@@ -30631,7 +30692,7 @@
     </row>
     <row r="934" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A934" s="2" t="s">
-        <v>945</v>
+        <v>841</v>
       </c>
       <c r="B934" s="2" t="s">
         <v>822</v>
@@ -30649,9 +30710,7 @@
       <c r="G934" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H934" s="7" t="s">
-        <v>946</v>
-      </c>
+      <c r="H934" s="7"/>
       <c r="I934" s="3" t="b">
         <v>0</v>
       </c>
@@ -30662,7 +30721,7 @@
     </row>
     <row r="935" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A935" s="2" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B935" s="2" t="s">
         <v>822</v>
@@ -30691,7 +30750,7 @@
     </row>
     <row r="936" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A936" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B936" s="2" t="s">
         <v>822</v>
@@ -30720,7 +30779,7 @@
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A937" s="2" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B937" s="2" t="s">
         <v>822</v>
@@ -30749,7 +30808,7 @@
     </row>
     <row r="938" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A938" s="2" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="B938" s="2" t="s">
         <v>822</v>
@@ -30778,7 +30837,7 @@
     </row>
     <row r="939" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A939" s="2" t="s">
-        <v>850</v>
+        <v>945</v>
       </c>
       <c r="B939" s="2" t="s">
         <v>822</v>
@@ -30796,7 +30855,9 @@
       <c r="G939" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H939" s="7"/>
+      <c r="H939" s="7" t="s">
+        <v>946</v>
+      </c>
       <c r="I939" s="3" t="b">
         <v>0</v>
       </c>
@@ -30807,7 +30868,7 @@
     </row>
     <row r="940" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A940" s="2" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="B940" s="2" t="s">
         <v>822</v>
@@ -30836,14 +30897,14 @@
     </row>
     <row r="941" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A941" s="2" t="s">
-        <v>956</v>
+        <v>847</v>
       </c>
       <c r="B941" s="2" t="s">
         <v>822</v>
       </c>
       <c r="C941" s="2"/>
       <c r="D941" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E941" s="3" t="b">
         <v>0</v>
@@ -30854,20 +30915,18 @@
       <c r="G941" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H941" s="7" t="s">
-        <v>957</v>
-      </c>
+      <c r="H941" s="7"/>
       <c r="I941" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J941" s="9"/>
       <c r="K941" s="2" t="s">
-        <v>875</v>
+        <v>11</v>
       </c>
     </row>
     <row r="942" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A942" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B942" s="2" t="s">
         <v>822</v>
@@ -30896,7 +30955,7 @@
     </row>
     <row r="943" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A943" s="2" t="s">
-        <v>735</v>
+        <v>849</v>
       </c>
       <c r="B943" s="2" t="s">
         <v>822</v>
@@ -30925,7 +30984,7 @@
     </row>
     <row r="944" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A944" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B944" s="2" t="s">
         <v>822</v>
@@ -30954,7 +31013,7 @@
     </row>
     <row r="945" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A945" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B945" s="2" t="s">
         <v>822</v>
@@ -30983,14 +31042,14 @@
     </row>
     <row r="946" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A946" s="2" t="s">
-        <v>855</v>
+        <v>956</v>
       </c>
       <c r="B946" s="2" t="s">
         <v>822</v>
       </c>
       <c r="C946" s="2"/>
       <c r="D946" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E946" s="3" t="b">
         <v>0</v>
@@ -31001,18 +31060,20 @@
       <c r="G946" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H946" s="7"/>
+      <c r="H946" s="7" t="s">
+        <v>957</v>
+      </c>
       <c r="I946" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J946" s="9"/>
       <c r="K946" s="2" t="s">
-        <v>11</v>
+        <v>875</v>
       </c>
     </row>
     <row r="947" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A947" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B947" s="2" t="s">
         <v>822</v>
@@ -31041,7 +31102,7 @@
     </row>
     <row r="948" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A948" s="2" t="s">
-        <v>857</v>
+        <v>735</v>
       </c>
       <c r="B948" s="2" t="s">
         <v>822</v>
@@ -31070,7 +31131,7 @@
     </row>
     <row r="949" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A949" s="2" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B949" s="2" t="s">
         <v>822</v>
@@ -31099,7 +31160,7 @@
     </row>
     <row r="950" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A950" s="2" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="B950" s="2" t="s">
         <v>822</v>
@@ -31128,7 +31189,7 @@
     </row>
     <row r="951" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A951" s="2" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="B951" s="2" t="s">
         <v>822</v>
@@ -31157,7 +31218,7 @@
     </row>
     <row r="952" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A952" s="2" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B952" s="2" t="s">
         <v>822</v>
@@ -31186,7 +31247,7 @@
     </row>
     <row r="953" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A953" s="2" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="B953" s="2" t="s">
         <v>822</v>
@@ -31215,7 +31276,7 @@
     </row>
     <row r="954" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A954" s="2" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="B954" s="2" t="s">
         <v>822</v>
@@ -31244,7 +31305,7 @@
     </row>
     <row r="955" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A955" s="2" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="B955" s="2" t="s">
         <v>822</v>
@@ -31273,7 +31334,7 @@
     </row>
     <row r="956" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A956" s="2" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="B956" s="2" t="s">
         <v>822</v>
@@ -31302,7 +31363,7 @@
     </row>
     <row r="957" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A957" s="2" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="B957" s="2" t="s">
         <v>822</v>
@@ -31331,7 +31392,7 @@
     </row>
     <row r="958" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A958" s="2" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="B958" s="2" t="s">
         <v>822</v>
@@ -31360,7 +31421,7 @@
     </row>
     <row r="959" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A959" s="2" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="B959" s="2" t="s">
         <v>822</v>
@@ -31384,6 +31445,151 @@
       </c>
       <c r="J959" s="9"/>
       <c r="K959" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="960" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A960" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B960" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C960" s="2"/>
+      <c r="D960" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E960" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F960" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G960" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H960" s="7"/>
+      <c r="I960" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J960" s="9"/>
+      <c r="K960" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="961" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A961" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B961" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C961" s="2"/>
+      <c r="D961" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E961" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F961" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G961" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H961" s="7"/>
+      <c r="I961" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J961" s="9"/>
+      <c r="K961" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="962" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A962" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B962" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C962" s="2"/>
+      <c r="D962" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E962" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F962" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G962" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H962" s="7"/>
+      <c r="I962" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J962" s="9"/>
+      <c r="K962" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="963" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A963" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B963" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C963" s="2"/>
+      <c r="D963" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E963" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F963" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G963" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H963" s="7"/>
+      <c r="I963" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J963" s="9"/>
+      <c r="K963" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="964" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A964" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B964" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C964" s="2"/>
+      <c r="D964" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E964" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F964" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G964" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H964" s="7"/>
+      <c r="I964" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J964" s="9"/>
+      <c r="K964" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -31427,27 +31633,27 @@
         <v>95</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A2)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A2)</f>
         <v>64</v>
       </c>
       <c r="C2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A2,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>3</v>
       </c>
       <c r="D2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A2,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>2</v>
       </c>
       <c r="E2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A2,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>4</v>
       </c>
       <c r="F2">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A2,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A2,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31456,27 +31662,27 @@
         <v>257</v>
       </c>
       <c r="B3">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A3)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A3)</f>
         <v>62</v>
       </c>
       <c r="C3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A3,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>3</v>
       </c>
       <c r="D3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A3,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>3</v>
       </c>
       <c r="E3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A3,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>10</v>
       </c>
       <c r="F3">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A3,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A3,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31485,28 +31691,28 @@
         <v>544</v>
       </c>
       <c r="B4">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A4)</f>
-        <v>56</v>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A4)</f>
+        <v>58</v>
       </c>
       <c r="C4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
-          Certifications!$D$3:$D$5018, TRUE)</f>
-        <v>1</v>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A4,
+          Certifications!$D$3:$D$5023, TRUE)</f>
+        <v>3</v>
       </c>
       <c r="D4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A4,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A4,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A4,
-          Certifications!$G$3:$G$5018, TRUE)</f>
-        <v>1</v>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A4,
+          Certifications!$G$3:$G$5023, TRUE)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -31514,27 +31720,27 @@
         <v>598</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A5)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A5)</f>
         <v>51</v>
       </c>
       <c r="C5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A5,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>5</v>
       </c>
       <c r="D5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A5,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A5,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A5,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A5,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31543,27 +31749,27 @@
         <v>497</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A6)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A6)</f>
         <v>51</v>
       </c>
       <c r="C6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A6,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A6,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A6,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F6">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A6,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A6,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31572,27 +31778,27 @@
         <v>155</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A7)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A7)</f>
         <v>51</v>
       </c>
       <c r="C7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A7,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A7,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A7,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A7,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A7,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31601,27 +31807,27 @@
         <v>696</v>
       </c>
       <c r="B8">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A8)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A8)</f>
         <v>54</v>
       </c>
       <c r="C8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A8,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>3</v>
       </c>
       <c r="D8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A8,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A8,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>2</v>
       </c>
       <c r="F8">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A8,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A8,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31630,27 +31836,27 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A9)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A9)</f>
         <v>50</v>
       </c>
       <c r="C9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A9,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A9,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A9,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F9">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A9,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A9,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31659,27 +31865,27 @@
         <v>880</v>
       </c>
       <c r="B10">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A10)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A10)</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A10,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A10,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A10,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A10,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A10,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31688,27 +31894,27 @@
         <v>207</v>
       </c>
       <c r="B11">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A11)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A11)</f>
         <v>50</v>
       </c>
       <c r="C11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A11,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A11,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A11,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F11">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A11,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A11,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31717,27 +31923,27 @@
         <v>647</v>
       </c>
       <c r="B12">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A12)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A12)</f>
         <v>53</v>
       </c>
       <c r="C12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A12,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>1</v>
       </c>
       <c r="D12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A12,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>1</v>
       </c>
       <c r="E12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A12,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>2</v>
       </c>
       <c r="F12">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A12,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A12,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31746,27 +31952,27 @@
         <v>746</v>
       </c>
       <c r="B13">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A13)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A13)</f>
         <v>50</v>
       </c>
       <c r="C13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A13,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>1</v>
       </c>
       <c r="D13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A13,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A13,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F13">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A13,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A13,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31775,27 +31981,27 @@
         <v>822</v>
       </c>
       <c r="B14">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A14)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A14)</f>
         <v>50</v>
       </c>
       <c r="C14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A14,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>1</v>
       </c>
       <c r="D14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A14,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A14,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F14">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A14,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A14,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31804,27 +32010,27 @@
         <v>311</v>
       </c>
       <c r="B15">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A15)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A15)</f>
         <v>49</v>
       </c>
       <c r="C15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A15,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A15,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A15,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F15">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A15,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A15,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31833,27 +32039,27 @@
         <v>449</v>
       </c>
       <c r="B16">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A16)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A16)</f>
         <v>48</v>
       </c>
       <c r="C16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A16,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="D16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A16,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A16,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F16">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A16,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A16,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31862,27 +32068,27 @@
         <v>775</v>
       </c>
       <c r="B17">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A17)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A17)</f>
         <v>47</v>
       </c>
       <c r="C17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A17,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>3</v>
       </c>
       <c r="D17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A17,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A17,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F17">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A17,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A17,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31891,28 +32097,28 @@
         <v>361</v>
       </c>
       <c r="B18">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A18)</f>
-        <v>46</v>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A18)</f>
+        <v>47</v>
       </c>
       <c r="C18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
-          Certifications!$D$3:$D$5018, TRUE)</f>
-        <v>0</v>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A18,
+          Certifications!$D$3:$D$5023, TRUE)</f>
+        <v>1</v>
       </c>
       <c r="D18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A18,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A18,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F18">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A18,
-          Certifications!$G$3:$G$5018, TRUE)</f>
-        <v>1</v>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A18,
+          Certifications!$G$3:$G$5023, TRUE)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -31920,27 +32126,27 @@
         <v>10</v>
       </c>
       <c r="B19">
-        <f>COUNTIF(Certifications!$B$3:$B$5018, Statistics!$A19)</f>
+        <f>COUNTIF(Certifications!$B$3:$B$5023, Statistics!$A19)</f>
         <v>33</v>
       </c>
       <c r="C19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
-          Certifications!$D$3:$D$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A19,
+          Certifications!$D$3:$D$5023, TRUE)</f>
         <v>2</v>
       </c>
       <c r="D19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
-          Certifications!$E$3:$E$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A19,
+          Certifications!$E$3:$E$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="E19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
-          Certifications!$F$3:$F$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A19,
+          Certifications!$F$3:$F$5023, TRUE)</f>
         <v>0</v>
       </c>
       <c r="F19">
-        <f>COUNTIFS(Certifications!$B$3:$B$5018, Statistics!$A19,
-          Certifications!$G$3:$G$5018, TRUE)</f>
+        <f>COUNTIFS(Certifications!$B$3:$B$5023, Statistics!$A19,
+          Certifications!$G$3:$G$5023, TRUE)</f>
         <v>0</v>
       </c>
     </row>
@@ -31966,20 +32172,20 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <f>COUNTA(Certifications!$A$3:$A$5018)</f>
-        <v>956</v>
+        <f>COUNTA(Certifications!$A$3:$A$5023)</f>
+        <v>962</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <f ca="1">COUNTA(UNIQUE(Certifications!$B$3:$B$5018))</f>
+        <f ca="1">COUNTA(UNIQUE(Certifications!$B$3:$B$5023))</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <f ca="1">NOW()</f>
-        <v>46131.408686921299</v>
+        <v>46145.683432060185</v>
       </c>
     </row>
   </sheetData>
